--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G10">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G16">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G24">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G35">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.39</v>
+        <v>2.85</v>
       </c>
       <c r="O47">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="P47">
-        <v>6.76</v>
+        <v>2.46</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.85</v>
+        <v>1.39</v>
       </c>
       <c r="O48">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="P48">
-        <v>2.46</v>
+        <v>6.76</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G56">

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G10">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.85</v>
+        <v>1.39</v>
       </c>
       <c r="O47">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="P47">
-        <v>2.46</v>
+        <v>6.76</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="Q48">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G24">

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q53">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU64"/>
+  <dimension ref="A1:AU67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-08-24 12:30:00</t>
+          <t>2026-08-24 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-08-24 12:30:00</t>
+          <t>2026-08-24 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-08-24 12:45:00</t>
+          <t>2026-08-24 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-08-24 13:00:00</t>
+          <t>2026-08-24 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-24 13:00:00</t>
+          <t>2026-08-24 12:45:00</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G10">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-08-24 13:30:00</t>
+          <t>2026-08-24 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G13">
@@ -2424,17 +2424,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-08-24 13:30:00</t>
+          <t>2026-08-24 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G14">
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G15">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="G16">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-08-24 13:40:00</t>
+          <t>2026-08-24 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-08-24 14:00:00</t>
+          <t>2026-08-24 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-08-24 14:00:00</t>
+          <t>2026-08-24 13:40:00</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.72</v>
+        <v>2.31</v>
       </c>
       <c r="O22">
-        <v>3.44</v>
+        <v>3.02</v>
       </c>
       <c r="P22">
-        <v>2.61</v>
+        <v>3.24</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -4016,22 +4016,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G23">
@@ -4179,22 +4179,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.58</v>
+        <v>2.02</v>
       </c>
       <c r="O25">
-        <v>3.66</v>
+        <v>3.54</v>
       </c>
       <c r="P25">
-        <v>2.43</v>
+        <v>3.39</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4668,22 +4668,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G29">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-08-24 14:05:00</t>
+          <t>2026-08-24 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-08-24 14:30:00</t>
+          <t>2026-08-24 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.07</v>
+        <v>1.56</v>
       </c>
       <c r="O31">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="P31">
-        <v>3.6</v>
+        <v>5.03</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-08-24 14:30:00</t>
+          <t>2026-08-24 14:05:00</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G32">
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:00</t>
+          <t>2026-08-24 14:30:00</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:00</t>
+          <t>2026-08-24 14:30:00</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G35">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-08-24 15:15:00</t>
+          <t>2026-08-24 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-08-24 15:30:00</t>
+          <t>2026-08-24 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-08-24 15:30:00</t>
+          <t>2026-08-24 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-08-24 15:30:00</t>
+          <t>2026-08-24 15:15:00</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="O40">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P40">
-        <v>2.65</v>
+        <v>3.46</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-08-24 15:45:00</t>
+          <t>2026-08-24 15:30:00</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-08-24 15:45:00</t>
+          <t>2026-08-24 15:30:00</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.17</v>
+        <v>2.65</v>
       </c>
       <c r="O43">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P43">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:00:00</t>
+          <t>2026-08-24 15:30:00</t>
         </is>
       </c>
     </row>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.34</v>
+        <v>1.69</v>
       </c>
       <c r="O44">
-        <v>3.81</v>
+        <v>3.74</v>
       </c>
       <c r="P44">
-        <v>2.21</v>
+        <v>4.8</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AB44">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:00:00</t>
+          <t>2026-08-24 15:45:00</t>
         </is>
       </c>
     </row>
@@ -7597,27 +7597,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:00:00</t>
+          <t>2026-08-24 15:45:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.85</v>
+        <v>2.17</v>
       </c>
       <c r="O46">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P46">
-        <v>2.46</v>
+        <v>3.25</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.39</v>
+        <v>3.34</v>
       </c>
       <c r="O47">
-        <v>4.5</v>
+        <v>3.81</v>
       </c>
       <c r="P47">
-        <v>6.76</v>
+        <v>2.21</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.27</v>
+        <v>2.85</v>
       </c>
       <c r="O49">
         <v>2.9</v>
       </c>
       <c r="P49">
-        <v>3.26</v>
+        <v>2.46</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:15:00</t>
+          <t>2026-08-24 16:00:00</t>
         </is>
       </c>
     </row>
@@ -8575,27 +8575,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G51">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:15:00</t>
+          <t>2026-08-24 16:00:00</t>
         </is>
       </c>
     </row>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-08-24 16:15:00</t>
+          <t>2026-08-24 16:00:00</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-08-24 16:30:00</t>
+          <t>2026-08-24 16:15:00</t>
         </is>
       </c>
     </row>
@@ -9064,27 +9064,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-08-24 16:30:00</t>
+          <t>2026-08-24 16:15:00</t>
         </is>
       </c>
     </row>
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-08-24 19:30:00</t>
+          <t>2026-08-24 16:15:00</t>
         </is>
       </c>
     </row>
@@ -9390,27 +9390,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-08-24 19:30:00</t>
+          <t>2026-08-24 16:30:00</t>
         </is>
       </c>
     </row>
@@ -9553,27 +9553,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P57">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-08-24 20:00:00</t>
+          <t>2026-08-24 16:30:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G58">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-08-24 20:00:00</t>
+          <t>2026-08-24 19:30:00</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G59">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-08-24 20:30:00</t>
+          <t>2026-08-24 19:30:00</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-08-24 20:30:00</t>
+          <t>2026-08-24 20:00:00</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G61">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-08-24 21:00:00</t>
+          <t>2026-08-24 20:00:00</t>
         </is>
       </c>
     </row>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-08-24 21:00:00</t>
+          <t>2026-08-24 20:30:00</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-08-24 21:00:00</t>
+          <t>2026-08-24 20:30:00</t>
         </is>
       </c>
     </row>
@@ -10699,151 +10699,640 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Qizilqum</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Nasaf</t>
+        </is>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>0</v>
+      </c>
+      <c r="AB64">
+        <v>0</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64">
+        <v>0</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>0</v>
+      </c>
+      <c r="AG64">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
+        <v>0</v>
+      </c>
+      <c r="AK64">
+        <v>0</v>
+      </c>
+      <c r="AL64">
+        <v>0</v>
+      </c>
+      <c r="AM64">
+        <v>-1</v>
+      </c>
+      <c r="AN64">
+        <v>-1</v>
+      </c>
+      <c r="AO64">
+        <v>-1</v>
+      </c>
+      <c r="AP64">
+        <v>-1</v>
+      </c>
+      <c r="AQ64">
+        <v>0</v>
+      </c>
+      <c r="AR64">
+        <v>0</v>
+      </c>
+      <c r="AS64">
+        <v>0</v>
+      </c>
+      <c r="AT64">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>2026-08-24 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Lokomotiv</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Bunyodkor</t>
+        </is>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <v>0</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>0</v>
+      </c>
+      <c r="AK65">
+        <v>0</v>
+      </c>
+      <c r="AL65">
+        <v>0</v>
+      </c>
+      <c r="AM65">
+        <v>-1</v>
+      </c>
+      <c r="AN65">
+        <v>-1</v>
+      </c>
+      <c r="AO65">
+        <v>-1</v>
+      </c>
+      <c r="AP65">
+        <v>-1</v>
+      </c>
+      <c r="AQ65">
+        <v>0</v>
+      </c>
+      <c r="AR65">
+        <v>0</v>
+      </c>
+      <c r="AS65">
+        <v>0</v>
+      </c>
+      <c r="AT65">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>2026-08-24 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Mash'al</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Navbahor</t>
+        </is>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>0</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66">
+        <v>0</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>0</v>
+      </c>
+      <c r="AK66">
+        <v>0</v>
+      </c>
+      <c r="AL66">
+        <v>0</v>
+      </c>
+      <c r="AM66">
+        <v>-1</v>
+      </c>
+      <c r="AN66">
+        <v>-1</v>
+      </c>
+      <c r="AO66">
+        <v>-1</v>
+      </c>
+      <c r="AP66">
+        <v>-1</v>
+      </c>
+      <c r="AQ66">
+        <v>0</v>
+      </c>
+      <c r="AR66">
+        <v>0</v>
+      </c>
+      <c r="AS66">
+        <v>0</v>
+      </c>
+      <c r="AT66">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>2026-08-24 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Libertad</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Macará</t>
         </is>
       </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64" t="inlineStr">
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>0</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
-        <v>0</v>
-      </c>
-      <c r="T64">
-        <v>0</v>
-      </c>
-      <c r="U64">
-        <v>0</v>
-      </c>
-      <c r="V64">
-        <v>0</v>
-      </c>
-      <c r="W64">
-        <v>0</v>
-      </c>
-      <c r="X64">
-        <v>0</v>
-      </c>
-      <c r="Y64">
-        <v>0</v>
-      </c>
-      <c r="Z64">
-        <v>0</v>
-      </c>
-      <c r="AA64">
-        <v>0</v>
-      </c>
-      <c r="AB64">
-        <v>0</v>
-      </c>
-      <c r="AC64">
-        <v>0</v>
-      </c>
-      <c r="AD64">
-        <v>0</v>
-      </c>
-      <c r="AE64">
-        <v>0</v>
-      </c>
-      <c r="AF64">
-        <v>0</v>
-      </c>
-      <c r="AG64">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>0</v>
-      </c>
-      <c r="AK64">
-        <v>0</v>
-      </c>
-      <c r="AL64">
-        <v>0</v>
-      </c>
-      <c r="AM64">
-        <v>-1</v>
-      </c>
-      <c r="AN64">
-        <v>-1</v>
-      </c>
-      <c r="AO64">
-        <v>-1</v>
-      </c>
-      <c r="AP64">
-        <v>-1</v>
-      </c>
-      <c r="AQ64">
-        <v>0</v>
-      </c>
-      <c r="AR64">
-        <v>0</v>
-      </c>
-      <c r="AS64">
-        <v>0</v>
-      </c>
-      <c r="AT64">
-        <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>0</v>
+      </c>
+      <c r="AK67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>-1</v>
+      </c>
+      <c r="AN67">
+        <v>-1</v>
+      </c>
+      <c r="AO67">
+        <v>-1</v>
+      </c>
+      <c r="AP67">
+        <v>-1</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>0</v>
+      </c>
+      <c r="AS67">
+        <v>0</v>
+      </c>
+      <c r="AT67">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
         <is>
           <t>2026-08-24 21:00:00</t>
         </is>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU67"/>
+  <dimension ref="A1:AU68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-08-24 11:30:00</t>
+          <t>2026-08-24 11:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-08-24 12:00:00</t>
+          <t>2026-08-24 11:30:00</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G5">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G6">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-08-24 12:30:00</t>
+          <t>2026-08-24 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-08-24 12:30:00</t>
+          <t>2026-08-24 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-24 12:45:00</t>
+          <t>2026-08-24 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-08-24 13:00:00</t>
+          <t>2026-08-24 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G12">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-08-24 13:30:00</t>
+          <t>2026-08-24 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,27 +2707,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G15">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-08-24 13:30:00</t>
+          <t>2026-08-24 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-08-24 13:30:00</t>
+          <t>2026-08-24 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-08-24 13:30:00</t>
+          <t>2026-08-24 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,22 +3364,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,17 +3402,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N19">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-08-24 13:40:00</t>
+          <t>2026-08-24 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>4.51</v>
+        <v>2.13</v>
       </c>
       <c r="O21">
-        <v>3.98</v>
+        <v>3.52</v>
       </c>
       <c r="P21">
-        <v>1.6</v>
+        <v>3.83</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-08-24 14:00:00</t>
+          <t>2026-08-24 13:30:00</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-08-24 14:00:00</t>
+          <t>2026-08-24 13:40:00</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.72</v>
+        <v>2.31</v>
       </c>
       <c r="O24">
-        <v>3.44</v>
+        <v>3.02</v>
       </c>
       <c r="P24">
-        <v>2.61</v>
+        <v>3.24</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4342,22 +4342,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.08</v>
+        <v>2.72</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P26">
-        <v>3.25</v>
+        <v>2.61</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.58</v>
+        <v>2.02</v>
       </c>
       <c r="O27">
-        <v>3.66</v>
+        <v>3.54</v>
       </c>
       <c r="P27">
-        <v>2.43</v>
+        <v>3.39</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4831,22 +4831,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-08-24 14:05:00</t>
+          <t>2026-08-24 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-08-24 14:30:00</t>
+          <t>2026-08-24 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5641,27 +5641,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.07</v>
+        <v>1.56</v>
       </c>
       <c r="O33">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="P33">
-        <v>3.6</v>
+        <v>5.03</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-08-24 14:30:00</t>
+          <t>2026-08-24 14:05:00</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G34">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:00</t>
+          <t>2026-08-24 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G38">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-08-24 15:15:00</t>
+          <t>2026-08-24 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.13</v>
+        <v>4.72</v>
       </c>
       <c r="O40">
-        <v>3</v>
+        <v>3.82</v>
       </c>
       <c r="P40">
-        <v>3.46</v>
+        <v>1.67</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,10 +6868,10 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-08-24 15:30:00</t>
+          <t>2026-08-24 15:15:00</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.69</v>
+        <v>2.65</v>
       </c>
       <c r="O44">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="P44">
-        <v>4.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-08-24 15:45:00</t>
+          <t>2026-08-24 15:30:00</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="O45">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="P45">
-        <v>6.85</v>
+        <v>4.8</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB45">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.17</v>
+        <v>1.55</v>
       </c>
       <c r="O46">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="P46">
-        <v>3.25</v>
+        <v>6.85</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7846,10 +7846,10 @@
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC46">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:00:00</t>
+          <t>2026-08-24 15:45:00</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.34</v>
+        <v>2.17</v>
       </c>
       <c r="O47">
-        <v>3.81</v>
+        <v>3.1</v>
       </c>
       <c r="P47">
-        <v>2.21</v>
+        <v>3.25</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.39</v>
+        <v>2.85</v>
       </c>
       <c r="O50">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="P50">
-        <v>6.76</v>
+        <v>2.46</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-08-24 16:15:00</t>
+          <t>2026-08-24 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9232,22 +9232,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="O55">
-        <v>3.77</v>
+        <v>4.1</v>
       </c>
       <c r="P55">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.79</v>
+        <v>1.77</v>
       </c>
       <c r="O56">
-        <v>3.27</v>
+        <v>3.77</v>
       </c>
       <c r="P56">
-        <v>2.65</v>
+        <v>5</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-08-24 16:30:00</t>
+          <t>2026-08-24 16:15:00</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G58">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-08-24 19:30:00</t>
+          <t>2026-08-24 16:30:00</t>
         </is>
       </c>
     </row>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G59">
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-08-24 20:00:00</t>
+          <t>2026-08-24 19:30:00</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-08-24 20:30:00</t>
+          <t>2026-08-24 20:00:00</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G63">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-08-24 21:00:00</t>
+          <t>2026-08-24 20:30:00</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G66">
@@ -11188,151 +11188,314 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Mash'al</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Navbahor</t>
+        </is>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>0</v>
+      </c>
+      <c r="AK67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>-1</v>
+      </c>
+      <c r="AN67">
+        <v>-1</v>
+      </c>
+      <c r="AO67">
+        <v>-1</v>
+      </c>
+      <c r="AP67">
+        <v>-1</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>0</v>
+      </c>
+      <c r="AS67">
+        <v>0</v>
+      </c>
+      <c r="AT67">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>2026-08-24 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Libertad</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Macará</t>
         </is>
       </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67" t="inlineStr">
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>0</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
-      <c r="W67">
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <v>0</v>
-      </c>
-      <c r="Y67">
-        <v>0</v>
-      </c>
-      <c r="Z67">
-        <v>0</v>
-      </c>
-      <c r="AA67">
-        <v>0</v>
-      </c>
-      <c r="AB67">
-        <v>0</v>
-      </c>
-      <c r="AC67">
-        <v>0</v>
-      </c>
-      <c r="AD67">
-        <v>0</v>
-      </c>
-      <c r="AE67">
-        <v>0</v>
-      </c>
-      <c r="AF67">
-        <v>0</v>
-      </c>
-      <c r="AG67">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>0</v>
-      </c>
-      <c r="AK67">
-        <v>0</v>
-      </c>
-      <c r="AL67">
-        <v>0</v>
-      </c>
-      <c r="AM67">
-        <v>-1</v>
-      </c>
-      <c r="AN67">
-        <v>-1</v>
-      </c>
-      <c r="AO67">
-        <v>-1</v>
-      </c>
-      <c r="AP67">
-        <v>-1</v>
-      </c>
-      <c r="AQ67">
-        <v>0</v>
-      </c>
-      <c r="AR67">
-        <v>0</v>
-      </c>
-      <c r="AS67">
-        <v>0</v>
-      </c>
-      <c r="AT67">
-        <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>0</v>
+      </c>
+      <c r="AB68">
+        <v>0</v>
+      </c>
+      <c r="AC68">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>0</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>0</v>
+      </c>
+      <c r="AG68">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>0</v>
+      </c>
+      <c r="AK68">
+        <v>0</v>
+      </c>
+      <c r="AL68">
+        <v>0</v>
+      </c>
+      <c r="AM68">
+        <v>-1</v>
+      </c>
+      <c r="AN68">
+        <v>-1</v>
+      </c>
+      <c r="AO68">
+        <v>-1</v>
+      </c>
+      <c r="AP68">
+        <v>-1</v>
+      </c>
+      <c r="AQ68">
+        <v>0</v>
+      </c>
+      <c r="AR68">
+        <v>0</v>
+      </c>
+      <c r="AS68">
+        <v>0</v>
+      </c>
+      <c r="AT68">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
         <is>
           <t>2026-08-24 21:00:00</t>
         </is>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU68"/>
+  <dimension ref="A1:AU65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G65">
@@ -11007,495 +11007,6 @@
         <v>0</v>
       </c>
       <c r="AU65" t="inlineStr">
-        <is>
-          <t>2026-08-24 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Lokomotiv</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Bunyodkor</t>
-        </is>
-      </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>0</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>0</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>0</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
-        <v>0</v>
-      </c>
-      <c r="T66">
-        <v>0</v>
-      </c>
-      <c r="U66">
-        <v>0</v>
-      </c>
-      <c r="V66">
-        <v>0</v>
-      </c>
-      <c r="W66">
-        <v>0</v>
-      </c>
-      <c r="X66">
-        <v>0</v>
-      </c>
-      <c r="Y66">
-        <v>0</v>
-      </c>
-      <c r="Z66">
-        <v>0</v>
-      </c>
-      <c r="AA66">
-        <v>0</v>
-      </c>
-      <c r="AB66">
-        <v>0</v>
-      </c>
-      <c r="AC66">
-        <v>0</v>
-      </c>
-      <c r="AD66">
-        <v>0</v>
-      </c>
-      <c r="AE66">
-        <v>0</v>
-      </c>
-      <c r="AF66">
-        <v>0</v>
-      </c>
-      <c r="AG66">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>0</v>
-      </c>
-      <c r="AK66">
-        <v>0</v>
-      </c>
-      <c r="AL66">
-        <v>0</v>
-      </c>
-      <c r="AM66">
-        <v>-1</v>
-      </c>
-      <c r="AN66">
-        <v>-1</v>
-      </c>
-      <c r="AO66">
-        <v>-1</v>
-      </c>
-      <c r="AP66">
-        <v>-1</v>
-      </c>
-      <c r="AQ66">
-        <v>0</v>
-      </c>
-      <c r="AR66">
-        <v>0</v>
-      </c>
-      <c r="AS66">
-        <v>0</v>
-      </c>
-      <c r="AT66">
-        <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>2026-08-24 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Mash'al</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Navbahor</t>
-        </is>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>0</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
-      <c r="W67">
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <v>0</v>
-      </c>
-      <c r="Y67">
-        <v>0</v>
-      </c>
-      <c r="Z67">
-        <v>0</v>
-      </c>
-      <c r="AA67">
-        <v>0</v>
-      </c>
-      <c r="AB67">
-        <v>0</v>
-      </c>
-      <c r="AC67">
-        <v>0</v>
-      </c>
-      <c r="AD67">
-        <v>0</v>
-      </c>
-      <c r="AE67">
-        <v>0</v>
-      </c>
-      <c r="AF67">
-        <v>0</v>
-      </c>
-      <c r="AG67">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>0</v>
-      </c>
-      <c r="AK67">
-        <v>0</v>
-      </c>
-      <c r="AL67">
-        <v>0</v>
-      </c>
-      <c r="AM67">
-        <v>-1</v>
-      </c>
-      <c r="AN67">
-        <v>-1</v>
-      </c>
-      <c r="AO67">
-        <v>-1</v>
-      </c>
-      <c r="AP67">
-        <v>-1</v>
-      </c>
-      <c r="AQ67">
-        <v>0</v>
-      </c>
-      <c r="AR67">
-        <v>0</v>
-      </c>
-      <c r="AS67">
-        <v>0</v>
-      </c>
-      <c r="AT67">
-        <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>2026-08-24 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Libertad</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Macará</t>
-        </is>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <v>0</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
-        <v>0</v>
-      </c>
-      <c r="T68">
-        <v>0</v>
-      </c>
-      <c r="U68">
-        <v>0</v>
-      </c>
-      <c r="V68">
-        <v>0</v>
-      </c>
-      <c r="W68">
-        <v>0</v>
-      </c>
-      <c r="X68">
-        <v>0</v>
-      </c>
-      <c r="Y68">
-        <v>0</v>
-      </c>
-      <c r="Z68">
-        <v>0</v>
-      </c>
-      <c r="AA68">
-        <v>0</v>
-      </c>
-      <c r="AB68">
-        <v>0</v>
-      </c>
-      <c r="AC68">
-        <v>0</v>
-      </c>
-      <c r="AD68">
-        <v>0</v>
-      </c>
-      <c r="AE68">
-        <v>0</v>
-      </c>
-      <c r="AF68">
-        <v>0</v>
-      </c>
-      <c r="AG68">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>0</v>
-      </c>
-      <c r="AK68">
-        <v>0</v>
-      </c>
-      <c r="AL68">
-        <v>0</v>
-      </c>
-      <c r="AM68">
-        <v>-1</v>
-      </c>
-      <c r="AN68">
-        <v>-1</v>
-      </c>
-      <c r="AO68">
-        <v>-1</v>
-      </c>
-      <c r="AP68">
-        <v>-1</v>
-      </c>
-      <c r="AQ68">
-        <v>0</v>
-      </c>
-      <c r="AR68">
-        <v>0</v>
-      </c>
-      <c r="AS68">
-        <v>0</v>
-      </c>
-      <c r="AT68">
-        <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
         <is>
           <t>2026-08-24 21:00:00</t>
         </is>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU65"/>
+  <dimension ref="A1:AU67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="O9">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P9">
-        <v>4.3</v>
+        <v>5.45</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-08-24 12:45:00</t>
+          <t>2026-08-24 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-08-24 13:00:00</t>
+          <t>2026-08-24 12:45:00</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G13">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="G15">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-08-24 13:30:00</t>
+          <t>2026-08-24 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3364,22 +3364,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N19">
@@ -3527,22 +3527,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G20">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-08-24 13:40:00</t>
+          <t>2026-08-24 13:30:00</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-08-24 14:00:00</t>
+          <t>2026-08-24 13:40:00</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.31</v>
+        <v>4.51</v>
       </c>
       <c r="O24">
-        <v>3.02</v>
+        <v>3.98</v>
       </c>
       <c r="P24">
-        <v>3.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4668,22 +4668,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4831,22 +4831,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.08</v>
+        <v>2.72</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P28">
-        <v>3.25</v>
+        <v>2.61</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.58</v>
+        <v>2.02</v>
       </c>
       <c r="O29">
-        <v>3.66</v>
+        <v>3.54</v>
       </c>
       <c r="P29">
-        <v>2.43</v>
+        <v>3.39</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5320,22 +5320,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5641,27 +5641,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-08-24 14:05:00</t>
+          <t>2026-08-24 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>6.54</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-08-24 14:30:00</t>
+          <t>2026-08-24 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,27 +5967,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.07</v>
+        <v>1.56</v>
       </c>
       <c r="O35">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="P35">
-        <v>3.6</v>
+        <v>5.03</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-08-24 14:30:00</t>
+          <t>2026-08-24 14:05:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G36">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:00</t>
+          <t>2026-08-24 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:00</t>
+          <t>2026-08-24 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G39">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,10 +6868,10 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-08-24 15:15:00</t>
+          <t>2026-08-24 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-08-24 15:30:00</t>
+          <t>2026-08-24 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-08-24 15:30:00</t>
+          <t>2026-08-24 15:15:00</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB45">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-08-24 15:45:00</t>
+          <t>2026-08-24 15:30:00</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.55</v>
+        <v>2.65</v>
       </c>
       <c r="O46">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="P46">
-        <v>6.85</v>
+        <v>2.65</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7846,10 +7846,10 @@
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC46">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-08-24 15:45:00</t>
+          <t>2026-08-24 15:30:00</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.17</v>
+        <v>1.69</v>
       </c>
       <c r="O47">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="P47">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:00:00</t>
+          <t>2026-08-24 15:45:00</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.34</v>
+        <v>1.55</v>
       </c>
       <c r="O48">
-        <v>3.81</v>
+        <v>4.5</v>
       </c>
       <c r="P48">
-        <v>2.21</v>
+        <v>6.85</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:00:00</t>
+          <t>2026-08-24 15:45:00</t>
         </is>
       </c>
     </row>
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.85</v>
+        <v>3.34</v>
       </c>
       <c r="O50">
-        <v>2.9</v>
+        <v>3.81</v>
       </c>
       <c r="P50">
-        <v>2.46</v>
+        <v>2.21</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8580,22 +8580,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Folgore Caratese</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.27</v>
+        <v>1.39</v>
       </c>
       <c r="O53">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="P53">
-        <v>3.26</v>
+        <v>6.76</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G54">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-08-24 16:15:00</t>
+          <t>2026-08-24 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Folgore Caratese</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="O55">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="P55">
-        <v>2.4</v>
+        <v>3.26</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-08-24 16:15:00</t>
+          <t>2026-08-24 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9553,27 +9553,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="O57">
-        <v>3.27</v>
+        <v>4.1</v>
       </c>
       <c r="P57">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-08-24 16:30:00</t>
+          <t>2026-08-24 16:15:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-08-24 16:30:00</t>
+          <t>2026-08-24 16:15:00</t>
         </is>
       </c>
     </row>
@@ -9879,27 +9879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-08-24 19:30:00</t>
+          <t>2026-08-24 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10042,27 +10042,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-08-24 19:30:00</t>
+          <t>2026-08-24 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P61">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-08-24 20:00:00</t>
+          <t>2026-08-24 19:30:00</t>
         </is>
       </c>
     </row>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-08-24 20:00:00</t>
+          <t>2026-08-24 19:30:00</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-08-24 20:30:00</t>
+          <t>2026-08-24 20:00:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-08-24 20:30:00</t>
+          <t>2026-08-24 20:00:00</t>
         </is>
       </c>
     </row>
@@ -10857,156 +10857,482 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Santiago Wanderers</t>
+        </is>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <v>0</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>0</v>
+      </c>
+      <c r="AK65">
+        <v>0</v>
+      </c>
+      <c r="AL65">
+        <v>0</v>
+      </c>
+      <c r="AM65">
+        <v>-1</v>
+      </c>
+      <c r="AN65">
+        <v>-1</v>
+      </c>
+      <c r="AO65">
+        <v>-1</v>
+      </c>
+      <c r="AP65">
+        <v>-1</v>
+      </c>
+      <c r="AQ65">
+        <v>0</v>
+      </c>
+      <c r="AR65">
+        <v>0</v>
+      </c>
+      <c r="AS65">
+        <v>0</v>
+      </c>
+      <c r="AT65">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>0</v>
+      </c>
+      <c r="AC66">
+        <v>0</v>
+      </c>
+      <c r="AD66">
+        <v>0</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>0</v>
+      </c>
+      <c r="AK66">
+        <v>0</v>
+      </c>
+      <c r="AL66">
+        <v>0</v>
+      </c>
+      <c r="AM66">
+        <v>-1</v>
+      </c>
+      <c r="AN66">
+        <v>-1</v>
+      </c>
+      <c r="AO66">
+        <v>-1</v>
+      </c>
+      <c r="AP66">
+        <v>-1</v>
+      </c>
+      <c r="AQ66">
+        <v>0</v>
+      </c>
+      <c r="AR66">
+        <v>0</v>
+      </c>
+      <c r="AS66">
+        <v>0</v>
+      </c>
+      <c r="AT66">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Libertad</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Macará</t>
         </is>
       </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65" t="inlineStr">
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
-      </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
-      </c>
-      <c r="Y65">
-        <v>0</v>
-      </c>
-      <c r="Z65">
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <v>0</v>
-      </c>
-      <c r="AB65">
-        <v>0</v>
-      </c>
-      <c r="AC65">
-        <v>0</v>
-      </c>
-      <c r="AD65">
-        <v>0</v>
-      </c>
-      <c r="AE65">
-        <v>0</v>
-      </c>
-      <c r="AF65">
-        <v>0</v>
-      </c>
-      <c r="AG65">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>0</v>
-      </c>
-      <c r="AK65">
-        <v>0</v>
-      </c>
-      <c r="AL65">
-        <v>0</v>
-      </c>
-      <c r="AM65">
-        <v>-1</v>
-      </c>
-      <c r="AN65">
-        <v>-1</v>
-      </c>
-      <c r="AO65">
-        <v>-1</v>
-      </c>
-      <c r="AP65">
-        <v>-1</v>
-      </c>
-      <c r="AQ65">
-        <v>0</v>
-      </c>
-      <c r="AR65">
-        <v>0</v>
-      </c>
-      <c r="AS65">
-        <v>0</v>
-      </c>
-      <c r="AT65">
-        <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>0</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>0</v>
+      </c>
+      <c r="AK67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>-1</v>
+      </c>
+      <c r="AN67">
+        <v>-1</v>
+      </c>
+      <c r="AO67">
+        <v>-1</v>
+      </c>
+      <c r="AP67">
+        <v>-1</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>0</v>
+      </c>
+      <c r="AS67">
+        <v>0</v>
+      </c>
+      <c r="AT67">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
         <is>
           <t>2026-08-24 21:00:00</t>
         </is>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -1948,55 +1948,55 @@
         <v>4.3</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3252,34 +3252,34 @@
         <v>2.14</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA18">
         <v>1.97</v>
@@ -3288,19 +3288,19 @@
         <v>1.72</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3904,34 +3904,34 @@
         <v>3.83</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AA22">
         <v>2.1</v>
@@ -3940,19 +3940,19 @@
         <v>1.65</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>6.54</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="O29">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P30">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>2.43</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>5.03</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL35">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -4230,55 +4230,55 @@
         <v>1.6</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,55 +4393,55 @@
         <v>3.24</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,55 +6349,55 @@
         <v>3.6</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -6687,10 +6687,10 @@
         <v>0</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W39">
         <v>0</v>
@@ -6699,31 +6699,31 @@
         <v>0</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>3.46</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>2.65</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,34 +7979,34 @@
         <v>4.8</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AA47">
         <v>2</v>
@@ -8015,19 +8015,19 @@
         <v>1.8</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8142,34 +8142,34 @@
         <v>6.85</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA48">
         <v>1.83</v>
@@ -8178,19 +8178,19 @@
         <v>1.89</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,10 +8305,10 @@
         <v>3.25</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -8317,43 +8317,43 @@
         <v>0</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X49">
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE49">
         <v>0</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8468,34 +8468,34 @@
         <v>2.21</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA50">
         <v>1.63</v>
@@ -8504,19 +8504,19 @@
         <v>2.15</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.85</v>
+        <v>1.39</v>
       </c>
       <c r="O52">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="P52">
-        <v>2.46</v>
+        <v>6.76</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9446,55 +9446,55 @@
         <v>0</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9609,55 +9609,55 @@
         <v>2.4</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9772,55 +9772,55 @@
         <v>5</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9935,55 +9935,55 @@
         <v>2.65</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL67">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P29">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="Q29">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R29">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S29">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>3.6</v>
+        <v>2.99</v>
       </c>
       <c r="U29">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V29">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AA29">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB29">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AC29">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD29">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE29">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF29">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG29">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AK29">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="O30">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="Q30">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R30">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T30">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="U30">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V30">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y30">
         <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA30">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB30">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC30">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD30">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE30">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
+        <v>1.55</v>
+      </c>
+      <c r="AG30">
+        <v>2.32</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.34</v>
+      </c>
+      <c r="AK30">
         <v>1.62</v>
-      </c>
-      <c r="AG30">
-        <v>2.14</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.26</v>
-      </c>
-      <c r="AK30">
-        <v>1.75</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>5.03</v>
+        <v>1.65</v>
       </c>
       <c r="O40">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="P40">
-        <v>1.52</v>
+        <v>4.37</v>
       </c>
       <c r="Q40">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="R40">
-        <v>2.69</v>
+        <v>2.46</v>
       </c>
       <c r="S40">
         <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="U40">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="V40">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W40">
         <v>1.18</v>
@@ -6865,28 +6865,28 @@
         <v>1.11</v>
       </c>
       <c r="Z40">
-        <v>5.45</v>
+        <v>5.75</v>
       </c>
       <c r="AA40">
         <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="AC40">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AD40">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AE40">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF40">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG40">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>1.17</v>
+        <v>2.08</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.65</v>
+        <v>5.03</v>
       </c>
       <c r="O41">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="P41">
-        <v>4.37</v>
+        <v>1.52</v>
       </c>
       <c r="Q41">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="R41">
-        <v>2.46</v>
+        <v>2.69</v>
       </c>
       <c r="S41">
         <v>1.22</v>
       </c>
       <c r="T41">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="U41">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="V41">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W41">
         <v>1.18</v>
@@ -7028,28 +7028,28 @@
         <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>5.75</v>
+        <v>5.45</v>
       </c>
       <c r="AA41">
         <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="AC41">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AD41">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE41">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF41">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG41">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>2.08</v>
+        <v>1.17</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8631,55 +8631,55 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>3.54</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL66">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q33">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G14">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q56">
         <v>2.77</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,61 +10415,61 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="O62">
         <v>3.4</v>
       </c>
       <c r="P62">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q62">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="R62">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S62">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T62">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U62">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V62">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W62">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z62">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA62">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AB62">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC62">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="AD62">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE62">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF62">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AG62">
         <v>1.85</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK62">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="P10">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="Q10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
         <v>2.39</v>
@@ -1960,34 +1960,34 @@
         <v>3.24</v>
       </c>
       <c r="U10">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
         <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z10">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA10">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC10">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AD10">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
@@ -1996,7 +1996,7 @@
         <v>1.75</v>
       </c>
       <c r="AG10">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
         <v>2.15</v>
@@ -6835,25 +6835,25 @@
         <v>4.2</v>
       </c>
       <c r="P40">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
       <c r="Q40">
         <v>2.1</v>
       </c>
       <c r="R40">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="S40">
         <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U40">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="V40">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W40">
         <v>1.18</v>
@@ -6868,13 +6868,13 @@
         <v>5.75</v>
       </c>
       <c r="AA40">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB40">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="AC40">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD40">
         <v>1.75</v>
@@ -6883,7 +6883,7 @@
         <v>1.28</v>
       </c>
       <c r="AF40">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG40">
         <v>2.5</v>
@@ -6902,7 +6902,7 @@
         <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>5.03</v>
+        <v>4.6</v>
       </c>
       <c r="O41">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P41">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q41">
         <v>4.6</v>
       </c>
       <c r="R41">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="S41">
         <v>1.22</v>
@@ -7013,13 +7013,13 @@
         <v>3.68</v>
       </c>
       <c r="U41">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="V41">
         <v>1.65</v>
       </c>
       <c r="W41">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X41">
         <v>1.02</v>
@@ -7028,7 +7028,7 @@
         <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="AA41">
         <v>1.4</v>
@@ -7037,19 +7037,19 @@
         <v>2.63</v>
       </c>
       <c r="AC41">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AD41">
         <v>1.67</v>
       </c>
       <c r="AE41">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF41">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG41">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7318,34 +7318,34 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="O43">
         <v>3</v>
       </c>
       <c r="P43">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="Q43">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S43">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T43">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U43">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V43">
         <v>1.28</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7372,10 +7372,10 @@
         <v>1.02</v>
       </c>
       <c r="AF43">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG43">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="O46">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="P46">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="Q46">
         <v>3.1</v>
@@ -7825,7 +7825,7 @@
         <v>1.45</v>
       </c>
       <c r="T46">
-        <v>2.24</v>
+        <v>2.55</v>
       </c>
       <c r="U46">
         <v>3.36</v>
@@ -7837,22 +7837,22 @@
         <v>1.05</v>
       </c>
       <c r="X46">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y46">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z46">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AA46">
         <v>2.5</v>
       </c>
       <c r="AB46">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AC46">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AD46">
         <v>1.16</v>
@@ -7861,10 +7861,10 @@
         <v>1.02</v>
       </c>
       <c r="AF46">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AG46">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK46">
         <v>1.5</v>
@@ -8350,10 +8350,10 @@
         <v>0</v>
       </c>
       <c r="AF49">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG49">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="O52">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="P52">
-        <v>6.76</v>
+        <v>7.7</v>
       </c>
       <c r="Q52">
         <v>1.83</v>
@@ -8806,7 +8806,7 @@
         <v>3</v>
       </c>
       <c r="U52">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V52">
         <v>1.39</v>
@@ -8858,7 +8858,7 @@
         <v>1.02</v>
       </c>
       <c r="AK52">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O54">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P54">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9277,10 +9277,10 @@
         <v>2.27</v>
       </c>
       <c r="O55">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P55">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="O61">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="P61">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q61">
-        <v>3.48</v>
+        <v>2.38</v>
       </c>
       <c r="R61">
+        <v>2.05</v>
+      </c>
+      <c r="S61">
+        <v>1.42</v>
+      </c>
+      <c r="T61">
+        <v>2.62</v>
+      </c>
+      <c r="U61">
+        <v>2.95</v>
+      </c>
+      <c r="V61">
+        <v>1.33</v>
+      </c>
+      <c r="W61">
+        <v>1.06</v>
+      </c>
+      <c r="X61">
+        <v>1.04</v>
+      </c>
+      <c r="Y61">
+        <v>1.3</v>
+      </c>
+      <c r="Z61">
+        <v>3</v>
+      </c>
+      <c r="AA61">
+        <v>2.05</v>
+      </c>
+      <c r="AB61">
+        <v>1.66</v>
+      </c>
+      <c r="AC61">
+        <v>3.9</v>
+      </c>
+      <c r="AD61">
+        <v>1.22</v>
+      </c>
+      <c r="AE61">
+        <v>1.09</v>
+      </c>
+      <c r="AF61">
         <v>1.92</v>
       </c>
-      <c r="S61">
-        <v>1.45</v>
-      </c>
-      <c r="T61">
-        <v>2.39</v>
-      </c>
-      <c r="U61">
-        <v>3.35</v>
-      </c>
-      <c r="V61">
-        <v>1.27</v>
-      </c>
-      <c r="W61">
-        <v>1.03</v>
-      </c>
-      <c r="X61">
-        <v>1.05</v>
-      </c>
-      <c r="Y61">
-        <v>1.42</v>
-      </c>
-      <c r="Z61">
-        <v>2.49</v>
-      </c>
-      <c r="AA61">
-        <v>2.6</v>
-      </c>
-      <c r="AB61">
-        <v>1.47</v>
-      </c>
-      <c r="AC61">
-        <v>4.2</v>
-      </c>
-      <c r="AD61">
-        <v>1.14</v>
-      </c>
-      <c r="AE61">
-        <v>1.01</v>
-      </c>
-      <c r="AF61">
-        <v>1.99</v>
-      </c>
       <c r="AG61">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AK61">
-        <v>1.42</v>
+        <v>2.02</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
+        <v>2.7</v>
+      </c>
+      <c r="O62">
+        <v>2.87</v>
+      </c>
+      <c r="P62">
+        <v>2.6</v>
+      </c>
+      <c r="Q62">
+        <v>3.48</v>
+      </c>
+      <c r="R62">
+        <v>1.92</v>
+      </c>
+      <c r="S62">
+        <v>1.45</v>
+      </c>
+      <c r="T62">
+        <v>2.39</v>
+      </c>
+      <c r="U62">
+        <v>3.35</v>
+      </c>
+      <c r="V62">
+        <v>1.27</v>
+      </c>
+      <c r="W62">
+        <v>1.03</v>
+      </c>
+      <c r="X62">
+        <v>1.05</v>
+      </c>
+      <c r="Y62">
+        <v>1.42</v>
+      </c>
+      <c r="Z62">
+        <v>2.49</v>
+      </c>
+      <c r="AA62">
+        <v>2.6</v>
+      </c>
+      <c r="AB62">
+        <v>1.47</v>
+      </c>
+      <c r="AC62">
+        <v>4.2</v>
+      </c>
+      <c r="AD62">
+        <v>1.14</v>
+      </c>
+      <c r="AE62">
+        <v>1.01</v>
+      </c>
+      <c r="AF62">
+        <v>1.99</v>
+      </c>
+      <c r="AG62">
         <v>1.73</v>
       </c>
-      <c r="O62">
-        <v>3.4</v>
-      </c>
-      <c r="P62">
-        <v>4.2</v>
-      </c>
-      <c r="Q62">
-        <v>2.38</v>
-      </c>
-      <c r="R62">
-        <v>2.05</v>
-      </c>
-      <c r="S62">
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>1.34</v>
+      </c>
+      <c r="AK62">
         <v>1.42</v>
-      </c>
-      <c r="T62">
-        <v>2.62</v>
-      </c>
-      <c r="U62">
-        <v>2.95</v>
-      </c>
-      <c r="V62">
-        <v>1.33</v>
-      </c>
-      <c r="W62">
-        <v>1.06</v>
-      </c>
-      <c r="X62">
-        <v>1.04</v>
-      </c>
-      <c r="Y62">
-        <v>1.3</v>
-      </c>
-      <c r="Z62">
-        <v>3</v>
-      </c>
-      <c r="AA62">
-        <v>2.05</v>
-      </c>
-      <c r="AB62">
-        <v>1.66</v>
-      </c>
-      <c r="AC62">
-        <v>3.9</v>
-      </c>
-      <c r="AD62">
-        <v>1.22</v>
-      </c>
-      <c r="AE62">
-        <v>1.09</v>
-      </c>
-      <c r="AF62">
-        <v>1.92</v>
-      </c>
-      <c r="AG62">
-        <v>1.85</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.16</v>
-      </c>
-      <c r="AK62">
-        <v>2.02</v>
       </c>
       <c r="AL62">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1785,22 +1785,22 @@
         <v>5.45</v>
       </c>
       <c r="Q9">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R9">
         <v>2.04</v>
       </c>
       <c r="S9">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T9">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="U9">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
         <v>1.02</v>
@@ -1809,31 +1809,31 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z9">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AA9">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AB9">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AC9">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AD9">
         <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AG9">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK9">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2105,10 +2105,10 @@
         <v>1.5</v>
       </c>
       <c r="O11">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P11">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -3243,28 +3243,28 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="O18">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="P18">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="Q18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="R18">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S18">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T18">
+        <v>2.59</v>
+      </c>
+      <c r="U18">
         <v>2.88</v>
-      </c>
-      <c r="U18">
-        <v>3</v>
       </c>
       <c r="V18">
         <v>1.36</v>
@@ -3273,28 +3273,28 @@
         <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
         <v>1.3</v>
       </c>
       <c r="Z18">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA18">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB18">
         <v>1.72</v>
       </c>
       <c r="AC18">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD18">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE18">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF18">
         <v>1.8</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="O19">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="P19">
+        <v>2.35</v>
+      </c>
+      <c r="Q19">
+        <v>3.75</v>
+      </c>
+      <c r="R19">
+        <v>1.92</v>
+      </c>
+      <c r="S19">
+        <v>1.49</v>
+      </c>
+      <c r="T19">
         <v>2.41</v>
       </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
@@ -3913,7 +3913,7 @@
         <v>1.5</v>
       </c>
       <c r="T22">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="U22">
         <v>3.22</v>
@@ -3922,10 +3922,10 @@
         <v>1.34</v>
       </c>
       <c r="W22">
+        <v>1.03</v>
+      </c>
+      <c r="X22">
         <v>1.04</v>
-      </c>
-      <c r="X22">
-        <v>1.08</v>
       </c>
       <c r="Y22">
         <v>1.36</v>
@@ -3934,22 +3934,22 @@
         <v>2.86</v>
       </c>
       <c r="AA22">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB22">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC22">
         <v>4</v>
       </c>
       <c r="AD22">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG22">
         <v>1.87</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
         <v>1.62</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>4.51</v>
+        <v>3.75</v>
       </c>
       <c r="O24">
-        <v>3.98</v>
+        <v>3.55</v>
       </c>
       <c r="P24">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="Q24">
         <v>4</v>
       </c>
       <c r="R24">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="S24">
         <v>1.25</v>
@@ -4257,10 +4257,10 @@
         <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="AA24">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB24">
         <v>2.3</v>
@@ -4275,10 +4275,10 @@
         <v>1.2</v>
       </c>
       <c r="AF24">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
         <v>3.24</v>
       </c>
       <c r="Q25">
-        <v>2.49</v>
+        <v>2.79</v>
       </c>
       <c r="R25">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="S25">
         <v>1.48</v>
@@ -4426,16 +4426,16 @@
         <v>2.29</v>
       </c>
       <c r="AB25">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC25">
         <v>4.05</v>
       </c>
       <c r="AD25">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE25">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
         <v>1.95</v>
@@ -4457,7 +4457,7 @@
         <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O26">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="P26">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="Q26">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R26">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U26">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="V26">
         <v>1.41</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>3.62</v>
+        <v>3.69</v>
       </c>
       <c r="AA26">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AB26">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AC26">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD26">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF26">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG26">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AK26">
         <v>3.62</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="O28">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.61</v>
+        <v>2.28</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="O29">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>3.39</v>
+        <v>3.55</v>
       </c>
       <c r="Q29">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R29">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S29">
         <v>1.33</v>
       </c>
       <c r="T29">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U29">
         <v>2.45</v>
@@ -5069,31 +5069,31 @@
         <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z29">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA29">
         <v>1.73</v>
       </c>
       <c r="AB29">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC29">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE29">
         <v>1.11</v>
       </c>
       <c r="AF29">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG29">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.26</v>
       </c>
       <c r="AK29">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="P30">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="Q30">
         <v>2.7</v>
@@ -5214,19 +5214,19 @@
         <v>2.18</v>
       </c>
       <c r="S30">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T30">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="U30">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V30">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
         <v>1</v>
@@ -5235,13 +5235,13 @@
         <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="AA30">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB30">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AC30">
         <v>2.62</v>
@@ -5256,7 +5256,7 @@
         <v>1.55</v>
       </c>
       <c r="AG30">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.34</v>
       </c>
       <c r="AK30">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,28 +5362,28 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="O31">
-        <v>3.66</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S31">
         <v>1.22</v>
       </c>
       <c r="T31">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="U31">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="V31">
         <v>1.58</v>
@@ -5395,31 +5395,31 @@
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA31">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AB31">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AC31">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="AD31">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE31">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF31">
         <v>1.5</v>
       </c>
       <c r="AG31">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK31">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,43 +5525,43 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="O32">
         <v>4</v>
       </c>
       <c r="P32">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q32">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="R32">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="U32">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W32">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z32">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="AA32">
         <v>1.75</v>
@@ -5573,10 +5573,10 @@
         <v>2.9</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF32">
         <v>1.7</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="O34">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="P34">
-        <v>6.54</v>
+        <v>6.68</v>
       </c>
       <c r="Q34">
         <v>1.85</v>
       </c>
       <c r="R34">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="S34">
         <v>1.23</v>
@@ -5878,34 +5878,34 @@
         <v>1.63</v>
       </c>
       <c r="W34">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z34">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="AA34">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB34">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AC34">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AD34">
         <v>1.6</v>
       </c>
       <c r="AE34">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF34">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
         <v>2.15</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AK34">
         <v>3</v>
@@ -6014,43 +6014,43 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="O35">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="P35">
-        <v>5.03</v>
+        <v>4.9</v>
       </c>
       <c r="Q35">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="R35">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T35">
         <v>3.6</v>
       </c>
       <c r="U35">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V35">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
         <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA35">
         <v>1.5</v>
@@ -6059,13 +6059,13 @@
         <v>2.28</v>
       </c>
       <c r="AC35">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AD35">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE35">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF35">
         <v>1.6</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,16 +6186,16 @@
         <v>4.4</v>
       </c>
       <c r="Q36">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="R36">
         <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T36">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U36">
         <v>2.88</v>
@@ -6210,19 +6210,19 @@
         <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z36">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="AA36">
         <v>2.05</v>
       </c>
       <c r="AB36">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC36">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AD36">
         <v>1.26</v>
@@ -6250,7 +6250,7 @@
         <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="O37">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="P37">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -6355,16 +6355,16 @@
         <v>2.12</v>
       </c>
       <c r="S37">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T37">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="U37">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="V37">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W37">
         <v>1.03</v>
@@ -6373,31 +6373,31 @@
         <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z37">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AA37">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AB37">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC37">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="AD37">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE37">
         <v>1.02</v>
       </c>
       <c r="AF37">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AG37">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AK37">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="O42">
         <v>2.99</v>
@@ -7164,10 +7164,10 @@
         <v>2.5</v>
       </c>
       <c r="Q42">
-        <v>4.25</v>
+        <v>3.69</v>
       </c>
       <c r="R42">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="S42">
         <v>1.42</v>
@@ -7176,34 +7176,34 @@
         <v>2.5</v>
       </c>
       <c r="U42">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="V42">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W42">
         <v>1</v>
       </c>
       <c r="X42">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Z42">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AA42">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB42">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC42">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AD42">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE42">
         <v>1.02</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="O44">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="P44">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="Q44">
         <v>2.79</v>
@@ -7502,7 +7502,7 @@
         <v>2.65</v>
       </c>
       <c r="U44">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="V44">
         <v>1.36</v>
@@ -7532,7 +7532,7 @@
         <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF44">
         <v>1.83</v>
@@ -7554,7 +7554,7 @@
         <v>1.33</v>
       </c>
       <c r="AK44">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="O47">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="P47">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -7985,7 +7985,7 @@
         <v>2.15</v>
       </c>
       <c r="S47">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T47">
         <v>3.02</v>
@@ -8000,7 +8000,7 @@
         <v>1.06</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
         <v>1.29</v>
@@ -8009,25 +8009,25 @@
         <v>3.53</v>
       </c>
       <c r="AA47">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB47">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC47">
         <v>3.25</v>
       </c>
       <c r="AD47">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE47">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF47">
         <v>1.75</v>
       </c>
       <c r="AG47">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK47">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,25 +8133,25 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="O48">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="P48">
-        <v>6.85</v>
+        <v>5</v>
       </c>
       <c r="Q48">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R48">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
         <v>1.37</v>
       </c>
       <c r="T48">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U48">
         <v>2.86</v>
@@ -8160,7 +8160,7 @@
         <v>1.43</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8169,28 +8169,28 @@
         <v>1.28</v>
       </c>
       <c r="Z48">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA48">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AB48">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC48">
         <v>3.2</v>
       </c>
       <c r="AD48">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE48">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG48">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.14</v>
       </c>
       <c r="AK48">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="O50">
-        <v>3.81</v>
+        <v>3.6</v>
       </c>
       <c r="P50">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q50">
         <v>4.15</v>
       </c>
       <c r="R50">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S50">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="U50">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V50">
         <v>1.55</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z50">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA50">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB50">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC50">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AD50">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE50">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF50">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG50">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R51">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="S51">
         <v>1.66</v>
@@ -8655,10 +8655,10 @@
         <v>1.1</v>
       </c>
       <c r="Y51">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z51">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AA51">
         <v>2.9</v>
@@ -8676,10 +8676,10 @@
         <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AG51">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK51">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9440,10 +9440,10 @@
         <v>2.06</v>
       </c>
       <c r="O56">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P56">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q56">
         <v>2.77</v>
@@ -9479,7 +9479,7 @@
         <v>2.13</v>
       </c>
       <c r="AB56">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC56">
         <v>4.2</v>
@@ -9494,7 +9494,7 @@
         <v>1.91</v>
       </c>
       <c r="AG56">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O57">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="P57">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q57">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="R57">
-        <v>2.76</v>
+        <v>2.54</v>
       </c>
       <c r="S57">
         <v>1.14</v>
@@ -9621,10 +9621,10 @@
         <v>4.6</v>
       </c>
       <c r="U57">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="V57">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="W57">
         <v>1.25</v>
@@ -9633,31 +9633,31 @@
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z57">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA57">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AB57">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="AC57">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AD57">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE57">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AF57">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AG57">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
         <v>1.48</v>
@@ -9763,19 +9763,19 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="O58">
-        <v>3.77</v>
+        <v>3.4</v>
       </c>
       <c r="P58">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q58">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R58">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S58">
         <v>1.47</v>
@@ -9784,10 +9784,10 @@
         <v>2.45</v>
       </c>
       <c r="U58">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="V58">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W58">
         <v>1.02</v>
@@ -9796,13 +9796,13 @@
         <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z58">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="AA58">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AB58">
         <v>1.52</v>
@@ -9814,13 +9814,13 @@
         <v>1.2</v>
       </c>
       <c r="AE58">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF58">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AG58">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK58">
         <v>2</v>
@@ -9926,19 +9926,19 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="O59">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="P59">
-        <v>2.65</v>
+        <v>2.28</v>
       </c>
       <c r="Q59">
         <v>3.5</v>
       </c>
       <c r="R59">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S59">
         <v>1.48</v>
@@ -9947,10 +9947,10 @@
         <v>2.5</v>
       </c>
       <c r="U59">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V59">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W59">
         <v>1.01</v>
@@ -9959,16 +9959,16 @@
         <v>1.1</v>
       </c>
       <c r="Y59">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="Z59">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AA59">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AB59">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AC59">
         <v>4.33</v>
@@ -9977,13 +9977,13 @@
         <v>1.17</v>
       </c>
       <c r="AE59">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF59">
         <v>2</v>
       </c>
       <c r="AG59">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10098,22 +10098,22 @@
         <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="R60">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S60">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T60">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U60">
-        <v>3.66</v>
+        <v>3.35</v>
       </c>
       <c r="V60">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="W60">
         <v>1.02</v>
@@ -10122,31 +10122,31 @@
         <v>1.06</v>
       </c>
       <c r="Y60">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="Z60">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AA60">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AB60">
         <v>1.5</v>
       </c>
       <c r="AC60">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AD60">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE60">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF60">
         <v>2.1</v>
       </c>
       <c r="AG60">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AK60">
         <v>1.53</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O61">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P61">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q61">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R61">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S61">
         <v>1.42</v>
@@ -10273,10 +10273,10 @@
         <v>2.62</v>
       </c>
       <c r="U61">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V61">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W61">
         <v>1.06</v>
@@ -10285,7 +10285,7 @@
         <v>1.04</v>
       </c>
       <c r="Y61">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z61">
         <v>3</v>
@@ -10300,13 +10300,13 @@
         <v>3.9</v>
       </c>
       <c r="AD61">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE61">
         <v>1.09</v>
       </c>
       <c r="AF61">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG61">
         <v>1.85</v>
@@ -10421,7 +10421,7 @@
         <v>2.87</v>
       </c>
       <c r="P62">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q62">
         <v>3.48</v>
@@ -10433,7 +10433,7 @@
         <v>1.45</v>
       </c>
       <c r="T62">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="U62">
         <v>3.35</v>
@@ -10442,7 +10442,7 @@
         <v>1.27</v>
       </c>
       <c r="W62">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X62">
         <v>1.05</v>
@@ -10472,7 +10472,7 @@
         <v>1.99</v>
       </c>
       <c r="AG62">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK62">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="O63">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="P63">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="Q63">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="R63">
         <v>2.05</v>
       </c>
       <c r="S63">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T63">
+        <v>2.57</v>
+      </c>
+      <c r="U63">
         <v>2.8</v>
       </c>
-      <c r="U63">
-        <v>2.78</v>
-      </c>
       <c r="V63">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W63">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y63">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z63">
-        <v>3.25</v>
+        <v>3.49</v>
       </c>
       <c r="AA63">
         <v>2.05</v>
       </c>
       <c r="AB63">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC63">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="AD63">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE63">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF63">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG63">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.31</v>
       </c>
       <c r="AK63">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,10 +10750,10 @@
         <v>6.15</v>
       </c>
       <c r="Q64">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="R64">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S64">
         <v>1.62</v>
@@ -10771,13 +10771,13 @@
         <v>1.03</v>
       </c>
       <c r="X64">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Y64">
         <v>1.62</v>
       </c>
       <c r="Z64">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AA64">
         <v>2.88</v>
@@ -10789,16 +10789,16 @@
         <v>5.6</v>
       </c>
       <c r="AD64">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AE64">
         <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AG64">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="O66">
         <v>3.65</v>
@@ -11085,7 +11085,7 @@
         <v>1.3</v>
       </c>
       <c r="T66">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U66">
         <v>2.6</v>
@@ -11100,7 +11100,7 @@
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z66">
         <v>3.72</v>
@@ -11112,19 +11112,19 @@
         <v>1.95</v>
       </c>
       <c r="AC66">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="AD66">
         <v>1.3</v>
       </c>
       <c r="AE66">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF66">
         <v>1.78</v>
       </c>
       <c r="AG66">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,34 +11230,34 @@
         </is>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O67">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="P67">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q67">
         <v>3.7</v>
       </c>
       <c r="R67">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="S67">
         <v>1.4</v>
       </c>
       <c r="T67">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="U67">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="V67">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W67">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X67">
         <v>1.02</v>
@@ -11269,13 +11269,13 @@
         <v>3.1</v>
       </c>
       <c r="AA67">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AB67">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC67">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AD67">
         <v>1.18</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -970,7 +970,7 @@
         <v>1.95</v>
       </c>
       <c r="Q4">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="R4">
         <v>2.04</v>
@@ -979,10 +979,10 @@
         <v>1.41</v>
       </c>
       <c r="T4">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="U4">
-        <v>3.11</v>
+        <v>2.99</v>
       </c>
       <c r="V4">
         <v>1.33</v>
@@ -1012,7 +1012,7 @@
         <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
         <v>1.85</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AK4">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1785,10 +1785,10 @@
         <v>5.45</v>
       </c>
       <c r="Q9">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="R9">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S9">
         <v>1.42</v>
@@ -1797,7 +1797,7 @@
         <v>2.75</v>
       </c>
       <c r="U9">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="V9">
         <v>1.33</v>
@@ -1812,25 +1812,25 @@
         <v>1.35</v>
       </c>
       <c r="Z9">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AA9">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AB9">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC9">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE9">
         <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AG9">
         <v>1.68</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="O10">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>4.32</v>
+        <v>4.5</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -1954,40 +1954,40 @@
         <v>2.39</v>
       </c>
       <c r="S10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="U10">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="V10">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA10">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB10">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AC10">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="AD10">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
@@ -3409,22 +3409,22 @@
         <v>3</v>
       </c>
       <c r="O19">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
         <v>2.35</v>
       </c>
       <c r="Q19">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="R19">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S19">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T19">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="U19">
         <v>3.3</v>
@@ -3445,25 +3445,25 @@
         <v>2.9</v>
       </c>
       <c r="AA19">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AB19">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC19">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AD19">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
         <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG19">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
+        <v>1.33</v>
+      </c>
+      <c r="AK19">
         <v>1.34</v>
-      </c>
-      <c r="AK19">
-        <v>1.35</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>7.9</v>
       </c>
       <c r="Q26">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R26">
-        <v>2.59</v>
+        <v>2.36</v>
       </c>
       <c r="S26">
         <v>1.36</v>
@@ -4586,10 +4586,10 @@
         <v>3.69</v>
       </c>
       <c r="AA26">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC26">
         <v>2.88</v>
@@ -4601,10 +4601,10 @@
         <v>1.12</v>
       </c>
       <c r="AF26">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AG26">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AK26">
-        <v>3.62</v>
+        <v>3.72</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -7321,22 +7321,22 @@
         <v>2.1</v>
       </c>
       <c r="O43">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="P43">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="Q43">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="R43">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S43">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T43">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U43">
         <v>3</v>
@@ -7357,13 +7357,13 @@
         <v>2.83</v>
       </c>
       <c r="AA43">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AB43">
         <v>1.62</v>
       </c>
       <c r="AC43">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AD43">
         <v>1.18</v>
@@ -7372,10 +7372,10 @@
         <v>1.02</v>
       </c>
       <c r="AF43">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG43">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK43">
         <v>1.58</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.37</v>
+        <v>2.68</v>
       </c>
       <c r="O46">
         <v>2.6</v>
       </c>
       <c r="P46">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="Q46">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="R46">
         <v>1.95</v>
       </c>
       <c r="S46">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T46">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="U46">
         <v>3.36</v>
       </c>
       <c r="V46">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W46">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X46">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y46">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Z46">
         <v>2.5</v>
       </c>
       <c r="AA46">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AB46">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AC46">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="AD46">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE46">
         <v>1.02</v>
       </c>
       <c r="AF46">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AG46">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK46">
         <v>1.5</v>
@@ -8797,13 +8797,13 @@
         <v>1.83</v>
       </c>
       <c r="R52">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="S52">
         <v>1.33</v>
       </c>
       <c r="T52">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="U52">
         <v>2.75</v>
@@ -8812,7 +8812,7 @@
         <v>1.39</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
         <v>1</v>
@@ -8842,7 +8842,7 @@
         <v>2.08</v>
       </c>
       <c r="AG52">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>2.37</v>
       </c>
       <c r="Q54">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="R54">
         <v>1.95</v>
@@ -9129,7 +9129,7 @@
         <v>1.44</v>
       </c>
       <c r="T54">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="U54">
         <v>3.12</v>
@@ -9141,22 +9141,22 @@
         <v>1.02</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
         <v>1.36</v>
       </c>
       <c r="Z54">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AA54">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AB54">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC54">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AD54">
         <v>1.18</v>
@@ -9165,10 +9165,10 @@
         <v>1.03</v>
       </c>
       <c r="AF54">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG54">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK54">
         <v>1.34</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="O55">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="P55">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q55">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -1009,7 +1009,7 @@
         <v>3.58</v>
       </c>
       <c r="AD4">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE4">
         <v>1.04</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AK4">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1818,10 +1818,10 @@
         <v>2.15</v>
       </c>
       <c r="AB9">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD9">
         <v>1.2</v>
@@ -1849,7 +1849,7 @@
         <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="O11">
-        <v>4.1</v>
+        <v>4.22</v>
       </c>
       <c r="P11">
-        <v>5.25</v>
+        <v>5.38</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="O18">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Q18">
         <v>4.2</v>
       </c>
       <c r="R18">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="S18">
         <v>1.36</v>
@@ -3264,34 +3264,34 @@
         <v>2.59</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V18">
         <v>1.36</v>
       </c>
       <c r="W18">
+        <v>1.05</v>
+      </c>
+      <c r="X18">
         <v>1.06</v>
-      </c>
-      <c r="X18">
-        <v>1.04</v>
       </c>
       <c r="Y18">
         <v>1.3</v>
       </c>
       <c r="Z18">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AA18">
         <v>2.02</v>
       </c>
       <c r="AB18">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC18">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD18">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE18">
         <v>1.06</v>
@@ -3300,7 +3300,7 @@
         <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3427,10 +3427,10 @@
         <v>2.44</v>
       </c>
       <c r="U19">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="V19">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W19">
         <v>1.02</v>
@@ -3439,10 +3439,10 @@
         <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AA19">
         <v>2.23</v>
@@ -3451,7 +3451,7 @@
         <v>1.65</v>
       </c>
       <c r="AC19">
-        <v>3.86</v>
+        <v>4.06</v>
       </c>
       <c r="AD19">
         <v>1.22</v>
@@ -3463,7 +3463,7 @@
         <v>1.88</v>
       </c>
       <c r="AG19">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3898,61 +3898,61 @@
         <v>2.2</v>
       </c>
       <c r="O22">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q22">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="R22">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S22">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T22">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="U22">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="V22">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
         <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z22">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="AA22">
         <v>2.15</v>
       </c>
       <c r="AB22">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC22">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AD22">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE22">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF22">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG22">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4233,22 +4233,22 @@
         <v>4</v>
       </c>
       <c r="R24">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
         <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U24">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="V24">
         <v>1.58</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4257,10 +4257,10 @@
         <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AA24">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB24">
         <v>2.3</v>
@@ -4278,7 +4278,7 @@
         <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4393,10 +4393,10 @@
         <v>3.24</v>
       </c>
       <c r="Q25">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="R25">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="S25">
         <v>1.48</v>
@@ -4411,10 +4411,10 @@
         <v>1.33</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
         <v>1.41</v>
@@ -4423,10 +4423,10 @@
         <v>2.62</v>
       </c>
       <c r="AA25">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AB25">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC25">
         <v>4.05</v>
@@ -4435,7 +4435,7 @@
         <v>1.16</v>
       </c>
       <c r="AE25">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
         <v>1.95</v>
@@ -4565,7 +4565,7 @@
         <v>1.36</v>
       </c>
       <c r="T26">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="U26">
         <v>2.66</v>
@@ -4580,7 +4580,7 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
         <v>3.69</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK26">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P28">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="P29">
-        <v>3.55</v>
+        <v>2.78</v>
       </c>
       <c r="Q29">
         <v>2.51</v>
@@ -5054,7 +5054,7 @@
         <v>1.33</v>
       </c>
       <c r="T29">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U29">
         <v>2.45</v>
@@ -5069,10 +5069,10 @@
         <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA29">
         <v>1.73</v>
@@ -5087,13 +5087,13 @@
         <v>1.36</v>
       </c>
       <c r="AE29">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG29">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5202,10 +5202,10 @@
         <v>2.17</v>
       </c>
       <c r="O30">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q30">
         <v>2.7</v>
@@ -5217,7 +5217,7 @@
         <v>1.29</v>
       </c>
       <c r="T30">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U30">
         <v>2.3</v>
@@ -5226,7 +5226,7 @@
         <v>1.52</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
         <v>1</v>
@@ -5235,19 +5235,19 @@
         <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>3.92</v>
+        <v>4.33</v>
       </c>
       <c r="AA30">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB30">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC30">
         <v>2.62</v>
       </c>
       <c r="AD30">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
         <v>1.14</v>
@@ -5256,7 +5256,7 @@
         <v>1.55</v>
       </c>
       <c r="AG30">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.34</v>
       </c>
       <c r="AK30">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P31">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
       </c>
       <c r="R31">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="S31">
         <v>1.22</v>
@@ -5389,13 +5389,13 @@
         <v>1.58</v>
       </c>
       <c r="W31">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z31">
         <v>4.6</v>
@@ -5407,10 +5407,10 @@
         <v>2.27</v>
       </c>
       <c r="AC31">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AD31">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE31">
         <v>1.18</v>
@@ -5419,7 +5419,7 @@
         <v>1.5</v>
       </c>
       <c r="AG31">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AK31">
         <v>1.5</v>
@@ -5528,19 +5528,19 @@
         <v>1.73</v>
       </c>
       <c r="O32">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
         <v>3.7</v>
       </c>
       <c r="Q32">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="R32">
         <v>2.35</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
         <v>3.22</v>
@@ -5558,22 +5558,22 @@
         <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="AA32">
         <v>1.75</v>
       </c>
       <c r="AB32">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC32">
         <v>2.9</v>
       </c>
       <c r="AD32">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE32">
         <v>1.14</v>
@@ -5582,7 +5582,7 @@
         <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
         <v>2</v>
@@ -5854,13 +5854,13 @@
         <v>1.41</v>
       </c>
       <c r="O34">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="P34">
-        <v>6.68</v>
+        <v>6.1</v>
       </c>
       <c r="Q34">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="R34">
         <v>2.63</v>
@@ -5884,13 +5884,13 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z34">
-        <v>5.25</v>
+        <v>5.05</v>
       </c>
       <c r="AA34">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB34">
         <v>2.45</v>
@@ -5902,7 +5902,7 @@
         <v>1.6</v>
       </c>
       <c r="AE34">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF34">
         <v>1.62</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
         <v>3</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="O35">
         <v>4.15</v>
       </c>
       <c r="P35">
-        <v>4.9</v>
+        <v>4.35</v>
       </c>
       <c r="Q35">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="R35">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="S35">
         <v>1.26</v>
@@ -6038,7 +6038,7 @@
         <v>2.25</v>
       </c>
       <c r="V35">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W35">
         <v>1.12</v>
@@ -6062,7 +6062,7 @@
         <v>2.12</v>
       </c>
       <c r="AD35">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE35">
         <v>1.22</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK35">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,16 +6186,16 @@
         <v>4.4</v>
       </c>
       <c r="Q36">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="R36">
         <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T36">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U36">
         <v>2.88</v>
@@ -6213,13 +6213,13 @@
         <v>1.28</v>
       </c>
       <c r="Z36">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="AA36">
         <v>2.05</v>
       </c>
       <c r="AB36">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC36">
         <v>3.55</v>
@@ -6250,7 +6250,7 @@
         <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,25 +6343,25 @@
         <v>2.03</v>
       </c>
       <c r="O37">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P37">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="Q37">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="R37">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S37">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="T37">
         <v>2.43</v>
       </c>
       <c r="U37">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="V37">
         <v>1.3</v>
@@ -6382,10 +6382,10 @@
         <v>2.43</v>
       </c>
       <c r="AB37">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC37">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="AD37">
         <v>1.17</v>
@@ -6397,7 +6397,7 @@
         <v>2.02</v>
       </c>
       <c r="AG37">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK37">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="O40">
+        <v>4.22</v>
+      </c>
+      <c r="P40">
         <v>4.2</v>
       </c>
-      <c r="P40">
-        <v>4.36</v>
-      </c>
       <c r="Q40">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="R40">
         <v>2.48</v>
@@ -6847,7 +6847,7 @@
         <v>1.22</v>
       </c>
       <c r="T40">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="U40">
         <v>2.03</v>
@@ -6856,10 +6856,10 @@
         <v>1.72</v>
       </c>
       <c r="W40">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
         <v>1.11</v>
@@ -6902,7 +6902,7 @@
         <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6998,13 +6998,13 @@
         <v>4.4</v>
       </c>
       <c r="P41">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q41">
         <v>4.6</v>
       </c>
       <c r="R41">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="S41">
         <v>1.22</v>
@@ -7025,10 +7025,10 @@
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z41">
-        <v>5.25</v>
+        <v>5.52</v>
       </c>
       <c r="AA41">
         <v>1.4</v>
@@ -7043,13 +7043,13 @@
         <v>1.67</v>
       </c>
       <c r="AE41">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AF41">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG41">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7158,25 +7158,25 @@
         <v>3.3</v>
       </c>
       <c r="O42">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="P42">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q42">
         <v>3.69</v>
       </c>
       <c r="R42">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S42">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T42">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U42">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="V42">
         <v>1.3</v>
@@ -7194,25 +7194,25 @@
         <v>2.5</v>
       </c>
       <c r="AA42">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AB42">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC42">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD42">
         <v>1.17</v>
       </c>
       <c r="AE42">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF42">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AG42">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK42">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="O44">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
         <v>3.25</v>
       </c>
       <c r="Q44">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="R44">
         <v>2</v>
@@ -7502,10 +7502,10 @@
         <v>2.65</v>
       </c>
       <c r="U44">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W44">
         <v>1.03</v>
@@ -7532,7 +7532,7 @@
         <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF44">
         <v>1.83</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK44">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="O47">
-        <v>3.9</v>
+        <v>3.18</v>
       </c>
       <c r="P47">
-        <v>3.9</v>
+        <v>4.12</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -7985,49 +7985,49 @@
         <v>2.15</v>
       </c>
       <c r="S47">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T47">
         <v>3.02</v>
       </c>
       <c r="U47">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V47">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W47">
         <v>1.06</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z47">
         <v>3.53</v>
       </c>
       <c r="AA47">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB47">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC47">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="AD47">
         <v>1.3</v>
       </c>
       <c r="AE47">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF47">
         <v>1.75</v>
       </c>
       <c r="AG47">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8136,25 +8136,25 @@
         <v>1.58</v>
       </c>
       <c r="O48">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="Q48">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S48">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T48">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U48">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="V48">
         <v>1.43</v>
@@ -8166,31 +8166,31 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z48">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AA48">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB48">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC48">
         <v>3.2</v>
       </c>
       <c r="AD48">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE48">
         <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG48">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.14</v>
       </c>
       <c r="AK48">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8465,58 +8465,58 @@
         <v>3.6</v>
       </c>
       <c r="P50">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="Q50">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="R50">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="S50">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="T50">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="V50">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W50">
         <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z50">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB50">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AC50">
-        <v>2.41</v>
+        <v>2.68</v>
       </c>
       <c r="AD50">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE50">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF50">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8631,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R51">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S51">
         <v>1.66</v>
@@ -8646,7 +8646,7 @@
         <v>4</v>
       </c>
       <c r="V51">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W51">
         <v>1.03</v>
@@ -8655,19 +8655,19 @@
         <v>1.1</v>
       </c>
       <c r="Y51">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z51">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AA51">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AB51">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC51">
-        <v>6.43</v>
+        <v>6.5</v>
       </c>
       <c r="AD51">
         <v>1.1</v>
@@ -8676,10 +8676,10 @@
         <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AG51">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK51">
         <v>1.4</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="O56">
         <v>3.1</v>
@@ -9452,7 +9452,7 @@
         <v>1.94</v>
       </c>
       <c r="S56">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="T56">
         <v>2.41</v>
@@ -9476,7 +9476,7 @@
         <v>2.89</v>
       </c>
       <c r="AA56">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="AB56">
         <v>1.6</v>
@@ -9600,25 +9600,25 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O57">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
         <v>2.3</v>
       </c>
       <c r="Q57">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="R57">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="S57">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T57">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="U57">
         <v>1.87</v>
@@ -9633,25 +9633,25 @@
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z57">
-        <v>7.5</v>
+        <v>6.85</v>
       </c>
       <c r="AA57">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AB57">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AC57">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AD57">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AE57">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AF57">
         <v>1.28</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK57">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9766,10 +9766,10 @@
         <v>1.73</v>
       </c>
       <c r="O58">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P58">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -9778,13 +9778,13 @@
         <v>2.02</v>
       </c>
       <c r="S58">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T58">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="U58">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V58">
         <v>1.29</v>
@@ -9796,7 +9796,7 @@
         <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z58">
         <v>2.83</v>
@@ -9805,7 +9805,7 @@
         <v>2.34</v>
       </c>
       <c r="AB58">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AC58">
         <v>4.33</v>
@@ -9814,13 +9814,13 @@
         <v>1.2</v>
       </c>
       <c r="AE58">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF58">
         <v>2.13</v>
       </c>
       <c r="AG58">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O59">
         <v>3</v>
       </c>
       <c r="P59">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="Q59">
         <v>3.5</v>
@@ -9944,7 +9944,7 @@
         <v>1.48</v>
       </c>
       <c r="T59">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U59">
         <v>3.4</v>
@@ -9959,31 +9959,31 @@
         <v>1.1</v>
       </c>
       <c r="Y59">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="Z59">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="AA59">
         <v>2.31</v>
       </c>
       <c r="AB59">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC59">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="AD59">
         <v>1.17</v>
       </c>
       <c r="AE59">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF59">
         <v>2</v>
       </c>
       <c r="AG59">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10101,19 +10101,19 @@
         <v>3.32</v>
       </c>
       <c r="R60">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S60">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="T60">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="U60">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="V60">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W60">
         <v>1.02</v>
@@ -10125,28 +10125,28 @@
         <v>1.46</v>
       </c>
       <c r="Z60">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="AA60">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="AB60">
         <v>1.5</v>
       </c>
       <c r="AC60">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="AD60">
         <v>1.13</v>
       </c>
       <c r="AE60">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF60">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG60">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AK60">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="O61">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P61">
-        <v>4.5</v>
+        <v>2.33</v>
       </c>
       <c r="Q61">
-        <v>2.3</v>
+        <v>3.75</v>
       </c>
       <c r="R61">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S61">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="T61">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="U61">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="V61">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W61">
+        <v>1.02</v>
+      </c>
+      <c r="X61">
         <v>1.06</v>
       </c>
-      <c r="X61">
-        <v>1.04</v>
-      </c>
       <c r="Y61">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="Z61">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AA61">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AB61">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AC61">
-        <v>3.9</v>
+        <v>4.53</v>
       </c>
       <c r="AD61">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AE61">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AF61">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG61">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="AK61">
-        <v>2.02</v>
+        <v>1.41</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="O62">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="P62">
-        <v>2.55</v>
+        <v>4.1</v>
       </c>
       <c r="Q62">
-        <v>3.48</v>
+        <v>2.25</v>
       </c>
       <c r="R62">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="S62">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T62">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="U62">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="V62">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="W62">
+        <v>1.04</v>
+      </c>
+      <c r="X62">
         <v>1.01</v>
       </c>
-      <c r="X62">
-        <v>1.05</v>
-      </c>
       <c r="Y62">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="Z62">
-        <v>2.49</v>
+        <v>3.25</v>
       </c>
       <c r="AA62">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AB62">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="AC62">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD62">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AE62">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF62">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AG62">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK62">
-        <v>1.44</v>
+        <v>2.07</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10581,61 +10581,61 @@
         <v>2.28</v>
       </c>
       <c r="O63">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="P63">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="Q63">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="R63">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S63">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T63">
         <v>2.57</v>
       </c>
       <c r="U63">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="V63">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W63">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X63">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y63">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z63">
-        <v>3.49</v>
+        <v>3.18</v>
       </c>
       <c r="AA63">
         <v>2.05</v>
       </c>
       <c r="AB63">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC63">
         <v>3.45</v>
       </c>
       <c r="AD63">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE63">
         <v>1.11</v>
       </c>
       <c r="AF63">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG63">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>1.62</v>
       </c>
       <c r="T64">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U64">
         <v>3.9</v>
@@ -10768,16 +10768,16 @@
         <v>1.18</v>
       </c>
       <c r="W64">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X64">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y64">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="Z64">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA64">
         <v>2.88</v>
@@ -10786,10 +10786,10 @@
         <v>1.36</v>
       </c>
       <c r="AC64">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="AD64">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE64">
         <v>1.03</v>
@@ -10922,13 +10922,13 @@
         <v>1.35</v>
       </c>
       <c r="T65">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="U65">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="V65">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="W65">
         <v>1.1</v>
@@ -10943,25 +10943,25 @@
         <v>3.45</v>
       </c>
       <c r="AA65">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AB65">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC65">
         <v>2.85</v>
       </c>
       <c r="AD65">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE65">
         <v>1.08</v>
       </c>
       <c r="AF65">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG65">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK65">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="O66">
         <v>3.65</v>
@@ -11085,10 +11085,10 @@
         <v>1.3</v>
       </c>
       <c r="T66">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U66">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V66">
         <v>1.42</v>
@@ -11100,10 +11100,10 @@
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z66">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="AA66">
         <v>1.75</v>
@@ -11112,19 +11112,19 @@
         <v>1.95</v>
       </c>
       <c r="AC66">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AD66">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE66">
         <v>1.13</v>
       </c>
       <c r="AF66">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG66">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11230,31 +11230,31 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="O67">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="P67">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q67">
         <v>3.7</v>
       </c>
       <c r="R67">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="S67">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T67">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U67">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="V67">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W67">
         <v>1.03</v>
@@ -11269,16 +11269,16 @@
         <v>3.1</v>
       </c>
       <c r="AA67">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AB67">
         <v>1.63</v>
       </c>
       <c r="AC67">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="AD67">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE67">
         <v>1.02</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -3249,13 +3249,13 @@
         <v>3.2</v>
       </c>
       <c r="P18">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q18">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="R18">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S18">
         <v>1.36</v>
@@ -3264,34 +3264,34 @@
         <v>2.59</v>
       </c>
       <c r="U18">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
         <v>1.3</v>
       </c>
       <c r="Z18">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA18">
         <v>2.02</v>
       </c>
       <c r="AB18">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD18">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE18">
         <v>1.06</v>
@@ -3300,7 +3300,7 @@
         <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -4230,19 +4230,19 @@
         <v>1.81</v>
       </c>
       <c r="Q24">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S24">
         <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="V24">
         <v>1.58</v>
@@ -4257,7 +4257,7 @@
         <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="AA24">
         <v>1.57</v>
@@ -4272,13 +4272,13 @@
         <v>1.5</v>
       </c>
       <c r="AE24">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
         <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>3.24</v>
       </c>
       <c r="Q25">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="R25">
         <v>2</v>
@@ -4411,22 +4411,22 @@
         <v>1.33</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y25">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z25">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA25">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AB25">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AC25">
         <v>4.05</v>
@@ -4435,7 +4435,7 @@
         <v>1.16</v>
       </c>
       <c r="AE25">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
         <v>1.95</v>
@@ -4457,7 +4457,7 @@
         <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -6207,7 +6207,7 @@
         <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y36">
         <v>1.28</v>
@@ -6219,7 +6219,7 @@
         <v>2.05</v>
       </c>
       <c r="AB36">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC36">
         <v>3.55</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -7167,16 +7167,16 @@
         <v>3.69</v>
       </c>
       <c r="R42">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S42">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="T42">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U42">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="V42">
         <v>1.3</v>
@@ -7200,19 +7200,19 @@
         <v>1.48</v>
       </c>
       <c r="AC42">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AD42">
         <v>1.17</v>
       </c>
       <c r="AE42">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF42">
         <v>1.87</v>
       </c>
       <c r="AG42">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7321,13 +7321,13 @@
         <v>2.1</v>
       </c>
       <c r="O43">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P43">
         <v>3.27</v>
       </c>
       <c r="Q43">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="R43">
         <v>1.92</v>
@@ -7363,7 +7363,7 @@
         <v>1.62</v>
       </c>
       <c r="AC43">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="AD43">
         <v>1.18</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="O44">
         <v>3.3</v>
@@ -7502,10 +7502,10 @@
         <v>2.65</v>
       </c>
       <c r="U44">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="V44">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
         <v>1.03</v>
@@ -7532,7 +7532,7 @@
         <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF44">
         <v>1.83</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK44">
         <v>1.65</v>
@@ -8465,7 +8465,7 @@
         <v>3.6</v>
       </c>
       <c r="P50">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q50">
         <v>4.3</v>
@@ -8474,22 +8474,22 @@
         <v>2.28</v>
       </c>
       <c r="S50">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="V50">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
         <v>1.18</v>
@@ -8498,25 +8498,25 @@
         <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AB50">
         <v>2.13</v>
       </c>
       <c r="AC50">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="AD50">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
         <v>1.18</v>
       </c>
       <c r="AF50">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8631,22 +8631,22 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R51">
         <v>1.72</v>
       </c>
       <c r="S51">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T51">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="U51">
         <v>4</v>
       </c>
       <c r="V51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W51">
         <v>1.03</v>
@@ -8655,19 +8655,19 @@
         <v>1.1</v>
       </c>
       <c r="Y51">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z51">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AA51">
         <v>2.83</v>
       </c>
       <c r="AB51">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AC51">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
       <c r="AD51">
         <v>1.1</v>
@@ -8676,7 +8676,7 @@
         <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AG51">
         <v>1.53</v>
@@ -8800,19 +8800,19 @@
         <v>2.28</v>
       </c>
       <c r="S52">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T52">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="U52">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V52">
         <v>1.39</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X52">
         <v>1</v>
@@ -8858,7 +8858,7 @@
         <v>1.02</v>
       </c>
       <c r="AK52">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9132,7 +9132,7 @@
         <v>2.46</v>
       </c>
       <c r="U54">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="V54">
         <v>1.28</v>
@@ -9156,10 +9156,10 @@
         <v>1.59</v>
       </c>
       <c r="AC54">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="AD54">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE54">
         <v>1.03</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
+        <v>1.3</v>
+      </c>
+      <c r="AK54">
         <v>1.33</v>
-      </c>
-      <c r="AK54">
-        <v>1.34</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9440,10 +9440,10 @@
         <v>2</v>
       </c>
       <c r="O56">
+        <v>3.2</v>
+      </c>
+      <c r="P56">
         <v>3.1</v>
-      </c>
-      <c r="P56">
-        <v>3.3</v>
       </c>
       <c r="Q56">
         <v>2.77</v>
@@ -9452,10 +9452,10 @@
         <v>1.94</v>
       </c>
       <c r="S56">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T56">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="U56">
         <v>3.1</v>
@@ -9473,16 +9473,16 @@
         <v>1.42</v>
       </c>
       <c r="Z56">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AA56">
         <v>2.23</v>
       </c>
       <c r="AB56">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC56">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD56">
         <v>1.2</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9944,46 +9944,46 @@
         <v>1.48</v>
       </c>
       <c r="T59">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="U59">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V59">
         <v>1.29</v>
       </c>
       <c r="W59">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X59">
         <v>1.1</v>
       </c>
       <c r="Y59">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="Z59">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AA59">
         <v>2.31</v>
       </c>
       <c r="AB59">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AC59">
-        <v>4.55</v>
+        <v>3.98</v>
       </c>
       <c r="AD59">
         <v>1.17</v>
       </c>
       <c r="AE59">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF59">
         <v>2</v>
       </c>
       <c r="AG59">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="R60">
         <v>1.85</v>
@@ -10125,16 +10125,16 @@
         <v>1.46</v>
       </c>
       <c r="Z60">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="AA60">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AB60">
         <v>1.5</v>
       </c>
       <c r="AC60">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD60">
         <v>1.13</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AK60">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,25 +10261,25 @@
         <v>2.33</v>
       </c>
       <c r="Q61">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R61">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="S61">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="T61">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="U61">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V61">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="W61">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X61">
         <v>1.06</v>
@@ -10288,22 +10288,22 @@
         <v>1.41</v>
       </c>
       <c r="Z61">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AA61">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB61">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC61">
-        <v>4.53</v>
+        <v>4.75</v>
       </c>
       <c r="AD61">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE61">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF61">
         <v>1.95</v>
@@ -10424,22 +10424,22 @@
         <v>4.1</v>
       </c>
       <c r="Q62">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="R62">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="S62">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T62">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="U62">
         <v>2.98</v>
       </c>
       <c r="V62">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W62">
         <v>1.04</v>
@@ -10451,7 +10451,7 @@
         <v>1.32</v>
       </c>
       <c r="Z62">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA62">
         <v>2</v>
@@ -10466,7 +10466,7 @@
         <v>1.25</v>
       </c>
       <c r="AE62">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF62">
         <v>1.9</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10753,31 +10753,31 @@
         <v>2.3</v>
       </c>
       <c r="R64">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="S64">
         <v>1.62</v>
       </c>
       <c r="T64">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="U64">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="V64">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W64">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X64">
         <v>1.13</v>
       </c>
       <c r="Y64">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Z64">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA64">
         <v>2.88</v>
@@ -10789,16 +10789,16 @@
         <v>6.5</v>
       </c>
       <c r="AD64">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE64">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF64">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AG64">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -8634,7 +8634,7 @@
         <v>3.4</v>
       </c>
       <c r="R51">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S51">
         <v>1.67</v>
@@ -8658,7 +8658,7 @@
         <v>1.62</v>
       </c>
       <c r="Z51">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AA51">
         <v>2.83</v>
@@ -8676,7 +8676,7 @@
         <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AG51">
         <v>1.53</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="O64">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P64">
-        <v>6.15</v>
+        <v>5.83</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -10762,13 +10762,13 @@
         <v>2.17</v>
       </c>
       <c r="U64">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="V64">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W64">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X64">
         <v>1.13</v>
@@ -10780,10 +10780,10 @@
         <v>2.25</v>
       </c>
       <c r="AA64">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="AB64">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC64">
         <v>6.5</v>
@@ -10798,7 +10798,7 @@
         <v>2.6</v>
       </c>
       <c r="AG64">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="Q4">
-        <v>4.33</v>
+        <v>4.55</v>
       </c>
       <c r="R4">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
         <v>1.41</v>
@@ -994,31 +994,31 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA4">
         <v>2.1</v>
       </c>
       <c r="AB4">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC4">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AD4">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE4">
         <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,16 +1133,16 @@
         <v>4.4</v>
       </c>
       <c r="Q5">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U5">
         <v>2.88</v>
@@ -1154,34 +1154,34 @@
         <v>1.06</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB5">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>2.87</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="O9">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="P9">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="Q9">
         <v>2.19</v>
       </c>
       <c r="R9">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="S9">
         <v>1.42</v>
@@ -1833,7 +1833,7 @@
         <v>2.06</v>
       </c>
       <c r="AG9">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK9">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O10">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P10">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -1954,16 +1954,16 @@
         <v>2.39</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U10">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
         <v>1.06</v>
@@ -1978,10 +1978,10 @@
         <v>3.7</v>
       </c>
       <c r="AA10">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB10">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC10">
         <v>2.78</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK10">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,10 +2105,10 @@
         <v>1.52</v>
       </c>
       <c r="O11">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="P11">
-        <v>5.38</v>
+        <v>5.25</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>3.04</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3246,10 +3246,10 @@
         <v>3.4</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="P18">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q18">
         <v>4.45</v>
@@ -3264,7 +3264,7 @@
         <v>2.59</v>
       </c>
       <c r="U18">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V18">
         <v>1.4</v>
@@ -3282,7 +3282,7 @@
         <v>2.97</v>
       </c>
       <c r="AA18">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB18">
         <v>1.8</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
+        <v>3.05</v>
+      </c>
+      <c r="O19">
         <v>3</v>
       </c>
-      <c r="O19">
-        <v>3.1</v>
-      </c>
       <c r="P19">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q19">
         <v>3.78</v>
@@ -3424,10 +3424,10 @@
         <v>1.48</v>
       </c>
       <c r="T19">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="U19">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="V19">
         <v>1.3</v>
@@ -3445,13 +3445,13 @@
         <v>2.7</v>
       </c>
       <c r="AA19">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AB19">
         <v>1.65</v>
       </c>
       <c r="AC19">
-        <v>4.06</v>
+        <v>3.86</v>
       </c>
       <c r="AD19">
         <v>1.22</v>
@@ -3463,7 +3463,7 @@
         <v>1.88</v>
       </c>
       <c r="AG19">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="P21">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O22">
         <v>3.15</v>
       </c>
       <c r="P22">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q22">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="R22">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="S22">
         <v>1.51</v>
       </c>
       <c r="T22">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="U22">
         <v>3.28</v>
@@ -3928,31 +3928,31 @@
         <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z22">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="AA22">
         <v>2.15</v>
       </c>
       <c r="AB22">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC22">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="AD22">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE22">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF22">
         <v>1.91</v>
       </c>
       <c r="AG22">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4230,22 +4230,22 @@
         <v>1.81</v>
       </c>
       <c r="Q24">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R24">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U24">
         <v>2.26</v>
       </c>
       <c r="V24">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W24">
         <v>1.13</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.95</v>
       </c>
       <c r="AK24">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4562,16 +4562,16 @@
         <v>2.36</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
         <v>2.85</v>
       </c>
       <c r="U26">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="V26">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
         <v>1.06</v>
@@ -4583,13 +4583,13 @@
         <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="AA26">
         <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AC26">
         <v>2.88</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK26">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="O28">
         <v>3.45</v>
@@ -5525,58 +5525,58 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P32">
         <v>3.7</v>
       </c>
       <c r="Q32">
+        <v>2.23</v>
+      </c>
+      <c r="R32">
         <v>2.31</v>
       </c>
-      <c r="R32">
-        <v>2.35</v>
-      </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T32">
-        <v>3.22</v>
+        <v>2.91</v>
       </c>
       <c r="U32">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="V32">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA32">
         <v>1.75</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC32">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AD32">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
         <v>1.7</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
         <v>2</v>
@@ -5857,52 +5857,52 @@
         <v>4.6</v>
       </c>
       <c r="P34">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="Q34">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="R34">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S34">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="U34">
         <v>2.08</v>
       </c>
       <c r="V34">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W34">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z34">
-        <v>5.05</v>
+        <v>5.25</v>
       </c>
       <c r="AA34">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB34">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AC34">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AD34">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE34">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF34">
         <v>1.62</v>
@@ -5924,7 +5924,7 @@
         <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6183,7 +6183,7 @@
         <v>3.5</v>
       </c>
       <c r="P36">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="Q36">
         <v>2.4</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="O37">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="P37">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="Q37">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="R37">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="S37">
         <v>1.53</v>
@@ -6361,7 +6361,7 @@
         <v>2.43</v>
       </c>
       <c r="U37">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="V37">
         <v>1.3</v>
@@ -6382,7 +6382,7 @@
         <v>2.43</v>
       </c>
       <c r="AB37">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AC37">
         <v>4.38</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK37">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="O38">
-        <v>4.95</v>
+        <v>4.41</v>
       </c>
       <c r="P38">
-        <v>5.3</v>
+        <v>5.08</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -7155,22 +7155,22 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O42">
         <v>3</v>
       </c>
       <c r="P42">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q42">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="R42">
         <v>1.91</v>
       </c>
       <c r="S42">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T42">
         <v>2.5</v>
@@ -7179,10 +7179,10 @@
         <v>3.4</v>
       </c>
       <c r="V42">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W42">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X42">
         <v>1.04</v>
@@ -7203,16 +7203,16 @@
         <v>4.55</v>
       </c>
       <c r="AD42">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE42">
         <v>1.01</v>
       </c>
       <c r="AF42">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AG42">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7321,13 +7321,13 @@
         <v>2.1</v>
       </c>
       <c r="O43">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P43">
         <v>3.27</v>
       </c>
       <c r="Q43">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="R43">
         <v>1.92</v>
@@ -7363,7 +7363,7 @@
         <v>1.62</v>
       </c>
       <c r="AC43">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="AD43">
         <v>1.18</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="O44">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P44">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="Q44">
         <v>2.8</v>
@@ -7505,7 +7505,7 @@
         <v>3.13</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W44">
         <v>1.03</v>
@@ -7554,7 +7554,7 @@
         <v>1.33</v>
       </c>
       <c r="AK44">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7816,28 +7816,28 @@
         <v>2.6</v>
       </c>
       <c r="Q46">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="R46">
         <v>1.95</v>
       </c>
       <c r="S46">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="T46">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="U46">
         <v>3.36</v>
       </c>
       <c r="V46">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X46">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y46">
         <v>1.5</v>
@@ -7846,25 +7846,25 @@
         <v>2.5</v>
       </c>
       <c r="AA46">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AB46">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AC46">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AD46">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE46">
         <v>1.02</v>
       </c>
       <c r="AF46">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AG46">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK46">
         <v>1.5</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O47">
         <v>3.18</v>
       </c>
       <c r="P47">
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -7985,46 +7985,46 @@
         <v>2.15</v>
       </c>
       <c r="S47">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T47">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="U47">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V47">
         <v>1.43</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y47">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z47">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="AA47">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AB47">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC47">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="AD47">
         <v>1.3</v>
       </c>
       <c r="AE47">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF47">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG47">
         <v>1.95</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK47">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,58 +8133,58 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="O48">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P48">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q48">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="R48">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="S48">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T48">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U48">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="V48">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W48">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z48">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA48">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB48">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AC48">
         <v>3.2</v>
       </c>
       <c r="AD48">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE48">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF48">
         <v>1.91</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK48">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O49">
         <v>3.1</v>
       </c>
       <c r="P49">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q49">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="R49">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U49">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="V49">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W49">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z49">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA49">
         <v>1.92</v>
       </c>
       <c r="AB49">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC49">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="AD49">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AG49">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8462,7 +8462,7 @@
         <v>3.5</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
         <v>1.9</v>
@@ -8471,7 +8471,7 @@
         <v>4.3</v>
       </c>
       <c r="R50">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
         <v>1.25</v>
@@ -8480,7 +8480,7 @@
         <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="V50">
         <v>1.53</v>
@@ -8516,7 +8516,7 @@
         <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
         <v>1.28</v>
@@ -9129,10 +9129,10 @@
         <v>1.44</v>
       </c>
       <c r="T54">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="U54">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="V54">
         <v>1.28</v>
@@ -9141,13 +9141,13 @@
         <v>1.02</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
         <v>1.36</v>
       </c>
       <c r="Z54">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AA54">
         <v>2.19</v>
@@ -9156,10 +9156,10 @@
         <v>1.59</v>
       </c>
       <c r="AC54">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AD54">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE54">
         <v>1.03</v>
@@ -9184,7 +9184,7 @@
         <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9440,7 +9440,7 @@
         <v>2</v>
       </c>
       <c r="O56">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P56">
         <v>3.1</v>
@@ -9458,16 +9458,16 @@
         <v>2.5</v>
       </c>
       <c r="U56">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="V56">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W56">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X56">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y56">
         <v>1.42</v>
@@ -9485,7 +9485,7 @@
         <v>4</v>
       </c>
       <c r="AD56">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE56">
         <v>1.01</v>
@@ -9510,7 +9510,7 @@
         <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9766,22 +9766,22 @@
         <v>1.73</v>
       </c>
       <c r="O58">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P58">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
       </c>
       <c r="R58">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S58">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T58">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="U58">
         <v>3.28</v>
@@ -9790,37 +9790,37 @@
         <v>1.29</v>
       </c>
       <c r="W58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X58">
         <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z58">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AA58">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AB58">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AC58">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD58">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF58">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AG58">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK58">
         <v>2</v>
@@ -9926,16 +9926,16 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="O59">
         <v>3</v>
       </c>
       <c r="P59">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="Q59">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="R59">
         <v>1.91</v>
@@ -9971,7 +9971,7 @@
         <v>1.64</v>
       </c>
       <c r="AC59">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AD59">
         <v>1.17</v>
@@ -9980,7 +9980,7 @@
         <v>1.06</v>
       </c>
       <c r="AF59">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG59">
         <v>1.8</v>
@@ -10098,7 +10098,7 @@
         <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="R60">
         <v>1.85</v>
@@ -10119,13 +10119,13 @@
         <v>1.02</v>
       </c>
       <c r="X60">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y60">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Z60">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="AA60">
         <v>2.45</v>
@@ -10134,7 +10134,7 @@
         <v>1.5</v>
       </c>
       <c r="AC60">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AD60">
         <v>1.13</v>
@@ -10143,10 +10143,10 @@
         <v>1.05</v>
       </c>
       <c r="AF60">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AG60">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10261,10 +10261,10 @@
         <v>2.33</v>
       </c>
       <c r="Q61">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R61">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="S61">
         <v>1.52</v>
@@ -10279,7 +10279,7 @@
         <v>1.3</v>
       </c>
       <c r="W61">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X61">
         <v>1.06</v>
@@ -10325,7 +10325,7 @@
         <v>1.36</v>
       </c>
       <c r="AK61">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O62">
         <v>3.25</v>
@@ -10439,7 +10439,7 @@
         <v>2.98</v>
       </c>
       <c r="V62">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W62">
         <v>1.04</v>
@@ -10457,7 +10457,7 @@
         <v>2</v>
       </c>
       <c r="AB62">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC62">
         <v>3.6</v>
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="O65">
+        <v>3.35</v>
+      </c>
+      <c r="P65">
         <v>3.3</v>
       </c>
-      <c r="P65">
-        <v>3.15</v>
-      </c>
       <c r="Q65">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="R65">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="S65">
         <v>1.35</v>
@@ -10946,38 +10946,38 @@
         <v>1.81</v>
       </c>
       <c r="AB65">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC65">
         <v>2.85</v>
       </c>
       <c r="AD65">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE65">
         <v>1.08</v>
       </c>
       <c r="AF65">
+        <v>1.65</v>
+      </c>
+      <c r="AG65">
+        <v>2.07</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>1.25</v>
+      </c>
+      <c r="AK65">
         <v>1.67</v>
-      </c>
-      <c r="AG65">
-        <v>2.05</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.24</v>
-      </c>
-      <c r="AK65">
-        <v>1.65</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11070,28 +11070,28 @@
         <v>1.71</v>
       </c>
       <c r="O66">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="P66">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q66">
         <v>2.29</v>
       </c>
       <c r="R66">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S66">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T66">
         <v>3.2</v>
       </c>
       <c r="U66">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="V66">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W66">
         <v>1.1</v>
@@ -11100,31 +11100,31 @@
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z66">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA66">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB66">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AC66">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AD66">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE66">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF66">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG66">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,34 +11230,34 @@
         </is>
       </c>
       <c r="N67">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="O67">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="P67">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="Q67">
         <v>3.7</v>
       </c>
       <c r="R67">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S67">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T67">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U67">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="V67">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W67">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
         <v>1.02</v>
@@ -11269,22 +11269,22 @@
         <v>3.1</v>
       </c>
       <c r="AA67">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AB67">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC67">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
       <c r="AD67">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE67">
         <v>1.02</v>
       </c>
       <c r="AF67">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG67">
         <v>1.83</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="O29">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>2.78</v>
+        <v>3.55</v>
       </c>
       <c r="Q29">
         <v>2.51</v>
@@ -5054,7 +5054,7 @@
         <v>1.33</v>
       </c>
       <c r="T29">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
         <v>2.45</v>
@@ -5066,13 +5066,13 @@
         <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z29">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA29">
         <v>1.73</v>
@@ -5084,10 +5084,10 @@
         <v>2.69</v>
       </c>
       <c r="AD29">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE29">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF29">
         <v>1.61</v>
@@ -5214,16 +5214,16 @@
         <v>2.18</v>
       </c>
       <c r="S30">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T30">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U30">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="V30">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W30">
         <v>1.09</v>
@@ -5241,13 +5241,13 @@
         <v>1.67</v>
       </c>
       <c r="AB30">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC30">
         <v>2.62</v>
       </c>
       <c r="AD30">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE30">
         <v>1.14</v>
@@ -5272,7 +5272,7 @@
         <v>1.34</v>
       </c>
       <c r="AK30">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,43 +5362,43 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="O31">
         <v>3.52</v>
       </c>
       <c r="P31">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
       </c>
       <c r="R31">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="S31">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U31">
         <v>2.15</v>
       </c>
       <c r="V31">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
         <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA31">
         <v>1.51</v>
@@ -5407,19 +5407,19 @@
         <v>2.27</v>
       </c>
       <c r="AC31">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AD31">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE31">
         <v>1.18</v>
       </c>
       <c r="AF31">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG31">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="O35">
         <v>4.15</v>
       </c>
       <c r="P35">
-        <v>4.35</v>
+        <v>4.9</v>
       </c>
       <c r="Q35">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="R35">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="S35">
         <v>1.26</v>
@@ -6035,22 +6035,22 @@
         <v>3.6</v>
       </c>
       <c r="U35">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V35">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="W35">
         <v>1.12</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="AA35">
         <v>1.5</v>
@@ -6059,10 +6059,10 @@
         <v>2.28</v>
       </c>
       <c r="AC35">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AD35">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AE35">
         <v>1.22</v>
@@ -6087,7 +6087,7 @@
         <v>1.15</v>
       </c>
       <c r="AK35">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>3.4</v>
       </c>
       <c r="R51">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="S51">
         <v>1.67</v>
@@ -8676,10 +8676,10 @@
         <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AG51">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -9609,10 +9609,10 @@
         <v>2.3</v>
       </c>
       <c r="Q57">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="R57">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="S57">
         <v>1.15</v>
@@ -9639,25 +9639,25 @@
         <v>6.85</v>
       </c>
       <c r="AA57">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AB57">
         <v>3.3</v>
       </c>
       <c r="AC57">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AD57">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AE57">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AF57">
         <v>1.28</v>
       </c>
       <c r="AG57">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AK57">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>3.44</v>
       </c>
       <c r="Q63">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="R63">
         <v>2.1</v>
       </c>
       <c r="S63">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T63">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="U63">
         <v>2.89</v>
       </c>
       <c r="V63">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W63">
         <v>1.07</v>
       </c>
       <c r="X63">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z63">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AA63">
         <v>2.05</v>
       </c>
       <c r="AB63">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC63">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="AD63">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE63">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF63">
         <v>1.74</v>
       </c>
       <c r="AG63">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10765,10 +10765,10 @@
         <v>3.9</v>
       </c>
       <c r="V64">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W64">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X64">
         <v>1.13</v>
@@ -10777,7 +10777,7 @@
         <v>1.62</v>
       </c>
       <c r="Z64">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AA64">
         <v>2.89</v>
@@ -10789,10 +10789,10 @@
         <v>6.5</v>
       </c>
       <c r="AD64">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE64">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF64">
         <v>2.6</v>
@@ -10910,7 +10910,7 @@
         <v>3.35</v>
       </c>
       <c r="P65">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q65">
         <v>2.64</v>
@@ -10952,7 +10952,7 @@
         <v>2.85</v>
       </c>
       <c r="AD65">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE65">
         <v>1.08</v>
@@ -10961,7 +10961,7 @@
         <v>1.65</v>
       </c>
       <c r="AG65">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK65">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11100,16 +11100,16 @@
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z66">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AA66">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB66">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AC66">
         <v>3</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="O67">
         <v>3.1</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -967,22 +967,22 @@
         <v>3.4</v>
       </c>
       <c r="P4">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="Q4">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="R4">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
         <v>2.66</v>
       </c>
       <c r="U4">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="V4">
         <v>1.33</v>
@@ -1000,10 +1000,10 @@
         <v>2.97</v>
       </c>
       <c r="AA4">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AB4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC4">
         <v>3.5</v>
@@ -1034,7 +1034,7 @@
         <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="O9">
         <v>3.55</v>
       </c>
       <c r="P9">
-        <v>5.55</v>
+        <v>4.45</v>
       </c>
       <c r="Q9">
         <v>2.19</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
+        <v>3.15</v>
+      </c>
+      <c r="O19">
         <v>3.05</v>
       </c>
-      <c r="O19">
-        <v>3</v>
-      </c>
       <c r="P19">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q19">
-        <v>3.78</v>
+        <v>3.98</v>
       </c>
       <c r="R19">
         <v>1.93</v>
@@ -3424,10 +3424,10 @@
         <v>1.48</v>
       </c>
       <c r="T19">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="U19">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="V19">
         <v>1.3</v>
@@ -3451,7 +3451,7 @@
         <v>1.65</v>
       </c>
       <c r="AC19">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="AD19">
         <v>1.22</v>
@@ -3460,10 +3460,10 @@
         <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG19">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="O26">
-        <v>5.05</v>
+        <v>4.75</v>
       </c>
       <c r="P26">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="Q26">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="R26">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="U26">
-        <v>2.71</v>
+        <v>2.79</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z26">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB26">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AC26">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AD26">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
         <v>1.12</v>
       </c>
       <c r="AF26">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AG26">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AK26">
-        <v>3.72</v>
+        <v>3.3</v>
       </c>
       <c r="AL26">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -970,7 +970,7 @@
         <v>1.83</v>
       </c>
       <c r="Q4">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="R4">
         <v>2.07</v>
@@ -979,13 +979,13 @@
         <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="U4">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W4">
         <v>1.03</v>
@@ -1000,16 +1000,16 @@
         <v>2.97</v>
       </c>
       <c r="AA4">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AB4">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC4">
         <v>3.5</v>
       </c>
       <c r="AD4">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
         <v>1.04</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
         <v>1.23</v>
@@ -1133,7 +1133,7 @@
         <v>4.4</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="R5">
         <v>2.14</v>
@@ -1148,7 +1148,7 @@
         <v>2.88</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
         <v>1.06</v>
@@ -1163,16 +1163,16 @@
         <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB5">
         <v>1.8</v>
       </c>
       <c r="AC5">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD5">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE5">
         <v>1.07</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
         <v>2.03</v>
@@ -1296,7 +1296,7 @@
         <v>2.87</v>
       </c>
       <c r="Q6">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R6">
         <v>1.95</v>
@@ -1344,7 +1344,7 @@
         <v>1.94</v>
       </c>
       <c r="AG6">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="O9">
         <v>3.55</v>
       </c>
       <c r="P9">
-        <v>4.45</v>
+        <v>5.45</v>
       </c>
       <c r="Q9">
         <v>2.19</v>
@@ -1815,7 +1815,7 @@
         <v>3.05</v>
       </c>
       <c r="AA9">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB9">
         <v>1.72</v>
@@ -1824,7 +1824,7 @@
         <v>3.7</v>
       </c>
       <c r="AD9">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
         <v>1.03</v>
@@ -2926,7 +2926,7 @@
         <v>3.04</v>
       </c>
       <c r="Q16">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="R16">
         <v>1.67</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O19">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q19">
         <v>3.98</v>
@@ -3439,7 +3439,7 @@
         <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z19">
         <v>2.7</v>
@@ -3448,7 +3448,7 @@
         <v>2.27</v>
       </c>
       <c r="AB19">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC19">
         <v>3.84</v>
@@ -3738,7 +3738,7 @@
         <v>2.99</v>
       </c>
       <c r="P21">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>2.78</v>
       </c>
       <c r="R25">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="S25">
         <v>1.48</v>
@@ -4414,7 +4414,7 @@
         <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
         <v>1.4</v>
@@ -4562,7 +4562,7 @@
         <v>2.29</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T26">
         <v>2.81</v>
@@ -4586,10 +4586,10 @@
         <v>3.34</v>
       </c>
       <c r="AA26">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB26">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AC26">
         <v>2.97</v>
@@ -5362,61 +5362,61 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="O31">
         <v>3.52</v>
       </c>
       <c r="P31">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
       </c>
       <c r="R31">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T31">
         <v>3.6</v>
       </c>
       <c r="U31">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="V31">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z31">
         <v>4.8</v>
       </c>
       <c r="AA31">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AB31">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AC31">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AD31">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE31">
         <v>1.18</v>
       </c>
       <c r="AF31">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG31">
         <v>2.5</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AK31">
         <v>1.5</v>
@@ -6343,10 +6343,10 @@
         <v>2.06</v>
       </c>
       <c r="O37">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P37">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -6361,10 +6361,10 @@
         <v>2.43</v>
       </c>
       <c r="U37">
-        <v>3.38</v>
+        <v>3.27</v>
       </c>
       <c r="V37">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W37">
         <v>1.03</v>
@@ -6388,7 +6388,7 @@
         <v>4.38</v>
       </c>
       <c r="AD37">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AE37">
         <v>1.02</v>
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O40">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="P40">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q40">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="R40">
         <v>2.48</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T40">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="U40">
         <v>2.03</v>
@@ -6856,13 +6856,13 @@
         <v>1.72</v>
       </c>
       <c r="W40">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z40">
         <v>5.75</v>
@@ -6874,10 +6874,10 @@
         <v>2.86</v>
       </c>
       <c r="AC40">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AD40">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE40">
         <v>1.28</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK40">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,22 +6992,22 @@
         </is>
       </c>
       <c r="N41">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="O41">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P41">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q41">
         <v>4.6</v>
       </c>
       <c r="R41">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="S41">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T41">
         <v>3.68</v>
@@ -7016,19 +7016,19 @@
         <v>2.11</v>
       </c>
       <c r="V41">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W41">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X41">
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z41">
-        <v>5.52</v>
+        <v>5.35</v>
       </c>
       <c r="AA41">
         <v>1.4</v>
@@ -7037,19 +7037,19 @@
         <v>2.63</v>
       </c>
       <c r="AC41">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AD41">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE41">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AF41">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG41">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O47">
         <v>3.18</v>
       </c>
       <c r="P47">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -7988,16 +7988,16 @@
         <v>1.36</v>
       </c>
       <c r="T47">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U47">
-        <v>2.56</v>
+        <v>2.81</v>
       </c>
       <c r="V47">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
         <v>1</v>
@@ -8462,7 +8462,7 @@
         <v>3.5</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P50">
         <v>1.9</v>
@@ -8477,7 +8477,7 @@
         <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
         <v>2.48</v>
@@ -8486,13 +8486,13 @@
         <v>1.53</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X50">
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z50">
         <v>4.4</v>
@@ -8513,10 +8513,10 @@
         <v>1.18</v>
       </c>
       <c r="AF50">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG50">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK50">
         <v>1.28</v>
@@ -8797,13 +8797,13 @@
         <v>1.83</v>
       </c>
       <c r="R52">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S52">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T52">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="U52">
         <v>2.63</v>
@@ -8812,7 +8812,7 @@
         <v>1.39</v>
       </c>
       <c r="W52">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X52">
         <v>1</v>
@@ -8824,25 +8824,25 @@
         <v>3.34</v>
       </c>
       <c r="AA52">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB52">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC52">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD52">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE52">
         <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AG52">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.02</v>
       </c>
       <c r="AK52">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,55 +8957,55 @@
         <v>0</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,55 +9120,55 @@
         <v>2.37</v>
       </c>
       <c r="Q54">
-        <v>3.68</v>
+        <v>3.73</v>
       </c>
       <c r="R54">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S54">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T54">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U54">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="V54">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W54">
         <v>1.02</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z54">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AA54">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AB54">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC54">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="AD54">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE54">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF54">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AG54">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK54">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,10 +9437,10 @@
         </is>
       </c>
       <c r="N56">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O56">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P56">
         <v>3.1</v>
@@ -9452,7 +9452,7 @@
         <v>1.94</v>
       </c>
       <c r="S56">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T56">
         <v>2.5</v>
@@ -9461,22 +9461,22 @@
         <v>3.25</v>
       </c>
       <c r="V56">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X56">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
         <v>1.42</v>
       </c>
       <c r="Z56">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA56">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AB56">
         <v>1.61</v>
@@ -9491,10 +9491,10 @@
         <v>1.01</v>
       </c>
       <c r="AF56">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG56">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL56">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -967,7 +967,7 @@
         <v>3.4</v>
       </c>
       <c r="P4">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="Q4">
         <v>4.65</v>
@@ -979,7 +979,7 @@
         <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="U4">
         <v>2.95</v>
@@ -1009,7 +1009,7 @@
         <v>3.5</v>
       </c>
       <c r="AD4">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE4">
         <v>1.04</v>
@@ -1133,46 +1133,46 @@
         <v>4.4</v>
       </c>
       <c r="Q5">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S5">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T5">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
         <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z5">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA5">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB5">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC5">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AD5">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
         <v>1.07</v>
@@ -1181,7 +1181,7 @@
         <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.2</v>
       </c>
       <c r="AK5">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1785,22 +1785,22 @@
         <v>5.45</v>
       </c>
       <c r="Q9">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="R9">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S9">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="U9">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
         <v>1.02</v>
@@ -1809,31 +1809,31 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA9">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AB9">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC9">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE9">
         <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AG9">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,22 +1939,22 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="O10">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P10">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="Q10">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R10">
         <v>2.39</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
         <v>2.99</v>
@@ -1963,7 +1963,7 @@
         <v>2.4</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W10">
         <v>1.06</v>
@@ -1978,19 +1978,19 @@
         <v>3.7</v>
       </c>
       <c r="AA10">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB10">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC10">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AD10">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
         <v>1.75</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O11">
         <v>4</v>
       </c>
       <c r="P11">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AB11">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -3246,31 +3246,31 @@
         <v>3.4</v>
       </c>
       <c r="O18">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q18">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
       <c r="R18">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T18">
         <v>2.59</v>
       </c>
       <c r="U18">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
         <v>1.04</v>
@@ -3288,7 +3288,7 @@
         <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AD18">
         <v>1.25</v>
@@ -3300,7 +3300,7 @@
         <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,28 +3406,28 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="O19">
         <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="Q19">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="R19">
         <v>1.93</v>
       </c>
       <c r="S19">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T19">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="U19">
-        <v>3.29</v>
+        <v>3.16</v>
       </c>
       <c r="V19">
         <v>1.3</v>
@@ -3448,22 +3448,22 @@
         <v>2.27</v>
       </c>
       <c r="AB19">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC19">
         <v>3.84</v>
       </c>
       <c r="AD19">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE19">
         <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG19">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>2.12</v>
       </c>
       <c r="O22">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P22">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
@@ -3913,7 +3913,7 @@
         <v>1.51</v>
       </c>
       <c r="T22">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U22">
         <v>3.28</v>
@@ -3925,7 +3925,7 @@
         <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y22">
         <v>1.38</v>
@@ -3937,22 +3937,22 @@
         <v>2.15</v>
       </c>
       <c r="AB22">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC22">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="AD22">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE22">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF22">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG22">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4227,19 +4227,19 @@
         <v>3.55</v>
       </c>
       <c r="P24">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q24">
         <v>4.2</v>
       </c>
       <c r="R24">
-        <v>2.46</v>
+        <v>2.31</v>
       </c>
       <c r="S24">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U24">
         <v>2.26</v>
@@ -4248,7 +4248,7 @@
         <v>1.56</v>
       </c>
       <c r="W24">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4257,19 +4257,19 @@
         <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="AA24">
         <v>1.57</v>
       </c>
       <c r="AB24">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC24">
         <v>2.45</v>
       </c>
       <c r="AD24">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AE24">
         <v>1.16</v>
@@ -4278,7 +4278,7 @@
         <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.95</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4550,10 +4550,10 @@
         <v>1.3</v>
       </c>
       <c r="O26">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="P26">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>1.78</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>3.3</v>
       </c>
       <c r="O28">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
         <v>2.15</v>
@@ -5036,37 +5036,37 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O29">
         <v>3.5</v>
       </c>
       <c r="P29">
-        <v>3.55</v>
+        <v>2.78</v>
       </c>
       <c r="Q29">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="R29">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="U29">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V29">
         <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
         <v>1.25</v>
@@ -5075,25 +5075,25 @@
         <v>4</v>
       </c>
       <c r="AA29">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB29">
         <v>2.05</v>
       </c>
       <c r="AC29">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AD29">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE29">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF29">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG29">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK29">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5226,7 +5226,7 @@
         <v>1.55</v>
       </c>
       <c r="W30">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
         <v>1</v>
@@ -5235,7 +5235,7 @@
         <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AA30">
         <v>1.67</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.63</v>
+        <v>2.34</v>
       </c>
       <c r="O31">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
         <v>2.45</v>
@@ -5386,10 +5386,10 @@
         <v>2.29</v>
       </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W31">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
         <v>1.12</v>
       </c>
       <c r="Z31">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="AA31">
         <v>1.57</v>
@@ -5407,10 +5407,10 @@
         <v>2.29</v>
       </c>
       <c r="AC31">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AD31">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE31">
         <v>1.18</v>
@@ -5528,31 +5528,31 @@
         <v>1.71</v>
       </c>
       <c r="O32">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q32">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="R32">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
         <v>2.41</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X32">
         <v>1.01</v>
@@ -5567,16 +5567,16 @@
         <v>1.75</v>
       </c>
       <c r="AB32">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AC32">
         <v>2.83</v>
       </c>
       <c r="AD32">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
         <v>1.7</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK32">
         <v>2</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="O34">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="P34">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Q34">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R34">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="S34">
         <v>1.25</v>
@@ -5884,13 +5884,13 @@
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA34">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB34">
         <v>2.48</v>
@@ -5902,7 +5902,7 @@
         <v>1.65</v>
       </c>
       <c r="AE34">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF34">
         <v>1.62</v>
@@ -6014,25 +6014,25 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="O35">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="P35">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R35">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S35">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T35">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U35">
         <v>2.27</v>
@@ -6050,7 +6050,7 @@
         <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>4.55</v>
+        <v>4.87</v>
       </c>
       <c r="AA35">
         <v>1.5</v>
@@ -6059,13 +6059,13 @@
         <v>2.28</v>
       </c>
       <c r="AC35">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AD35">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AE35">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF35">
         <v>1.6</v>
@@ -6183,19 +6183,19 @@
         <v>3.5</v>
       </c>
       <c r="P36">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="Q36">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S36">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T36">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="U36">
         <v>2.88</v>
@@ -6216,7 +6216,7 @@
         <v>3.24</v>
       </c>
       <c r="AA36">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB36">
         <v>1.8</v>
@@ -6250,7 +6250,7 @@
         <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6346,7 +6346,7 @@
         <v>3.1</v>
       </c>
       <c r="P37">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -6355,7 +6355,7 @@
         <v>1.97</v>
       </c>
       <c r="S37">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="T37">
         <v>2.43</v>
@@ -6376,7 +6376,7 @@
         <v>1.41</v>
       </c>
       <c r="Z37">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AA37">
         <v>2.43</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="O38">
         <v>4.41</v>
@@ -6844,7 +6844,7 @@
         <v>2.48</v>
       </c>
       <c r="S40">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
         <v>3.68</v>
@@ -6859,7 +6859,7 @@
         <v>1.18</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
         <v>1.08</v>
@@ -6877,7 +6877,7 @@
         <v>2</v>
       </c>
       <c r="AD40">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE40">
         <v>1.28</v>
@@ -7007,10 +7007,10 @@
         <v>2.6</v>
       </c>
       <c r="S41">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T41">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="U41">
         <v>2.11</v>
@@ -7025,25 +7025,25 @@
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z41">
-        <v>5.35</v>
+        <v>5.25</v>
       </c>
       <c r="AA41">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB41">
         <v>2.63</v>
       </c>
       <c r="AC41">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AD41">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE41">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF41">
         <v>1.48</v>
@@ -7155,28 +7155,28 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O42">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P42">
         <v>2.5</v>
       </c>
       <c r="Q42">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="R42">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S42">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T42">
         <v>2.5</v>
       </c>
       <c r="U42">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="V42">
         <v>1.29</v>
@@ -7185,13 +7185,13 @@
         <v>1.02</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y42">
         <v>1.47</v>
       </c>
       <c r="Z42">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AA42">
         <v>2.33</v>
@@ -7203,13 +7203,13 @@
         <v>4.55</v>
       </c>
       <c r="AD42">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE42">
         <v>1.01</v>
       </c>
       <c r="AF42">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG42">
         <v>1.7</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK42">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7321,25 +7321,25 @@
         <v>2.1</v>
       </c>
       <c r="O43">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P43">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="Q43">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="R43">
         <v>1.92</v>
       </c>
       <c r="S43">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T43">
         <v>2.47</v>
       </c>
       <c r="U43">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="V43">
         <v>1.28</v>
@@ -7484,13 +7484,13 @@
         <v>2.11</v>
       </c>
       <c r="O44">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P44">
         <v>2.98</v>
       </c>
       <c r="Q44">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="R44">
         <v>2</v>
@@ -7502,7 +7502,7 @@
         <v>2.65</v>
       </c>
       <c r="U44">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="V44">
         <v>1.33</v>
@@ -7538,7 +7538,7 @@
         <v>1.83</v>
       </c>
       <c r="AG44">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7816,25 +7816,25 @@
         <v>2.6</v>
       </c>
       <c r="Q46">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="R46">
         <v>1.95</v>
       </c>
       <c r="S46">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="T46">
         <v>2.4</v>
       </c>
       <c r="U46">
-        <v>3.36</v>
+        <v>3.6</v>
       </c>
       <c r="V46">
         <v>1.25</v>
       </c>
       <c r="W46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X46">
         <v>1.11</v>
@@ -7849,19 +7849,19 @@
         <v>2.45</v>
       </c>
       <c r="AB46">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AC46">
         <v>5</v>
       </c>
       <c r="AD46">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE46">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF46">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG46">
         <v>1.67</v>
@@ -7880,7 +7880,7 @@
         <v>1.4</v>
       </c>
       <c r="AK46">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="O47">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="P47">
-        <v>3.52</v>
+        <v>4.1</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -8021,7 +8021,7 @@
         <v>1.3</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
         <v>1.74</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O48">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="P48">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="Q48">
         <v>2.18</v>
@@ -8148,49 +8148,49 @@
         <v>2.08</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
         <v>2.9</v>
       </c>
       <c r="U48">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="V48">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W48">
         <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z48">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA48">
         <v>1.9</v>
       </c>
       <c r="AB48">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AC48">
         <v>3.2</v>
       </c>
       <c r="AD48">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE48">
         <v>1.1</v>
       </c>
       <c r="AF48">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG48">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>2.81</v>
       </c>
       <c r="R49">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S49">
         <v>1.38</v>
@@ -8317,10 +8317,10 @@
         <v>2.67</v>
       </c>
       <c r="U49">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V49">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W49">
         <v>1.03</v>
@@ -8335,10 +8335,10 @@
         <v>3.2</v>
       </c>
       <c r="AA49">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB49">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AC49">
         <v>3.28</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
         <v>1.56</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O50">
         <v>3.7</v>
@@ -8640,13 +8640,13 @@
         <v>1.67</v>
       </c>
       <c r="T51">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="U51">
         <v>4</v>
       </c>
       <c r="V51">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W51">
         <v>1.03</v>
@@ -8658,13 +8658,13 @@
         <v>1.62</v>
       </c>
       <c r="Z51">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AA51">
         <v>2.83</v>
       </c>
       <c r="AB51">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AC51">
         <v>6.43</v>
@@ -9446,7 +9446,7 @@
         <v>3.1</v>
       </c>
       <c r="Q56">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="R56">
         <v>1.94</v>
@@ -9479,7 +9479,7 @@
         <v>2.25</v>
       </c>
       <c r="AB56">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC56">
         <v>4</v>
@@ -9491,10 +9491,10 @@
         <v>1.01</v>
       </c>
       <c r="AF56">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AG56">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9609,10 +9609,10 @@
         <v>2.3</v>
       </c>
       <c r="Q57">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="R57">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="S57">
         <v>1.15</v>
@@ -9636,28 +9636,28 @@
         <v>1.04</v>
       </c>
       <c r="Z57">
-        <v>6.85</v>
+        <v>7.5</v>
       </c>
       <c r="AA57">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB57">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC57">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AD57">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AE57">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AF57">
         <v>1.28</v>
       </c>
       <c r="AG57">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AK57">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,77 +9763,77 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O58">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P58">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
       </c>
       <c r="R58">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="S58">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T58">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="U58">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="V58">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W58">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X58">
         <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="Z58">
         <v>2.8</v>
       </c>
       <c r="AA58">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AB58">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AC58">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD58">
+        <v>1.18</v>
+      </c>
+      <c r="AE58">
+        <v>1.06</v>
+      </c>
+      <c r="AF58">
+        <v>2.05</v>
+      </c>
+      <c r="AG58">
+        <v>1.7</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
         <v>1.17</v>
-      </c>
-      <c r="AE58">
-        <v>1.03</v>
-      </c>
-      <c r="AF58">
-        <v>2.15</v>
-      </c>
-      <c r="AG58">
-        <v>1.62</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.15</v>
       </c>
       <c r="AK58">
         <v>2</v>
@@ -9929,13 +9929,13 @@
         <v>2.77</v>
       </c>
       <c r="O59">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="P59">
         <v>2.28</v>
       </c>
       <c r="Q59">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="R59">
         <v>1.91</v>
@@ -9950,7 +9950,7 @@
         <v>3.25</v>
       </c>
       <c r="V59">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W59">
         <v>1.05</v>
@@ -9962,13 +9962,13 @@
         <v>1.36</v>
       </c>
       <c r="Z59">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="AA59">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AB59">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AC59">
         <v>4</v>
@@ -9980,7 +9980,7 @@
         <v>1.06</v>
       </c>
       <c r="AF59">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG59">
         <v>1.8</v>
@@ -10098,10 +10098,10 @@
         <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="R60">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="S60">
         <v>1.54</v>
@@ -10110,10 +10110,10 @@
         <v>2.49</v>
       </c>
       <c r="U60">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="V60">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W60">
         <v>1.02</v>
@@ -10122,7 +10122,7 @@
         <v>1.07</v>
       </c>
       <c r="Y60">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Z60">
         <v>2.57</v>
@@ -10131,13 +10131,13 @@
         <v>2.45</v>
       </c>
       <c r="AB60">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC60">
         <v>4.55</v>
       </c>
       <c r="AD60">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE60">
         <v>1.05</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AK60">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O61">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P61">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q61">
         <v>3.45</v>
       </c>
       <c r="R61">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="S61">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T61">
         <v>2.4</v>
       </c>
       <c r="U61">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="V61">
         <v>1.3</v>
       </c>
       <c r="W61">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X61">
         <v>1.06</v>
       </c>
       <c r="Y61">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Z61">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AA61">
         <v>2.4</v>
       </c>
       <c r="AB61">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AC61">
-        <v>4.75</v>
+        <v>4.35</v>
       </c>
       <c r="AD61">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE61">
         <v>1.05</v>
       </c>
       <c r="AF61">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG61">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AK61">
         <v>1.36</v>
@@ -10415,28 +10415,28 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O62">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P62">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="Q62">
+        <v>2.24</v>
+      </c>
+      <c r="R62">
         <v>2.27</v>
       </c>
-      <c r="R62">
-        <v>2.26</v>
-      </c>
       <c r="S62">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T62">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="U62">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="V62">
         <v>1.36</v>
@@ -10448,7 +10448,7 @@
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z62">
         <v>3.08</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK62">
         <v>2.1</v>
@@ -10747,28 +10747,28 @@
         <v>3.2</v>
       </c>
       <c r="P64">
-        <v>5.83</v>
+        <v>6.15</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
       </c>
       <c r="R64">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="S64">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="T64">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="U64">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="V64">
         <v>1.22</v>
       </c>
       <c r="W64">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X64">
         <v>1.13</v>
@@ -10777,28 +10777,28 @@
         <v>1.62</v>
       </c>
       <c r="Z64">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AA64">
-        <v>2.89</v>
+        <v>2.35</v>
       </c>
       <c r="AB64">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC64">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AD64">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AE64">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AG64">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>3.35</v>
       </c>
       <c r="P65">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q65">
         <v>2.64</v>
@@ -10937,10 +10937,10 @@
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="AA65">
         <v>1.81</v>
@@ -10952,13 +10952,13 @@
         <v>2.85</v>
       </c>
       <c r="AD65">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE65">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF65">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG65">
         <v>2.05</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="O66">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P66">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="Q66">
         <v>2.29</v>
@@ -11091,7 +11091,7 @@
         <v>2.6</v>
       </c>
       <c r="V66">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W66">
         <v>1.1</v>
@@ -11100,19 +11100,19 @@
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z66">
         <v>3.7</v>
       </c>
       <c r="AA66">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB66">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC66">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD66">
         <v>1.33</v>
@@ -11121,10 +11121,10 @@
         <v>1.1</v>
       </c>
       <c r="AF66">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG66">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11236,13 +11236,13 @@
         <v>3.1</v>
       </c>
       <c r="P67">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q67">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="R67">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
         <v>1.42</v>
@@ -11257,7 +11257,7 @@
         <v>1.3</v>
       </c>
       <c r="W67">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X67">
         <v>1.02</v>
@@ -11278,10 +11278,10 @@
         <v>3.82</v>
       </c>
       <c r="AD67">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE67">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF67">
         <v>1.83</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P4">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="Q4">
-        <v>4.65</v>
+        <v>4.71</v>
       </c>
       <c r="R4">
         <v>2.07</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="U4">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="V4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W4">
         <v>1.03</v>
@@ -997,19 +997,19 @@
         <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
       <c r="AA4">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB4">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC4">
         <v>3.5</v>
       </c>
       <c r="AD4">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
         <v>1.04</v>
@@ -1034,7 +1034,7 @@
         <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="O5">
         <v>3.55</v>
       </c>
       <c r="P5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q5">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R5">
         <v>2.2</v>
       </c>
       <c r="S5">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U5">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
         <v>1.06</v>
@@ -1157,28 +1157,28 @@
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA5">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB5">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC5">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE5">
         <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG5">
         <v>1.8</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="O6">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
         <v>2.87</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK6">
         <v>1.5</v>
@@ -1776,28 +1776,28 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="O9">
         <v>3.55</v>
       </c>
       <c r="P9">
-        <v>5.45</v>
+        <v>4.45</v>
       </c>
       <c r="Q9">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="R9">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T9">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="U9">
-        <v>3.11</v>
+        <v>3.18</v>
       </c>
       <c r="V9">
         <v>1.34</v>
@@ -1809,31 +1809,31 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="AA9">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB9">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="AD9">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE9">
         <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AG9">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,61 +1939,61 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="O10">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P10">
         <v>4.6</v>
       </c>
       <c r="Q10">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="S10">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="U10">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z10">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AA10">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AB10">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC10">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD10">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
         <v>1.95</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK10">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="O16">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="P16">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="Q16">
         <v>3.56</v>
@@ -2968,13 +2968,13 @@
         <v>1.02</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF16">
         <v>2.67</v>
       </c>
       <c r="AG16">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O18">
         <v>3.2</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q18">
-        <v>4.49</v>
+        <v>4.33</v>
       </c>
       <c r="R18">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="S18">
         <v>1.4</v>
@@ -3264,7 +3264,7 @@
         <v>2.59</v>
       </c>
       <c r="U18">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="V18">
         <v>1.36</v>
@@ -3279,7 +3279,7 @@
         <v>1.3</v>
       </c>
       <c r="Z18">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA18">
         <v>2</v>
@@ -3300,7 +3300,7 @@
         <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AK18">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,31 +3406,31 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O19">
         <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="Q19">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="R19">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="S19">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T19">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="U19">
-        <v>3.16</v>
+        <v>3.31</v>
       </c>
       <c r="V19">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W19">
         <v>1.02</v>
@@ -3439,19 +3439,19 @@
         <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z19">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AA19">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AB19">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC19">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="AD19">
         <v>1.18</v>
@@ -3460,10 +3460,10 @@
         <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG19">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="O21">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="P21">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>3.1</v>
       </c>
       <c r="P22">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
@@ -3910,10 +3910,10 @@
         <v>1.98</v>
       </c>
       <c r="S22">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="U22">
         <v>3.28</v>
@@ -3925,7 +3925,7 @@
         <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y22">
         <v>1.38</v>
@@ -3937,22 +3937,22 @@
         <v>2.15</v>
       </c>
       <c r="AB22">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AC22">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="AD22">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE22">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF22">
         <v>1.92</v>
       </c>
       <c r="AG22">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4230,22 +4230,22 @@
         <v>1.8</v>
       </c>
       <c r="Q24">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="R24">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="S24">
         <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="V24">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W24">
         <v>1.11</v>
@@ -4257,28 +4257,28 @@
         <v>1.14</v>
       </c>
       <c r="Z24">
-        <v>4.75</v>
+        <v>4.66</v>
       </c>
       <c r="AA24">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB24">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC24">
         <v>2.45</v>
       </c>
       <c r="AD24">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF24">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AG24">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.95</v>
       </c>
       <c r="AK24">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
         <v>1.67</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O26">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="P26">
-        <v>10</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q26">
         <v>1.78</v>
@@ -4568,7 +4568,7 @@
         <v>2.81</v>
       </c>
       <c r="U26">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="V26">
         <v>1.41</v>
@@ -4586,25 +4586,25 @@
         <v>3.34</v>
       </c>
       <c r="AA26">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AB26">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC26">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="AD26">
         <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
         <v>2.33</v>
       </c>
       <c r="AG26">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="P28">
         <v>2.15</v>
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="P29">
         <v>2.78</v>
       </c>
       <c r="Q29">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="R29">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T29">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="U29">
         <v>2.5</v>
@@ -5066,7 +5066,7 @@
         <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
         <v>1.25</v>
@@ -5075,22 +5075,22 @@
         <v>4</v>
       </c>
       <c r="AA29">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB29">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC29">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD29">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE29">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF29">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG29">
         <v>2.05</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK29">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="P30">
         <v>2.5</v>
@@ -5220,13 +5220,13 @@
         <v>3.05</v>
       </c>
       <c r="U30">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="V30">
         <v>1.55</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X30">
         <v>1</v>
@@ -5238,13 +5238,13 @@
         <v>4</v>
       </c>
       <c r="AA30">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB30">
         <v>2.15</v>
       </c>
       <c r="AC30">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AD30">
         <v>1.41</v>
@@ -5253,10 +5253,10 @@
         <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="O31">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P31">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
@@ -5377,19 +5377,19 @@
         <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U31">
         <v>2.29</v>
       </c>
       <c r="V31">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W31">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5398,7 +5398,7 @@
         <v>1.12</v>
       </c>
       <c r="Z31">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AA31">
         <v>1.57</v>
@@ -5416,7 +5416,7 @@
         <v>1.18</v>
       </c>
       <c r="AF31">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG31">
         <v>2.5</v>
@@ -5525,16 +5525,16 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P32">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q32">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="R32">
         <v>2.3</v>
@@ -5570,7 +5570,7 @@
         <v>2.04</v>
       </c>
       <c r="AC32">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AD32">
         <v>1.33</v>
@@ -5851,49 +5851,49 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="O34">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="P34">
-        <v>6.9</v>
+        <v>5.6</v>
       </c>
       <c r="Q34">
         <v>1.85</v>
       </c>
       <c r="R34">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
         <v>3.64</v>
       </c>
       <c r="U34">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V34">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W34">
         <v>1.14</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>5.1</v>
+        <v>5.75</v>
       </c>
       <c r="AA34">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB34">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="AC34">
         <v>2.19</v>
@@ -6023,16 +6023,16 @@
         <v>5</v>
       </c>
       <c r="Q35">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R35">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S35">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T35">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
         <v>2.27</v>
@@ -6050,7 +6050,7 @@
         <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>4.87</v>
+        <v>5</v>
       </c>
       <c r="AA35">
         <v>1.5</v>
@@ -6059,16 +6059,16 @@
         <v>2.28</v>
       </c>
       <c r="AC35">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AD35">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE35">
         <v>1.24</v>
       </c>
       <c r="AF35">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG35">
         <v>2.2</v>
@@ -6186,16 +6186,16 @@
         <v>4.2</v>
       </c>
       <c r="Q36">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="R36">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="S36">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T36">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="U36">
         <v>2.88</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="O37">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="P37">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="Q37">
         <v>2.75</v>
@@ -6355,16 +6355,16 @@
         <v>1.97</v>
       </c>
       <c r="S37">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="T37">
         <v>2.43</v>
       </c>
       <c r="U37">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="V37">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W37">
         <v>1.03</v>
@@ -6376,19 +6376,19 @@
         <v>1.41</v>
       </c>
       <c r="Z37">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AA37">
         <v>2.43</v>
       </c>
       <c r="AB37">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AC37">
-        <v>4.38</v>
+        <v>4.43</v>
       </c>
       <c r="AD37">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE37">
         <v>1.02</v>
@@ -6397,7 +6397,7 @@
         <v>2.02</v>
       </c>
       <c r="AG37">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AK37">
         <v>1.79</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O38">
-        <v>4.41</v>
+        <v>4.6</v>
       </c>
       <c r="P38">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O39">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P39">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="Q39">
         <v>2.6</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.65</v>
+        <v>4.75</v>
       </c>
       <c r="O40">
         <v>4.2</v>
       </c>
       <c r="P40">
-        <v>4.33</v>
+        <v>1.53</v>
       </c>
       <c r="Q40">
-        <v>2.05</v>
+        <v>4.6</v>
       </c>
       <c r="R40">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="S40">
+        <v>1.2</v>
+      </c>
+      <c r="T40">
+        <v>4</v>
+      </c>
+      <c r="U40">
+        <v>2.11</v>
+      </c>
+      <c r="V40">
+        <v>1.67</v>
+      </c>
+      <c r="W40">
+        <v>1.14</v>
+      </c>
+      <c r="X40">
+        <v>1.02</v>
+      </c>
+      <c r="Y40">
+        <v>1.14</v>
+      </c>
+      <c r="Z40">
+        <v>5.25</v>
+      </c>
+      <c r="AA40">
+        <v>1.41</v>
+      </c>
+      <c r="AB40">
+        <v>2.63</v>
+      </c>
+      <c r="AC40">
+        <v>2.11</v>
+      </c>
+      <c r="AD40">
+        <v>1.67</v>
+      </c>
+      <c r="AE40">
+        <v>1.25</v>
+      </c>
+      <c r="AF40">
+        <v>1.48</v>
+      </c>
+      <c r="AG40">
+        <v>2.45</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.22</v>
       </c>
-      <c r="T40">
-        <v>3.68</v>
-      </c>
-      <c r="U40">
-        <v>2.03</v>
-      </c>
-      <c r="V40">
-        <v>1.72</v>
-      </c>
-      <c r="W40">
-        <v>1.18</v>
-      </c>
-      <c r="X40">
-        <v>1.01</v>
-      </c>
-      <c r="Y40">
-        <v>1.08</v>
-      </c>
-      <c r="Z40">
-        <v>5.75</v>
-      </c>
-      <c r="AA40">
-        <v>1.39</v>
-      </c>
-      <c r="AB40">
-        <v>2.86</v>
-      </c>
-      <c r="AC40">
-        <v>2</v>
-      </c>
-      <c r="AD40">
-        <v>1.77</v>
-      </c>
-      <c r="AE40">
-        <v>1.28</v>
-      </c>
-      <c r="AF40">
-        <v>1.43</v>
-      </c>
-      <c r="AG40">
-        <v>2.5</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
+      <c r="AK40">
         <v>1.17</v>
-      </c>
-      <c r="AK40">
-        <v>2.25</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>4.75</v>
+        <v>1.6</v>
       </c>
       <c r="O41">
+        <v>4</v>
+      </c>
+      <c r="P41">
         <v>4.2</v>
       </c>
-      <c r="P41">
-        <v>1.53</v>
-      </c>
       <c r="Q41">
-        <v>4.6</v>
+        <v>2.05</v>
       </c>
       <c r="R41">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="S41">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T41">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U41">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="V41">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W41">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z41">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AA41">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="AC41">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="AD41">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AE41">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF41">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK41">
-        <v>1.17</v>
+        <v>2.25</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="O42">
         <v>3.1</v>
@@ -7167,7 +7167,7 @@
         <v>4.2</v>
       </c>
       <c r="R42">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S42">
         <v>1.5</v>
@@ -7185,7 +7185,7 @@
         <v>1.02</v>
       </c>
       <c r="X42">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
         <v>1.47</v>
@@ -7194,7 +7194,7 @@
         <v>2.62</v>
       </c>
       <c r="AA42">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AB42">
         <v>1.48</v>
@@ -7203,7 +7203,7 @@
         <v>4.55</v>
       </c>
       <c r="AD42">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE42">
         <v>1.01</v>
@@ -7228,7 +7228,7 @@
         <v>1.32</v>
       </c>
       <c r="AK42">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7321,13 +7321,13 @@
         <v>2.1</v>
       </c>
       <c r="O43">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P43">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="Q43">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="R43">
         <v>1.92</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK43">
         <v>1.58</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="O44">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
         <v>2.98</v>
       </c>
       <c r="Q44">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="R44">
         <v>2</v>
@@ -7502,7 +7502,7 @@
         <v>2.65</v>
       </c>
       <c r="U44">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="V44">
         <v>1.33</v>
@@ -7538,7 +7538,7 @@
         <v>1.83</v>
       </c>
       <c r="AG44">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7807,22 +7807,22 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.68</v>
+        <v>2.37</v>
       </c>
       <c r="O46">
         <v>2.6</v>
       </c>
       <c r="P46">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q46">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="R46">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S46">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="T46">
         <v>2.4</v>
@@ -7834,7 +7834,7 @@
         <v>1.25</v>
       </c>
       <c r="W46">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X46">
         <v>1.11</v>
@@ -7849,19 +7849,19 @@
         <v>2.45</v>
       </c>
       <c r="AB46">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC46">
         <v>5</v>
       </c>
       <c r="AD46">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE46">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF46">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AG46">
         <v>1.67</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK46">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O47">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q47">
         <v>2.38</v>
@@ -7991,16 +7991,16 @@
         <v>3.1</v>
       </c>
       <c r="U47">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="V47">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W47">
         <v>1.06</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
         <v>1.28</v>
@@ -8012,22 +8012,22 @@
         <v>1.82</v>
       </c>
       <c r="AB47">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC47">
         <v>3.25</v>
       </c>
       <c r="AD47">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF47">
         <v>1.74</v>
       </c>
       <c r="AG47">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8133,28 +8133,28 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="O48">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>4.95</v>
+        <v>5.75</v>
       </c>
       <c r="Q48">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="R48">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T48">
         <v>2.9</v>
       </c>
       <c r="U48">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="V48">
         <v>1.4</v>
@@ -8163,16 +8163,16 @@
         <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z48">
         <v>3.6</v>
       </c>
       <c r="AA48">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AB48">
         <v>1.9</v>
@@ -8181,7 +8181,7 @@
         <v>3.2</v>
       </c>
       <c r="AD48">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE48">
         <v>1.1</v>
@@ -8190,7 +8190,7 @@
         <v>1.87</v>
       </c>
       <c r="AG48">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.15</v>
       </c>
       <c r="AK48">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8308,7 +8308,7 @@
         <v>2.81</v>
       </c>
       <c r="R49">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S49">
         <v>1.38</v>
@@ -8335,10 +8335,10 @@
         <v>3.2</v>
       </c>
       <c r="AA49">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB49">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AC49">
         <v>3.28</v>
@@ -8350,10 +8350,10 @@
         <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG49">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8474,25 +8474,25 @@
         <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="U50">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="V50">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W50">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z50">
         <v>4.4</v>
@@ -8510,13 +8510,13 @@
         <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
         <v>1.53</v>
       </c>
       <c r="AG50">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8637,10 +8637,10 @@
         <v>1.85</v>
       </c>
       <c r="S51">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="T51">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U51">
         <v>4</v>
@@ -8658,7 +8658,7 @@
         <v>1.62</v>
       </c>
       <c r="Z51">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AA51">
         <v>2.83</v>
@@ -8667,7 +8667,7 @@
         <v>1.33</v>
       </c>
       <c r="AC51">
-        <v>6.43</v>
+        <v>6.35</v>
       </c>
       <c r="AD51">
         <v>1.1</v>
@@ -8676,10 +8676,10 @@
         <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG51">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.44</v>
       </c>
       <c r="AK51">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
+        <v>1.72</v>
+      </c>
+      <c r="O52">
+        <v>3.4</v>
+      </c>
+      <c r="P52">
+        <v>4.26</v>
+      </c>
+      <c r="Q52">
+        <v>2.34</v>
+      </c>
+      <c r="R52">
+        <v>2.1</v>
+      </c>
+      <c r="S52">
+        <v>1.39</v>
+      </c>
+      <c r="T52">
+        <v>2.63</v>
+      </c>
+      <c r="U52">
+        <v>2.79</v>
+      </c>
+      <c r="V52">
         <v>1.35</v>
       </c>
-      <c r="O52">
-        <v>4.33</v>
-      </c>
-      <c r="P52">
-        <v>7.7</v>
-      </c>
-      <c r="Q52">
-        <v>1.83</v>
-      </c>
-      <c r="R52">
-        <v>2.29</v>
-      </c>
-      <c r="S52">
-        <v>1.33</v>
-      </c>
-      <c r="T52">
-        <v>2.86</v>
-      </c>
-      <c r="U52">
-        <v>2.63</v>
-      </c>
-      <c r="V52">
-        <v>1.39</v>
-      </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
+        <v>1.25</v>
+      </c>
+      <c r="Z52">
+        <v>3.28</v>
+      </c>
+      <c r="AA52">
+        <v>1.96</v>
+      </c>
+      <c r="AB52">
+        <v>1.79</v>
+      </c>
+      <c r="AC52">
+        <v>3.2</v>
+      </c>
+      <c r="AD52">
+        <v>1.26</v>
+      </c>
+      <c r="AE52">
+        <v>1.06</v>
+      </c>
+      <c r="AF52">
+        <v>1.8</v>
+      </c>
+      <c r="AG52">
+        <v>1.84</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.24</v>
       </c>
-      <c r="Z52">
-        <v>3.34</v>
-      </c>
-      <c r="AA52">
-        <v>1.8</v>
-      </c>
-      <c r="AB52">
-        <v>2</v>
-      </c>
-      <c r="AC52">
-        <v>2.92</v>
-      </c>
-      <c r="AD52">
-        <v>1.31</v>
-      </c>
-      <c r="AE52">
-        <v>1.08</v>
-      </c>
-      <c r="AF52">
-        <v>2.06</v>
-      </c>
-      <c r="AG52">
-        <v>1.65</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.02</v>
-      </c>
       <c r="AK52">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q53">
-        <v>2.46</v>
+        <v>2.05</v>
       </c>
       <c r="R53">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="S53">
         <v>1.38</v>
@@ -8969,43 +8969,43 @@
         <v>2.67</v>
       </c>
       <c r="U53">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="V53">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W53">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y53">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z53">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="AA53">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AB53">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC53">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AD53">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE53">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF53">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="AG53">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK53">
-        <v>1.79</v>
+        <v>2.63</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9114,77 +9114,77 @@
         <v>2.75</v>
       </c>
       <c r="O54">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="P54">
         <v>2.37</v>
       </c>
       <c r="Q54">
-        <v>3.73</v>
+        <v>4.3</v>
       </c>
       <c r="R54">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S54">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="T54">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="U54">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="V54">
+        <v>1.22</v>
+      </c>
+      <c r="W54">
+        <v>1</v>
+      </c>
+      <c r="X54">
+        <v>1.06</v>
+      </c>
+      <c r="Y54">
+        <v>1.5</v>
+      </c>
+      <c r="Z54">
+        <v>2.38</v>
+      </c>
+      <c r="AA54">
+        <v>2.46</v>
+      </c>
+      <c r="AB54">
+        <v>1.43</v>
+      </c>
+      <c r="AC54">
+        <v>4.8</v>
+      </c>
+      <c r="AD54">
+        <v>1.12</v>
+      </c>
+      <c r="AE54">
+        <v>1.04</v>
+      </c>
+      <c r="AF54">
+        <v>2.09</v>
+      </c>
+      <c r="AG54">
+        <v>1.63</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
+        <v>1.53</v>
+      </c>
+      <c r="AK54">
         <v>1.3</v>
-      </c>
-      <c r="W54">
-        <v>1.02</v>
-      </c>
-      <c r="X54">
-        <v>1.04</v>
-      </c>
-      <c r="Y54">
-        <v>1.37</v>
-      </c>
-      <c r="Z54">
-        <v>2.66</v>
-      </c>
-      <c r="AA54">
-        <v>2.35</v>
-      </c>
-      <c r="AB54">
-        <v>1.57</v>
-      </c>
-      <c r="AC54">
-        <v>3.98</v>
-      </c>
-      <c r="AD54">
-        <v>1.17</v>
-      </c>
-      <c r="AE54">
-        <v>1.02</v>
-      </c>
-      <c r="AF54">
-        <v>1.88</v>
-      </c>
-      <c r="AG54">
-        <v>1.79</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ54">
-        <v>1.28</v>
-      </c>
-      <c r="AK54">
-        <v>1.33</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9446,25 +9446,25 @@
         <v>3.1</v>
       </c>
       <c r="Q56">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="R56">
         <v>1.94</v>
       </c>
       <c r="S56">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T56">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U56">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V56">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W56">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X56">
         <v>1.02</v>
@@ -9473,7 +9473,7 @@
         <v>1.42</v>
       </c>
       <c r="Z56">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA56">
         <v>2.25</v>
@@ -9491,7 +9491,7 @@
         <v>1.01</v>
       </c>
       <c r="AF56">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG56">
         <v>1.8</v>
@@ -9510,7 +9510,7 @@
         <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9603,7 +9603,7 @@
         <v>2.5</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P57">
         <v>2.3</v>
@@ -9627,7 +9627,7 @@
         <v>1.87</v>
       </c>
       <c r="W57">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X57">
         <v>1.01</v>
@@ -9639,10 +9639,10 @@
         <v>7.5</v>
       </c>
       <c r="AA57">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB57">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC57">
         <v>1.8</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="O58">
         <v>3.4</v>
@@ -9778,10 +9778,10 @@
         <v>2.01</v>
       </c>
       <c r="S58">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T58">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="U58">
         <v>3.1</v>
@@ -9790,7 +9790,7 @@
         <v>1.33</v>
       </c>
       <c r="W58">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X58">
         <v>1.04</v>
@@ -9808,7 +9808,7 @@
         <v>1.6</v>
       </c>
       <c r="AC58">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD58">
         <v>1.18</v>
@@ -9926,19 +9926,19 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.77</v>
+        <v>2.97</v>
       </c>
       <c r="O59">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="P59">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="Q59">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R59">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S59">
         <v>1.48</v>
@@ -9950,7 +9950,7 @@
         <v>3.25</v>
       </c>
       <c r="V59">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W59">
         <v>1.05</v>
@@ -9962,13 +9962,13 @@
         <v>1.36</v>
       </c>
       <c r="Z59">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AA59">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AB59">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AC59">
         <v>4</v>
@@ -9980,10 +9980,10 @@
         <v>1.06</v>
       </c>
       <c r="AF59">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG59">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AK59">
         <v>1.36</v>
@@ -10098,16 +10098,16 @@
         <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="R60">
         <v>1.95</v>
       </c>
       <c r="S60">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="T60">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="U60">
         <v>3.55</v>
@@ -10122,7 +10122,7 @@
         <v>1.07</v>
       </c>
       <c r="Y60">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Z60">
         <v>2.57</v>
@@ -10134,7 +10134,7 @@
         <v>1.53</v>
       </c>
       <c r="AC60">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD60">
         <v>1.17</v>
@@ -10143,10 +10143,10 @@
         <v>1.05</v>
       </c>
       <c r="AF60">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AG60">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK60">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="O61">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P61">
         <v>2.45</v>
@@ -10267,13 +10267,13 @@
         <v>1.86</v>
       </c>
       <c r="S61">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T61">
         <v>2.4</v>
       </c>
       <c r="U61">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="V61">
         <v>1.3</v>
@@ -10297,19 +10297,19 @@
         <v>1.52</v>
       </c>
       <c r="AC61">
-        <v>4.35</v>
+        <v>4.53</v>
       </c>
       <c r="AD61">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE61">
         <v>1.05</v>
       </c>
       <c r="AF61">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG61">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10421,13 +10421,13 @@
         <v>3.5</v>
       </c>
       <c r="P62">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="Q62">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="R62">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S62">
         <v>1.39</v>
@@ -10436,7 +10436,7 @@
         <v>2.73</v>
       </c>
       <c r="U62">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="V62">
         <v>1.36</v>
@@ -10448,10 +10448,10 @@
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z62">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AA62">
         <v>2</v>
@@ -10469,10 +10469,10 @@
         <v>1.05</v>
       </c>
       <c r="AF62">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG62">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10599,7 +10599,7 @@
         <v>2.7</v>
       </c>
       <c r="U63">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="V63">
         <v>1.38</v>
@@ -10611,7 +10611,7 @@
         <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z63">
         <v>3.25</v>
@@ -10629,13 +10629,13 @@
         <v>1.26</v>
       </c>
       <c r="AE63">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF63">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AG63">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK63">
         <v>1.6</v>
@@ -10741,19 +10741,19 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="O64">
         <v>3.2</v>
       </c>
       <c r="P64">
-        <v>6.15</v>
+        <v>5.5</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
       </c>
       <c r="R64">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S64">
         <v>1.61</v>
@@ -10762,7 +10762,7 @@
         <v>2.25</v>
       </c>
       <c r="U64">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="V64">
         <v>1.22</v>
@@ -10777,28 +10777,28 @@
         <v>1.62</v>
       </c>
       <c r="Z64">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AA64">
-        <v>2.35</v>
+        <v>2.85</v>
       </c>
       <c r="AB64">
         <v>1.36</v>
       </c>
       <c r="AC64">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AD64">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AE64">
         <v>1.03</v>
       </c>
       <c r="AF64">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AG64">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10910,25 +10910,25 @@
         <v>3.35</v>
       </c>
       <c r="P65">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q65">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="R65">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S65">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T65">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U65">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V65">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W65">
         <v>1.1</v>
@@ -10937,16 +10937,16 @@
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z65">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="AA65">
         <v>1.81</v>
       </c>
       <c r="AB65">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC65">
         <v>2.85</v>
@@ -10955,13 +10955,13 @@
         <v>1.31</v>
       </c>
       <c r="AE65">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF65">
         <v>1.66</v>
       </c>
       <c r="AG65">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11091,7 +11091,7 @@
         <v>2.6</v>
       </c>
       <c r="V66">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W66">
         <v>1.1</v>
@@ -11100,7 +11100,7 @@
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z66">
         <v>3.7</v>
@@ -11109,19 +11109,19 @@
         <v>1.77</v>
       </c>
       <c r="AB66">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC66">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD66">
         <v>1.33</v>
       </c>
       <c r="AE66">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF66">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG66">
         <v>1.95</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="O67">
         <v>3.1</v>
       </c>
       <c r="P67">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q67">
         <v>3.78</v>
       </c>
       <c r="R67">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S67">
         <v>1.42</v>
@@ -11260,7 +11260,7 @@
         <v>1.03</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y67">
         <v>1.36</v>
@@ -11269,7 +11269,7 @@
         <v>3.1</v>
       </c>
       <c r="AA67">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB67">
         <v>1.62</v>
@@ -11281,7 +11281,7 @@
         <v>1.19</v>
       </c>
       <c r="AE67">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF67">
         <v>1.83</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="O4">
         <v>3.45</v>
       </c>
       <c r="P4">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="Q4">
-        <v>4.71</v>
+        <v>4.65</v>
       </c>
       <c r="R4">
         <v>2.07</v>
@@ -979,10 +979,10 @@
         <v>1.41</v>
       </c>
       <c r="T4">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="U4">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="V4">
         <v>1.35</v>
@@ -997,13 +997,13 @@
         <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>3.18</v>
+        <v>2.97</v>
       </c>
       <c r="AA4">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AB4">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AC4">
         <v>3.5</v>
@@ -1015,10 +1015,10 @@
         <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
         <v>1.21</v>
@@ -1139,16 +1139,16 @@
         <v>2.2</v>
       </c>
       <c r="S5">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
         <v>2.8</v>
       </c>
       <c r="U5">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W5">
         <v>1.06</v>
@@ -1166,10 +1166,10 @@
         <v>1.87</v>
       </c>
       <c r="AB5">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD5">
         <v>1.29</v>
@@ -1178,10 +1178,10 @@
         <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AG5">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
         <v>2.03</v>
@@ -1290,10 +1290,10 @@
         <v>2.25</v>
       </c>
       <c r="O6">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P6">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q6">
         <v>3.02</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
         <v>1.5</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="O9">
         <v>3.55</v>
       </c>
       <c r="P9">
-        <v>4.45</v>
+        <v>5.45</v>
       </c>
       <c r="Q9">
         <v>2.18</v>
       </c>
       <c r="R9">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="S9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T9">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="U9">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W9">
         <v>1.02</v>
@@ -1809,13 +1809,13 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z9">
-        <v>3.06</v>
+        <v>2.92</v>
       </c>
       <c r="AA9">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AB9">
         <v>1.72</v>
@@ -1849,7 +1849,7 @@
         <v>1.28</v>
       </c>
       <c r="AK9">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="O10">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
@@ -1954,13 +1954,13 @@
         <v>2.42</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="U10">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V10">
         <v>1.44</v>
@@ -1969,10 +1969,10 @@
         <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
         <v>3.82</v>
@@ -1984,19 +1984,19 @@
         <v>2.05</v>
       </c>
       <c r="AC10">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD10">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE10">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
         <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
         <v>2.15</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q18">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="R18">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T18">
         <v>2.59</v>
       </c>
       <c r="U18">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="V18">
         <v>1.36</v>
       </c>
       <c r="W18">
+        <v>1.04</v>
+      </c>
+      <c r="X18">
         <v>1.06</v>
-      </c>
-      <c r="X18">
-        <v>1.04</v>
       </c>
       <c r="Y18">
         <v>1.3</v>
       </c>
       <c r="Z18">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA18">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC18">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD18">
         <v>1.25</v>
       </c>
       <c r="AE18">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF18">
         <v>1.8</v>
       </c>
       <c r="AG18">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AK18">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P19">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q19">
         <v>3.85</v>
       </c>
       <c r="R19">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="S19">
         <v>1.47</v>
@@ -3427,10 +3427,10 @@
         <v>2.63</v>
       </c>
       <c r="U19">
-        <v>3.31</v>
+        <v>3.22</v>
       </c>
       <c r="V19">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W19">
         <v>1.02</v>
@@ -3439,7 +3439,7 @@
         <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z19">
         <v>2.66</v>
@@ -3448,13 +3448,13 @@
         <v>2.29</v>
       </c>
       <c r="AB19">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AC19">
         <v>3.92</v>
       </c>
       <c r="AD19">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE19">
         <v>1.03</v>
@@ -3463,7 +3463,7 @@
         <v>1.9</v>
       </c>
       <c r="AG19">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AK19">
         <v>1.33</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O21">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P21">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>2.12</v>
       </c>
       <c r="O22">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="P22">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
@@ -3910,10 +3910,10 @@
         <v>1.98</v>
       </c>
       <c r="S22">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T22">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="U22">
         <v>3.28</v>
@@ -3937,7 +3937,7 @@
         <v>2.15</v>
       </c>
       <c r="AB22">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AC22">
         <v>4.2</v>
@@ -3949,10 +3949,10 @@
         <v>1.06</v>
       </c>
       <c r="AF22">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG22">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O24">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q24">
-        <v>4.27</v>
+        <v>3.64</v>
       </c>
       <c r="R24">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="S24">
         <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U24">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z24">
-        <v>4.66</v>
+        <v>4.49</v>
       </c>
       <c r="AA24">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AC24">
         <v>2.45</v>
       </c>
       <c r="AD24">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE24">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF24">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AG24">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.95</v>
+        <v>1.16</v>
       </c>
       <c r="AK24">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4396,7 +4396,7 @@
         <v>2.78</v>
       </c>
       <c r="R25">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="S25">
         <v>1.48</v>
@@ -4420,7 +4420,7 @@
         <v>1.4</v>
       </c>
       <c r="Z25">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AA25">
         <v>2.19</v>
@@ -4435,10 +4435,10 @@
         <v>1.16</v>
       </c>
       <c r="AE25">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF25">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG25">
         <v>1.75</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="O26">
         <v>4.75</v>
@@ -4571,7 +4571,7 @@
         <v>2.69</v>
       </c>
       <c r="V26">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
         <v>1.05</v>
@@ -4580,19 +4580,19 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
         <v>3.34</v>
       </c>
       <c r="AA26">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AB26">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AC26">
-        <v>3.13</v>
+        <v>2.97</v>
       </c>
       <c r="AD26">
         <v>1.3</v>
@@ -4604,7 +4604,7 @@
         <v>2.33</v>
       </c>
       <c r="AG26">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4876,10 +4876,10 @@
         <v>3.1</v>
       </c>
       <c r="O28">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="P28">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5854,16 +5854,16 @@
         <v>1.39</v>
       </c>
       <c r="O34">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="P34">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="Q34">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R34">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S34">
         <v>1.22</v>
@@ -5875,37 +5875,37 @@
         <v>2.12</v>
       </c>
       <c r="V34">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W34">
         <v>1.14</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
         <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>5.75</v>
+        <v>5.1</v>
       </c>
       <c r="AA34">
         <v>1.47</v>
       </c>
       <c r="AB34">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="AC34">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="AD34">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE34">
         <v>1.22</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG34">
         <v>2.15</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK34">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6183,19 +6183,19 @@
         <v>3.5</v>
       </c>
       <c r="P36">
-        <v>4.2</v>
+        <v>4.42</v>
       </c>
       <c r="Q36">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="R36">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
         <v>1.43</v>
       </c>
       <c r="T36">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="U36">
         <v>2.88</v>
@@ -6250,7 +6250,7 @@
         <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O39">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P39">
+        <v>2.7</v>
+      </c>
+      <c r="Q39">
+        <v>3.02</v>
+      </c>
+      <c r="R39">
+        <v>2.12</v>
+      </c>
+      <c r="S39">
+        <v>1.35</v>
+      </c>
+      <c r="T39">
+        <v>2.9</v>
+      </c>
+      <c r="U39">
+        <v>2.65</v>
+      </c>
+      <c r="V39">
+        <v>1.42</v>
+      </c>
+      <c r="W39">
+        <v>1.07</v>
+      </c>
+      <c r="X39">
+        <v>1.02</v>
+      </c>
+      <c r="Y39">
+        <v>1.26</v>
+      </c>
+      <c r="Z39">
+        <v>3.4</v>
+      </c>
+      <c r="AA39">
+        <v>1.85</v>
+      </c>
+      <c r="AB39">
+        <v>1.85</v>
+      </c>
+      <c r="AC39">
         <v>3.1</v>
       </c>
-      <c r="Q39">
-        <v>2.6</v>
-      </c>
-      <c r="R39">
-        <v>2.2</v>
-      </c>
-      <c r="S39">
-        <v>0</v>
-      </c>
-      <c r="T39">
-        <v>0</v>
-      </c>
-      <c r="U39">
-        <v>2.55</v>
-      </c>
-      <c r="V39">
-        <v>1.38</v>
-      </c>
-      <c r="W39">
-        <v>0</v>
-      </c>
-      <c r="X39">
-        <v>0</v>
-      </c>
-      <c r="Y39">
-        <v>1.25</v>
-      </c>
-      <c r="Z39">
-        <v>3.3</v>
-      </c>
-      <c r="AA39">
-        <v>1.82</v>
-      </c>
-      <c r="AB39">
-        <v>1.81</v>
-      </c>
-      <c r="AC39">
-        <v>3</v>
-      </c>
       <c r="AD39">
+        <v>1.31</v>
+      </c>
+      <c r="AE39">
+        <v>1.08</v>
+      </c>
+      <c r="AF39">
+        <v>1.71</v>
+      </c>
+      <c r="AG39">
+        <v>2.03</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.3</v>
       </c>
-      <c r="AE39">
-        <v>0</v>
-      </c>
-      <c r="AF39">
-        <v>1.7</v>
-      </c>
-      <c r="AG39">
-        <v>2</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.23</v>
-      </c>
       <c r="AK39">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6835,58 +6835,58 @@
         <v>4.2</v>
       </c>
       <c r="P40">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q40">
         <v>4.6</v>
       </c>
       <c r="R40">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="S40">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T40">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U40">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="V40">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z40">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA40">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AB40">
         <v>2.63</v>
       </c>
       <c r="AC40">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AD40">
         <v>1.67</v>
       </c>
       <c r="AE40">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF40">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AG40">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O41">
         <v>4</v>
       </c>
       <c r="P41">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q41">
         <v>2.05</v>
@@ -7007,7 +7007,7 @@
         <v>2.48</v>
       </c>
       <c r="S41">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T41">
         <v>3.68</v>
@@ -7019,7 +7019,7 @@
         <v>1.71</v>
       </c>
       <c r="W41">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7034,13 +7034,13 @@
         <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="AC41">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AD41">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE41">
         <v>1.28</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK41">
         <v>2.25</v>
@@ -7155,46 +7155,46 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="O42">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P42">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q42">
-        <v>4.2</v>
+        <v>4.71</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S42">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T42">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="U42">
         <v>3.6</v>
       </c>
       <c r="V42">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W42">
         <v>1.02</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y42">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z42">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AA42">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AB42">
         <v>1.48</v>
@@ -7203,10 +7203,10 @@
         <v>4.55</v>
       </c>
       <c r="AD42">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE42">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF42">
         <v>2.06</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK42">
         <v>1.25</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="O45">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P45">
         <v>3.4</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="O46">
         <v>2.6</v>
       </c>
       <c r="P46">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q46">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="R46">
         <v>1.91</v>
       </c>
       <c r="S46">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="T46">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U46">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="V46">
         <v>1.25</v>
       </c>
       <c r="W46">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X46">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y46">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Z46">
+        <v>2.59</v>
+      </c>
+      <c r="AA46">
         <v>2.5</v>
       </c>
-      <c r="AA46">
-        <v>2.45</v>
-      </c>
       <c r="AB46">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AC46">
         <v>5</v>
       </c>
       <c r="AD46">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE46">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF46">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG46">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK46">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
-        <v>3.9</v>
+        <v>3.52</v>
       </c>
       <c r="Q47">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="R47">
         <v>2.15</v>
@@ -7991,10 +7991,10 @@
         <v>3.1</v>
       </c>
       <c r="U47">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V47">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="W47">
         <v>1.06</v>
@@ -8012,22 +8012,22 @@
         <v>1.82</v>
       </c>
       <c r="AB47">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC47">
         <v>3.25</v>
       </c>
       <c r="AD47">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE47">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF47">
         <v>1.74</v>
       </c>
       <c r="AG47">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O48">
         <v>4</v>
       </c>
       <c r="P48">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="Q48">
         <v>2.1</v>
@@ -8148,22 +8148,22 @@
         <v>2.36</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T48">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U48">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="V48">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W48">
         <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.29</v>
@@ -8172,10 +8172,10 @@
         <v>3.6</v>
       </c>
       <c r="AA48">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AB48">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC48">
         <v>3.2</v>
@@ -8187,7 +8187,7 @@
         <v>1.1</v>
       </c>
       <c r="AF48">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG48">
         <v>1.83</v>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="O52">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
-        <v>4.26</v>
+        <v>3.8</v>
       </c>
       <c r="Q52">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="R52">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S52">
         <v>1.39</v>
@@ -8806,10 +8806,10 @@
         <v>2.63</v>
       </c>
       <c r="U52">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="V52">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W52">
         <v>1.03</v>
@@ -8818,47 +8818,47 @@
         <v>1.03</v>
       </c>
       <c r="Y52">
+        <v>1.26</v>
+      </c>
+      <c r="Z52">
+        <v>3.4</v>
+      </c>
+      <c r="AA52">
+        <v>1.92</v>
+      </c>
+      <c r="AB52">
+        <v>1.87</v>
+      </c>
+      <c r="AC52">
+        <v>3.5</v>
+      </c>
+      <c r="AD52">
         <v>1.25</v>
       </c>
-      <c r="Z52">
-        <v>3.28</v>
-      </c>
-      <c r="AA52">
-        <v>1.96</v>
-      </c>
-      <c r="AB52">
-        <v>1.79</v>
-      </c>
-      <c r="AC52">
-        <v>3.2</v>
-      </c>
-      <c r="AD52">
-        <v>1.26</v>
-      </c>
       <c r="AE52">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF52">
+        <v>1.78</v>
+      </c>
+      <c r="AG52">
+        <v>1.89</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>1.25</v>
+      </c>
+      <c r="AK52">
         <v>1.8</v>
-      </c>
-      <c r="AG52">
-        <v>1.84</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.24</v>
-      </c>
-      <c r="AK52">
-        <v>1.91</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,25 +8957,25 @@
         <v>7.7</v>
       </c>
       <c r="Q53">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R53">
         <v>2.12</v>
       </c>
       <c r="S53">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T53">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="U53">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V53">
         <v>1.34</v>
       </c>
       <c r="W53">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
         <v>1.02</v>
@@ -8984,13 +8984,13 @@
         <v>1.29</v>
       </c>
       <c r="Z53">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA53">
         <v>1.97</v>
       </c>
       <c r="AB53">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC53">
         <v>3.34</v>
@@ -8999,13 +8999,13 @@
         <v>1.24</v>
       </c>
       <c r="AE53">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF53">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG53">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,25 +9111,25 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="O54">
         <v>2.85</v>
       </c>
       <c r="P54">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="Q54">
-        <v>4.3</v>
+        <v>4.13</v>
       </c>
       <c r="R54">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="S54">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="T54">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U54">
         <v>3.5</v>
@@ -9138,37 +9138,37 @@
         <v>1.22</v>
       </c>
       <c r="W54">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X54">
         <v>1.06</v>
       </c>
       <c r="Y54">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Z54">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AA54">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AB54">
         <v>1.43</v>
       </c>
       <c r="AC54">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD54">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE54">
         <v>1.04</v>
       </c>
       <c r="AF54">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AG54">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="O55">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="P55">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC55">
         <v>0</v>
@@ -9437,46 +9437,46 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O56">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P56">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q56">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="R56">
         <v>1.94</v>
       </c>
       <c r="S56">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T56">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="U56">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="V56">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W56">
+        <v>1.01</v>
+      </c>
+      <c r="X56">
         <v>1.05</v>
-      </c>
-      <c r="X56">
-        <v>1.02</v>
       </c>
       <c r="Y56">
         <v>1.42</v>
       </c>
       <c r="Z56">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA56">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AB56">
         <v>1.63</v>
@@ -9494,7 +9494,7 @@
         <v>1.91</v>
       </c>
       <c r="AG56">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="O58">
         <v>3.4</v>
       </c>
       <c r="P58">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q58">
         <v>2.38</v>
@@ -9778,13 +9778,13 @@
         <v>2.01</v>
       </c>
       <c r="S58">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T58">
         <v>2.47</v>
       </c>
       <c r="U58">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V58">
         <v>1.33</v>
@@ -9796,7 +9796,7 @@
         <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z58">
         <v>2.8</v>
@@ -9811,16 +9811,16 @@
         <v>4.4</v>
       </c>
       <c r="AD58">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE58">
         <v>1.06</v>
       </c>
       <c r="AF58">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG58">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.97</v>
+        <v>2.77</v>
       </c>
       <c r="O59">
         <v>3</v>
       </c>
       <c r="P59">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -9950,10 +9950,10 @@
         <v>3.25</v>
       </c>
       <c r="V59">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W59">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X59">
         <v>1.1</v>
@@ -9965,13 +9965,13 @@
         <v>2.71</v>
       </c>
       <c r="AA59">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AB59">
         <v>1.55</v>
       </c>
       <c r="AC59">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AD59">
         <v>1.17</v>
@@ -10098,10 +10098,10 @@
         <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="R60">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S60">
         <v>1.56</v>
@@ -10110,7 +10110,7 @@
         <v>2.45</v>
       </c>
       <c r="U60">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="V60">
         <v>1.28</v>
@@ -10125,7 +10125,7 @@
         <v>1.52</v>
       </c>
       <c r="Z60">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AA60">
         <v>2.45</v>
@@ -10134,7 +10134,7 @@
         <v>1.53</v>
       </c>
       <c r="AC60">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AD60">
         <v>1.17</v>
@@ -10143,10 +10143,10 @@
         <v>1.05</v>
       </c>
       <c r="AF60">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AG60">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK60">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AL60">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU67"/>
+  <dimension ref="A1:AU68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="O7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P7">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="Q7">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="R7">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="S7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="U7">
         <v>2.5</v>
       </c>
       <c r="V7">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA7">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AB7">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD7">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE7">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AG7">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AK7">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,10 +1622,10 @@
         <v>2.8</v>
       </c>
       <c r="Q8">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="R8">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S8">
         <v>1.44</v>
@@ -1658,19 +1658,19 @@
         <v>1.57</v>
       </c>
       <c r="AC8">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD8">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE8">
         <v>1.03</v>
       </c>
       <c r="AF8">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG8">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O11">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P11">
         <v>5</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB11">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3243,58 +3243,58 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O18">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P18">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q18">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S18">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T18">
         <v>2.59</v>
       </c>
       <c r="U18">
-        <v>2.77</v>
+        <v>3.06</v>
       </c>
       <c r="V18">
         <v>1.36</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
         <v>1.3</v>
       </c>
       <c r="Z18">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA18">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB18">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC18">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD18">
         <v>1.25</v>
       </c>
       <c r="AE18">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF18">
         <v>1.8</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.73</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
         <v>1.18</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,19 +4221,19 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P24">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q24">
-        <v>3.64</v>
+        <v>4.19</v>
       </c>
       <c r="R24">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="S24">
         <v>1.25</v>
@@ -4242,7 +4242,7 @@
         <v>3.4</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V24">
         <v>1.55</v>
@@ -4257,19 +4257,19 @@
         <v>1.15</v>
       </c>
       <c r="Z24">
-        <v>4.49</v>
+        <v>4.6</v>
       </c>
       <c r="AA24">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB24">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="AC24">
         <v>2.45</v>
       </c>
       <c r="AD24">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE24">
         <v>1.16</v>
@@ -4278,7 +4278,7 @@
         <v>1.55</v>
       </c>
       <c r="AG24">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK24">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,52 +4393,52 @@
         <v>3.24</v>
       </c>
       <c r="Q25">
-        <v>2.78</v>
+        <v>2.49</v>
       </c>
       <c r="R25">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S25">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T25">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U25">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X25">
         <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z25">
         <v>2.5</v>
       </c>
       <c r="AA25">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AB25">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AC25">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD25">
         <v>1.16</v>
       </c>
       <c r="AE25">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG25">
         <v>1.75</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AK25">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O28">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB28">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="O29">
-        <v>3.23</v>
+        <v>3.31</v>
       </c>
       <c r="P29">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="Q29">
+        <v>2.7</v>
+      </c>
+      <c r="R29">
+        <v>2.18</v>
+      </c>
+      <c r="S29">
+        <v>1.32</v>
+      </c>
+      <c r="T29">
+        <v>3.05</v>
+      </c>
+      <c r="U29">
         <v>2.41</v>
       </c>
-      <c r="R29">
-        <v>2.13</v>
-      </c>
-      <c r="S29">
-        <v>1.35</v>
-      </c>
-      <c r="T29">
-        <v>2.9</v>
-      </c>
-      <c r="U29">
-        <v>2.5</v>
-      </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA29">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AB29">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC29">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="AD29">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE29">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF29">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AG29">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="AK29">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="O30">
-        <v>3.31</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
+        <v>3.69</v>
+      </c>
+      <c r="Q30">
+        <v>2.41</v>
+      </c>
+      <c r="R30">
+        <v>2.13</v>
+      </c>
+      <c r="S30">
+        <v>1.35</v>
+      </c>
+      <c r="T30">
+        <v>3.1</v>
+      </c>
+      <c r="U30">
         <v>2.5</v>
       </c>
-      <c r="Q30">
-        <v>2.7</v>
-      </c>
-      <c r="R30">
-        <v>2.18</v>
-      </c>
-      <c r="S30">
-        <v>1.32</v>
-      </c>
-      <c r="T30">
-        <v>3.05</v>
-      </c>
-      <c r="U30">
-        <v>2.38</v>
-      </c>
       <c r="V30">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W30">
+        <v>1.07</v>
+      </c>
+      <c r="X30">
+        <v>1.04</v>
+      </c>
+      <c r="Y30">
+        <v>1.22</v>
+      </c>
+      <c r="Z30">
+        <v>3.58</v>
+      </c>
+      <c r="AA30">
+        <v>1.8</v>
+      </c>
+      <c r="AB30">
+        <v>2.04</v>
+      </c>
+      <c r="AC30">
+        <v>2.83</v>
+      </c>
+      <c r="AD30">
+        <v>1.33</v>
+      </c>
+      <c r="AE30">
         <v>1.09</v>
       </c>
-      <c r="X30">
-        <v>1</v>
-      </c>
-      <c r="Y30">
-        <v>1.2</v>
-      </c>
-      <c r="Z30">
-        <v>4</v>
-      </c>
-      <c r="AA30">
-        <v>1.66</v>
-      </c>
-      <c r="AB30">
-        <v>2.15</v>
-      </c>
-      <c r="AC30">
-        <v>2.63</v>
-      </c>
-      <c r="AD30">
-        <v>1.41</v>
-      </c>
-      <c r="AE30">
-        <v>1.14</v>
-      </c>
       <c r="AF30">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AG30">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,22 +5362,22 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="O31">
-        <v>3.52</v>
+        <v>3.65</v>
       </c>
       <c r="P31">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="Q31">
         <v>2.9</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S31">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T31">
         <v>3.8</v>
@@ -5395,28 +5395,28 @@
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z31">
         <v>5</v>
       </c>
       <c r="AA31">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB31">
         <v>2.29</v>
       </c>
       <c r="AC31">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AD31">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE31">
         <v>1.18</v>
       </c>
       <c r="AF31">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AG31">
         <v>2.5</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AK31">
         <v>1.5</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="O32">
         <v>4.05</v>
@@ -5537,37 +5537,37 @@
         <v>2.23</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="U32">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="V32">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
         <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="AA32">
         <v>1.75</v>
       </c>
       <c r="AB32">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AC32">
         <v>2.81</v>
@@ -5576,7 +5576,7 @@
         <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
         <v>1.7</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
         <v>2</v>
@@ -6026,22 +6026,22 @@
         <v>2.06</v>
       </c>
       <c r="R35">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S35">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U35">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V35">
         <v>1.58</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X35">
         <v>1.01</v>
@@ -6065,7 +6065,7 @@
         <v>1.54</v>
       </c>
       <c r="AE35">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AF35">
         <v>1.57</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK35">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6183,19 +6183,19 @@
         <v>3.5</v>
       </c>
       <c r="P36">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="Q36">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S36">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T36">
-        <v>2.93</v>
+        <v>2.62</v>
       </c>
       <c r="U36">
         <v>2.88</v>
@@ -6222,7 +6222,7 @@
         <v>1.8</v>
       </c>
       <c r="AC36">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AD36">
         <v>1.26</v>
@@ -6231,10 +6231,10 @@
         <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AG36">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>2.02</v>
       </c>
       <c r="O37">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="P37">
         <v>3.35</v>
@@ -6352,7 +6352,7 @@
         <v>2.75</v>
       </c>
       <c r="R37">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="S37">
         <v>1.53</v>
@@ -6361,10 +6361,10 @@
         <v>2.43</v>
       </c>
       <c r="U37">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="V37">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W37">
         <v>1.03</v>
@@ -6373,10 +6373,10 @@
         <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Z37">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="AA37">
         <v>2.43</v>
@@ -6385,7 +6385,7 @@
         <v>1.6</v>
       </c>
       <c r="AC37">
-        <v>4.43</v>
+        <v>4.2</v>
       </c>
       <c r="AD37">
         <v>1.17</v>
@@ -6394,7 +6394,7 @@
         <v>1.02</v>
       </c>
       <c r="AF37">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG37">
         <v>1.74</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="O38">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P38">
         <v>5</v>
@@ -6699,10 +6699,10 @@
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA39">
         <v>1.85</v>
@@ -6711,7 +6711,7 @@
         <v>1.85</v>
       </c>
       <c r="AC39">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD39">
         <v>1.31</v>
@@ -6720,10 +6720,10 @@
         <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG39">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AK39">
         <v>1.53</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.64</v>
+        <v>4.05</v>
       </c>
       <c r="O42">
         <v>2.8</v>
       </c>
       <c r="P42">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q42">
-        <v>4.71</v>
+        <v>4.22</v>
       </c>
       <c r="R42">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S42">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="T42">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="U42">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="V42">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W42">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X42">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z42">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA42">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AB42">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AC42">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AD42">
         <v>1.17</v>
       </c>
       <c r="AE42">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF42">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AG42">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.28</v>
       </c>
       <c r="AK42">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O43">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="P43">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="Q43">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="R43">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="S43">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T43">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="U43">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="V43">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W43">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z43">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="AA43">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="AB43">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC43">
-        <v>3.86</v>
+        <v>4.6</v>
       </c>
       <c r="AD43">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE43">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF43">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AG43">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
         <v>1.58</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="O44">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="P44">
-        <v>2.98</v>
+        <v>3.38</v>
       </c>
       <c r="Q44">
         <v>2.8</v>
@@ -7499,13 +7499,13 @@
         <v>1.4</v>
       </c>
       <c r="T44">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U44">
-        <v>2.83</v>
+        <v>3.15</v>
       </c>
       <c r="V44">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W44">
         <v>1.03</v>
@@ -7520,7 +7520,7 @@
         <v>3.1</v>
       </c>
       <c r="AA44">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB44">
         <v>1.7</v>
@@ -7532,7 +7532,7 @@
         <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF44">
         <v>1.83</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK44">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7973,46 +7973,46 @@
         <v>1.72</v>
       </c>
       <c r="O47">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P47">
         <v>3.52</v>
       </c>
       <c r="Q47">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R47">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S47">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U47">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="V47">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z47">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="AA47">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB47">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC47">
         <v>3.25</v>
@@ -8021,13 +8021,13 @@
         <v>1.3</v>
       </c>
       <c r="AE47">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF47">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AG47">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O49">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P49">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q49">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="R49">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S49">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T49">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="U49">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="V49">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W49">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z49">
         <v>3.2</v>
       </c>
       <c r="AA49">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AB49">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC49">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD49">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF49">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG49">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK49">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O50">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P50">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q50">
         <v>4.3</v>
@@ -8477,28 +8477,28 @@
         <v>1.29</v>
       </c>
       <c r="T50">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="U50">
-        <v>2.31</v>
+        <v>2.48</v>
       </c>
       <c r="V50">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W50">
         <v>1.1</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z50">
         <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB50">
         <v>2.13</v>
@@ -8510,13 +8510,13 @@
         <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF50">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG50">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.26</v>
+        <v>1.85</v>
       </c>
       <c r="AK50">
         <v>1.28</v>
@@ -8631,16 +8631,16 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="R51">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="S51">
         <v>1.65</v>
       </c>
       <c r="T51">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U51">
         <v>4</v>
@@ -8652,13 +8652,13 @@
         <v>1.03</v>
       </c>
       <c r="X51">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y51">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z51">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AA51">
         <v>2.83</v>
@@ -8667,7 +8667,7 @@
         <v>1.33</v>
       </c>
       <c r="AC51">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="AD51">
         <v>1.1</v>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O56">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P56">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="Q56">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="R56">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S56">
         <v>1.46</v>
@@ -9470,19 +9470,19 @@
         <v>1.05</v>
       </c>
       <c r="Y56">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z56">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AA56">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AB56">
         <v>1.63</v>
       </c>
       <c r="AC56">
-        <v>4</v>
+        <v>4.16</v>
       </c>
       <c r="AD56">
         <v>1.22</v>
@@ -9491,7 +9491,7 @@
         <v>1.01</v>
       </c>
       <c r="AF56">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AG56">
         <v>1.78</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK56">
         <v>1.7</v>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O57">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P57">
         <v>2.3</v>
@@ -9612,22 +9612,22 @@
         <v>2.88</v>
       </c>
       <c r="R57">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="S57">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T57">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="U57">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V57">
         <v>1.87</v>
       </c>
       <c r="W57">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X57">
         <v>1.01</v>
@@ -9639,25 +9639,25 @@
         <v>7.5</v>
       </c>
       <c r="AA57">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AB57">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AC57">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AD57">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AE57">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AF57">
         <v>1.28</v>
       </c>
       <c r="AG57">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK57">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,16 +9763,16 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O58">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P58">
         <v>4.5</v>
       </c>
       <c r="Q58">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R58">
         <v>2.01</v>
@@ -9781,28 +9781,28 @@
         <v>1.47</v>
       </c>
       <c r="T58">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="U58">
         <v>3.3</v>
       </c>
       <c r="V58">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W58">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X58">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y58">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z58">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="AA58">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AB58">
         <v>1.6</v>
@@ -9820,7 +9820,7 @@
         <v>2.15</v>
       </c>
       <c r="AG58">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.17</v>
       </c>
       <c r="AK58">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9944,16 +9944,16 @@
         <v>1.48</v>
       </c>
       <c r="T59">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="U59">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V59">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W59">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X59">
         <v>1.1</v>
@@ -9962,13 +9962,13 @@
         <v>1.36</v>
       </c>
       <c r="Z59">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="AA59">
         <v>2.3</v>
       </c>
       <c r="AB59">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC59">
         <v>3.98</v>
@@ -9977,7 +9977,7 @@
         <v>1.17</v>
       </c>
       <c r="AE59">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF59">
         <v>2</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AK59">
         <v>1.36</v>
@@ -10098,19 +10098,19 @@
         <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="R60">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="S60">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="T60">
         <v>2.45</v>
       </c>
       <c r="U60">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V60">
         <v>1.28</v>
@@ -10122,19 +10122,19 @@
         <v>1.07</v>
       </c>
       <c r="Y60">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z60">
         <v>2.5</v>
       </c>
       <c r="AA60">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AB60">
         <v>1.53</v>
       </c>
       <c r="AC60">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AD60">
         <v>1.17</v>
@@ -10143,7 +10143,7 @@
         <v>1.05</v>
       </c>
       <c r="AF60">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG60">
         <v>1.67</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK60">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,37 +10252,37 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="O61">
         <v>2.8</v>
       </c>
       <c r="P61">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="Q61">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="R61">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="S61">
         <v>1.54</v>
       </c>
       <c r="T61">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="U61">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="V61">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W61">
         <v>1.01</v>
       </c>
       <c r="X61">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y61">
         <v>1.43</v>
@@ -10291,25 +10291,25 @@
         <v>2.46</v>
       </c>
       <c r="AA61">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AB61">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC61">
-        <v>4.53</v>
+        <v>4.4</v>
       </c>
       <c r="AD61">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE61">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF61">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG61">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AK61">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,19 +10415,19 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O62">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P62">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="Q62">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="R62">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="S62">
         <v>1.39</v>
@@ -10436,7 +10436,7 @@
         <v>2.73</v>
       </c>
       <c r="U62">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="V62">
         <v>1.36</v>
@@ -10448,19 +10448,19 @@
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z62">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="AA62">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB62">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC62">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="AD62">
         <v>1.25</v>
@@ -10469,10 +10469,10 @@
         <v>1.05</v>
       </c>
       <c r="AF62">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG62">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK62">
         <v>2.12</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="O64">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P64">
         <v>5.5</v>
       </c>
       <c r="Q64">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="R64">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="S64">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="U64">
-        <v>3.8</v>
+        <v>2.15</v>
       </c>
       <c r="V64">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="W64">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X64">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.62</v>
+        <v>1.19</v>
       </c>
       <c r="Z64">
-        <v>2.2</v>
+        <v>4.55</v>
       </c>
       <c r="AA64">
-        <v>2.85</v>
+        <v>1.54</v>
       </c>
       <c r="AB64">
-        <v>1.36</v>
+        <v>2.28</v>
       </c>
       <c r="AC64">
-        <v>6.5</v>
+        <v>2.46</v>
       </c>
       <c r="AD64">
-        <v>1.08</v>
+        <v>1.56</v>
       </c>
       <c r="AE64">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AF64">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG64">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AK64">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,81 +10904,81 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="O65">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P65">
-        <v>3.15</v>
+        <v>5.5</v>
       </c>
       <c r="Q65">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="R65">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="S65">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="T65">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="U65">
-        <v>2.75</v>
+        <v>3.74</v>
       </c>
       <c r="V65">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="W65">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X65">
+        <v>1.08</v>
+      </c>
+      <c r="Y65">
+        <v>1.54</v>
+      </c>
+      <c r="Z65">
+        <v>2.32</v>
+      </c>
+      <c r="AA65">
+        <v>2.76</v>
+      </c>
+      <c r="AB65">
+        <v>1.39</v>
+      </c>
+      <c r="AC65">
+        <v>6</v>
+      </c>
+      <c r="AD65">
+        <v>1.08</v>
+      </c>
+      <c r="AE65">
         <v>1.01</v>
       </c>
-      <c r="Y65">
-        <v>1.23</v>
-      </c>
-      <c r="Z65">
-        <v>3.6</v>
-      </c>
-      <c r="AA65">
-        <v>1.81</v>
-      </c>
-      <c r="AB65">
-        <v>1.93</v>
-      </c>
-      <c r="AC65">
-        <v>2.85</v>
-      </c>
-      <c r="AD65">
-        <v>1.31</v>
-      </c>
-      <c r="AE65">
-        <v>1.08</v>
-      </c>
       <c r="AF65">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="AG65">
+        <v>1.44</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>1.26</v>
+      </c>
+      <c r="AK65">
         <v>2.1</v>
       </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.25</v>
-      </c>
-      <c r="AK65">
-        <v>1.7</v>
-      </c>
       <c r="AL65">
         <v>0</v>
       </c>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-08-24 20:30:00</t>
+          <t>2026-08-24 20:00:00</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,52 +11067,52 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="O66">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P66">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q66">
-        <v>2.29</v>
+        <v>2.48</v>
       </c>
       <c r="R66">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S66">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="T66">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U66">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="V66">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W66">
         <v>1.1</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
         <v>1.22</v>
       </c>
       <c r="Z66">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="AA66">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AB66">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC66">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD66">
         <v>1.33</v>
@@ -11121,10 +11121,10 @@
         <v>1.08</v>
       </c>
       <c r="AF66">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG66">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK66">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11183,156 +11183,319 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N67">
+        <v>1.7</v>
+      </c>
+      <c r="O67">
+        <v>3.65</v>
+      </c>
+      <c r="P67">
+        <v>4.2</v>
+      </c>
+      <c r="Q67">
+        <v>2.29</v>
+      </c>
+      <c r="R67">
+        <v>2.25</v>
+      </c>
+      <c r="S67">
+        <v>1.3</v>
+      </c>
+      <c r="T67">
+        <v>3.05</v>
+      </c>
+      <c r="U67">
+        <v>2.6</v>
+      </c>
+      <c r="V67">
+        <v>1.42</v>
+      </c>
+      <c r="W67">
+        <v>1.1</v>
+      </c>
+      <c r="X67">
+        <v>1.01</v>
+      </c>
+      <c r="Y67">
+        <v>1.22</v>
+      </c>
+      <c r="Z67">
+        <v>3.7</v>
+      </c>
+      <c r="AA67">
+        <v>1.83</v>
+      </c>
+      <c r="AB67">
+        <v>1.98</v>
+      </c>
+      <c r="AC67">
+        <v>3.08</v>
+      </c>
+      <c r="AD67">
+        <v>1.3</v>
+      </c>
+      <c r="AE67">
+        <v>1.08</v>
+      </c>
+      <c r="AF67">
+        <v>1.78</v>
+      </c>
+      <c r="AG67">
+        <v>2</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>1.2</v>
+      </c>
+      <c r="AK67">
+        <v>2</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>-1</v>
+      </c>
+      <c r="AN67">
+        <v>-1</v>
+      </c>
+      <c r="AO67">
+        <v>-1</v>
+      </c>
+      <c r="AP67">
+        <v>-1</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>0</v>
+      </c>
+      <c r="AS67">
+        <v>0</v>
+      </c>
+      <c r="AT67">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>2026-08-24 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Libertad</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Macará</t>
         </is>
       </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67" t="inlineStr">
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N67">
-        <v>2.95</v>
-      </c>
-      <c r="O67">
+      <c r="N68">
+        <v>2.67</v>
+      </c>
+      <c r="O68">
+        <v>2.9</v>
+      </c>
+      <c r="P68">
+        <v>2.18</v>
+      </c>
+      <c r="Q68">
+        <v>3.56</v>
+      </c>
+      <c r="R68">
+        <v>1.94</v>
+      </c>
+      <c r="S68">
+        <v>1.44</v>
+      </c>
+      <c r="T68">
+        <v>2.5</v>
+      </c>
+      <c r="U68">
+        <v>3.08</v>
+      </c>
+      <c r="V68">
+        <v>1.3</v>
+      </c>
+      <c r="W68">
+        <v>1.03</v>
+      </c>
+      <c r="X68">
+        <v>1.02</v>
+      </c>
+      <c r="Y68">
+        <v>1.36</v>
+      </c>
+      <c r="Z68">
         <v>3.1</v>
       </c>
-      <c r="P67">
+      <c r="AA68">
         <v>2.18</v>
       </c>
-      <c r="Q67">
-        <v>3.78</v>
-      </c>
-      <c r="R67">
-        <v>2.05</v>
-      </c>
-      <c r="S67">
-        <v>1.42</v>
-      </c>
-      <c r="T67">
-        <v>2.5</v>
-      </c>
-      <c r="U67">
-        <v>3.08</v>
-      </c>
-      <c r="V67">
+      <c r="AB68">
+        <v>1.51</v>
+      </c>
+      <c r="AC68">
+        <v>3.82</v>
+      </c>
+      <c r="AD68">
+        <v>1.19</v>
+      </c>
+      <c r="AE68">
+        <v>1.02</v>
+      </c>
+      <c r="AF68">
+        <v>1.83</v>
+      </c>
+      <c r="AG68">
+        <v>1.86</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
         <v>1.3</v>
       </c>
-      <c r="W67">
-        <v>1.03</v>
-      </c>
-      <c r="X67">
-        <v>1.06</v>
-      </c>
-      <c r="Y67">
+      <c r="AK68">
         <v>1.36</v>
       </c>
-      <c r="Z67">
-        <v>3.1</v>
-      </c>
-      <c r="AA67">
-        <v>2.15</v>
-      </c>
-      <c r="AB67">
-        <v>1.62</v>
-      </c>
-      <c r="AC67">
-        <v>3.82</v>
-      </c>
-      <c r="AD67">
-        <v>1.19</v>
-      </c>
-      <c r="AE67">
-        <v>1.02</v>
-      </c>
-      <c r="AF67">
-        <v>1.83</v>
-      </c>
-      <c r="AG67">
-        <v>1.83</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.3</v>
-      </c>
-      <c r="AK67">
-        <v>1.36</v>
-      </c>
-      <c r="AL67">
-        <v>0</v>
-      </c>
-      <c r="AM67">
-        <v>-1</v>
-      </c>
-      <c r="AN67">
-        <v>-1</v>
-      </c>
-      <c r="AO67">
-        <v>-1</v>
-      </c>
-      <c r="AP67">
-        <v>-1</v>
-      </c>
-      <c r="AQ67">
-        <v>0</v>
-      </c>
-      <c r="AR67">
-        <v>0</v>
-      </c>
-      <c r="AS67">
-        <v>0</v>
-      </c>
-      <c r="AT67">
-        <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
+      <c r="AL68">
+        <v>0</v>
+      </c>
+      <c r="AM68">
+        <v>-1</v>
+      </c>
+      <c r="AN68">
+        <v>-1</v>
+      </c>
+      <c r="AO68">
+        <v>-1</v>
+      </c>
+      <c r="AP68">
+        <v>-1</v>
+      </c>
+      <c r="AQ68">
+        <v>0</v>
+      </c>
+      <c r="AR68">
+        <v>0</v>
+      </c>
+      <c r="AS68">
+        <v>0</v>
+      </c>
+      <c r="AT68">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
         <is>
           <t>2026-08-24 21:00:00</t>
         </is>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -801,22 +801,22 @@
         <v>2.45</v>
       </c>
       <c r="O3">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P3">
+        <v>2.7</v>
+      </c>
+      <c r="Q3">
+        <v>3.1</v>
+      </c>
+      <c r="R3">
+        <v>2</v>
+      </c>
+      <c r="S3">
+        <v>1.42</v>
+      </c>
+      <c r="T3">
         <v>2.65</v>
-      </c>
-      <c r="Q3">
-        <v>3.14</v>
-      </c>
-      <c r="R3">
-        <v>1.89</v>
-      </c>
-      <c r="S3">
-        <v>1.48</v>
-      </c>
-      <c r="T3">
-        <v>2.36</v>
       </c>
       <c r="U3">
         <v>3.08</v>
@@ -825,37 +825,37 @@
         <v>1.29</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z3">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="AA3">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AB3">
         <v>1.64</v>
       </c>
       <c r="AC3">
-        <v>3.78</v>
+        <v>3.72</v>
       </c>
       <c r="AD3">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE3">
         <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG3">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -967,25 +967,25 @@
         <v>3.45</v>
       </c>
       <c r="P4">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="Q4">
-        <v>4.65</v>
+        <v>4.01</v>
       </c>
       <c r="R4">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="S4">
         <v>1.41</v>
       </c>
       <c r="T4">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="U4">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="V4">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
         <v>1.03</v>
@@ -997,16 +997,16 @@
         <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>2.97</v>
+        <v>3.23</v>
       </c>
       <c r="AA4">
         <v>2.09</v>
       </c>
       <c r="AB4">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AC4">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD4">
         <v>1.22</v>
@@ -1015,10 +1015,10 @@
         <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG4">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1142,46 +1142,46 @@
         <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="V5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
         <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z5">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB5">
         <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD5">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE5">
         <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK5">
         <v>2.03</v>
@@ -1296,7 +1296,7 @@
         <v>2.9</v>
       </c>
       <c r="Q6">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="R6">
         <v>1.95</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="O7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P7">
-        <v>5.25</v>
+        <v>2.85</v>
       </c>
       <c r="Q7">
-        <v>1.92</v>
+        <v>3.02</v>
       </c>
       <c r="R7">
-        <v>2.55</v>
+        <v>2.02</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="V7">
+        <v>1.29</v>
+      </c>
+      <c r="W7">
+        <v>1.03</v>
+      </c>
+      <c r="X7">
+        <v>1.05</v>
+      </c>
+      <c r="Y7">
+        <v>1.36</v>
+      </c>
+      <c r="Z7">
+        <v>2.88</v>
+      </c>
+      <c r="AA7">
+        <v>2.25</v>
+      </c>
+      <c r="AB7">
+        <v>1.57</v>
+      </c>
+      <c r="AC7">
+        <v>4.1</v>
+      </c>
+      <c r="AD7">
+        <v>1.17</v>
+      </c>
+      <c r="AE7">
+        <v>1.03</v>
+      </c>
+      <c r="AF7">
+        <v>1.91</v>
+      </c>
+      <c r="AG7">
+        <v>1.78</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.33</v>
+      </c>
+      <c r="AK7">
         <v>1.5</v>
-      </c>
-      <c r="W7">
-        <v>1.13</v>
-      </c>
-      <c r="X7">
-        <v>1.01</v>
-      </c>
-      <c r="Y7">
-        <v>1.17</v>
-      </c>
-      <c r="Z7">
-        <v>4.5</v>
-      </c>
-      <c r="AA7">
-        <v>1.6</v>
-      </c>
-      <c r="AB7">
-        <v>2.2</v>
-      </c>
-      <c r="AC7">
-        <v>2.75</v>
-      </c>
-      <c r="AD7">
-        <v>1.42</v>
-      </c>
-      <c r="AE7">
-        <v>1.14</v>
-      </c>
-      <c r="AF7">
-        <v>1.79</v>
-      </c>
-      <c r="AG7">
-        <v>1.92</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.1</v>
-      </c>
-      <c r="AK7">
-        <v>2.5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.3</v>
+        <v>1.46</v>
       </c>
       <c r="O8">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="P8">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="Q8">
-        <v>3.13</v>
+        <v>1.95</v>
       </c>
       <c r="R8">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="S8">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="T8">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="U8">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="V8">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="Z8">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="AA8">
+        <v>1.5</v>
+      </c>
+      <c r="AB8">
+        <v>2.4</v>
+      </c>
+      <c r="AC8">
         <v>2.25</v>
       </c>
-      <c r="AB8">
-        <v>1.57</v>
-      </c>
-      <c r="AC8">
-        <v>4.5</v>
-      </c>
       <c r="AD8">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AE8">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AF8">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AG8">
-        <v>1.78</v>
+        <v>2.17</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>1.5</v>
+        <v>2.44</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O9">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P9">
-        <v>5.45</v>
+        <v>5.8</v>
       </c>
       <c r="Q9">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R9">
         <v>2.03</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1945,46 +1945,46 @@
         <v>3.7</v>
       </c>
       <c r="P10">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q10">
         <v>2.1</v>
       </c>
       <c r="R10">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="S10">
         <v>1.32</v>
       </c>
       <c r="T10">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W10">
         <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z10">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AA10">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
         <v>2.05</v>
       </c>
       <c r="AC10">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="AD10">
         <v>1.36</v>
@@ -1993,7 +1993,7 @@
         <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AG10">
         <v>1.9</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK10">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>1.51</v>
       </c>
       <c r="O11">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P11">
         <v>5</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB11">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="O12">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q12">
-        <v>2.33</v>
+        <v>3.24</v>
       </c>
       <c r="R12">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="T12">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="U12">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="V12">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z12">
-        <v>3.82</v>
+        <v>2.88</v>
       </c>
       <c r="AA12">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AC12">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="AD12">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AE12">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AK12">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="O13">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q13">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R13">
         <v>2.1</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="U13">
         <v>2.88</v>
@@ -2461,31 +2461,31 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z13">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA13">
         <v>2</v>
       </c>
       <c r="AB13">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC13">
         <v>3.5</v>
       </c>
       <c r="AD13">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE13">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AG13">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="AK13">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>2.24</v>
+        <v>3.72</v>
       </c>
       <c r="Q14">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="R14">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="S14">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
-        <v>2.92</v>
+        <v>2.38</v>
       </c>
       <c r="V14">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z14">
-        <v>2.97</v>
+        <v>3.84</v>
       </c>
       <c r="AA14">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB14">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AC14">
-        <v>3.48</v>
+        <v>2.75</v>
       </c>
       <c r="AD14">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AE14">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF14">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AG14">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK14">
-        <v>1.31</v>
+        <v>1.85</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2926,7 +2926,7 @@
         <v>3</v>
       </c>
       <c r="Q16">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="R16">
         <v>1.67</v>
@@ -2938,7 +2938,7 @@
         <v>1.93</v>
       </c>
       <c r="U16">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="V16">
         <v>1.12</v>
@@ -2950,19 +2950,19 @@
         <v>1.14</v>
       </c>
       <c r="Y16">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Z16">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AA16">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AB16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AC16">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD16">
         <v>1.02</v>
@@ -2971,10 +2971,10 @@
         <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="AG16">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AK16">
         <v>1.4</v>
@@ -3086,7 +3086,7 @@
         <v>3.02</v>
       </c>
       <c r="P17">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3252,10 +3252,10 @@
         <v>2.04</v>
       </c>
       <c r="Q18">
-        <v>3.65</v>
+        <v>4.26</v>
       </c>
       <c r="R18">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
         <v>1.41</v>
@@ -3282,10 +3282,10 @@
         <v>2.97</v>
       </c>
       <c r="AA18">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AB18">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC18">
         <v>3.34</v>
@@ -3297,7 +3297,7 @@
         <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG18">
         <v>1.9</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.77</v>
       </c>
       <c r="AK18">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,22 +3409,22 @@
         <v>2.88</v>
       </c>
       <c r="O19">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P19">
         <v>2.3</v>
       </c>
       <c r="Q19">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="R19">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="S19">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="T19">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="U19">
         <v>3.22</v>
@@ -3445,16 +3445,16 @@
         <v>2.66</v>
       </c>
       <c r="AA19">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AB19">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC19">
         <v>3.92</v>
       </c>
       <c r="AD19">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE19">
         <v>1.03</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AK19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>3.1</v>
       </c>
       <c r="P21">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="P22">
-        <v>3.08</v>
+        <v>3.65</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
@@ -3913,7 +3913,7 @@
         <v>1.51</v>
       </c>
       <c r="T22">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U22">
         <v>3.28</v>
@@ -3922,10 +3922,10 @@
         <v>1.33</v>
       </c>
       <c r="W22">
+        <v>1.03</v>
+      </c>
+      <c r="X22">
         <v>1.04</v>
-      </c>
-      <c r="X22">
-        <v>1.06</v>
       </c>
       <c r="Y22">
         <v>1.38</v>
@@ -3934,13 +3934,13 @@
         <v>2.77</v>
       </c>
       <c r="AA22">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB22">
         <v>1.62</v>
       </c>
       <c r="AC22">
-        <v>4.2</v>
+        <v>3.86</v>
       </c>
       <c r="AD22">
         <v>1.22</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AK22">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,52 +4058,52 @@
         </is>
       </c>
       <c r="N23">
-        <v>4.92</v>
+        <v>5.05</v>
       </c>
       <c r="O23">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="P23">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="Q23">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="R23">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U23">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="V23">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="AA23">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AB23">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC23">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AD23">
         <v>1.57</v>
@@ -4115,7 +4115,7 @@
         <v>1.55</v>
       </c>
       <c r="AG23">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
+        <v>2.25</v>
+      </c>
+      <c r="AK23">
         <v>1.17</v>
-      </c>
-      <c r="AK23">
-        <v>1.15</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,34 +4221,34 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O24">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
         <v>1.8</v>
       </c>
       <c r="Q24">
-        <v>4.19</v>
+        <v>3.6</v>
       </c>
       <c r="R24">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T24">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U24">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W24">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4257,19 +4257,19 @@
         <v>1.15</v>
       </c>
       <c r="Z24">
-        <v>4.6</v>
+        <v>4.53</v>
       </c>
       <c r="AA24">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB24">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AC24">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AD24">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE24">
         <v>1.16</v>
@@ -4278,7 +4278,7 @@
         <v>1.55</v>
       </c>
       <c r="AG24">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,58 +4384,58 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="O25">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="P25">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="Q25">
-        <v>2.49</v>
+        <v>3.16</v>
       </c>
       <c r="R25">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="S25">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="T25">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U25">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V25">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y25">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z25">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AA25">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AB25">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AC25">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AD25">
         <v>1.16</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF25">
         <v>1.95</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK25">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,22 +4550,22 @@
         <v>1.27</v>
       </c>
       <c r="O26">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="P26">
-        <v>8.460000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="Q26">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="R26">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="S26">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="U26">
         <v>2.69</v>
@@ -4580,25 +4580,25 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z26">
-        <v>3.34</v>
+        <v>3.57</v>
       </c>
       <c r="AA26">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB26">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AC26">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AD26">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF26">
         <v>2.33</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK26">
-        <v>3.38</v>
+        <v>2.99</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O29">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q29">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R29">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S29">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T29">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="U29">
         <v>2.41</v>
@@ -5063,7 +5063,7 @@
         <v>1.49</v>
       </c>
       <c r="W29">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X29">
         <v>1</v>
@@ -5072,22 +5072,22 @@
         <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.33</v>
+        <v>3.95</v>
       </c>
       <c r="AA29">
         <v>1.66</v>
       </c>
       <c r="AB29">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC29">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="AD29">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE29">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
         <v>1.53</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AK29">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,22 +5199,22 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3.69</v>
+        <v>3.55</v>
       </c>
       <c r="Q30">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="R30">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
         <v>3.1</v>
@@ -5226,37 +5226,37 @@
         <v>1.44</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AA30">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AB30">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC30">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AD30">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE30">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AG30">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="O31">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="Q31">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="R31">
         <v>2.5</v>
       </c>
       <c r="S31">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="U31">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="V31">
         <v>1.58</v>
       </c>
       <c r="W31">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA31">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB31">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AC31">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AD31">
         <v>1.5</v>
       </c>
       <c r="AE31">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF31">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AG31">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
+        <v>1.29</v>
+      </c>
+      <c r="AK31">
         <v>1.44</v>
-      </c>
-      <c r="AK31">
-        <v>1.5</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O32">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q32">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="R32">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>2.91</v>
+        <v>3.29</v>
       </c>
       <c r="U32">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z32">
-        <v>3.88</v>
+        <v>3.55</v>
       </c>
       <c r="AA32">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB32">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AC32">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG32">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK32">
         <v>2</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="O34">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="P34">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Q34">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R34">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T34">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="U34">
         <v>2.12</v>
       </c>
       <c r="V34">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W34">
         <v>1.14</v>
@@ -5884,31 +5884,31 @@
         <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA34">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB34">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AC34">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AD34">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE34">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF34">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AK34">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,34 +6014,34 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="O35">
         <v>4.25</v>
       </c>
       <c r="P35">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q35">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="R35">
         <v>2.38</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T35">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V35">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W35">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
         <v>1.01</v>
@@ -6053,19 +6053,19 @@
         <v>5</v>
       </c>
       <c r="AA35">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AB35">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AC35">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AD35">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AE35">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF35">
         <v>1.57</v>
@@ -6087,7 +6087,7 @@
         <v>1.19</v>
       </c>
       <c r="AK35">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,46 +6180,46 @@
         <v>1.83</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="P36">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q36">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="R36">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
         <v>1.41</v>
       </c>
       <c r="T36">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U36">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W36">
         <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y36">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z36">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AA36">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AB36">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC36">
         <v>3.45</v>
@@ -6231,10 +6231,10 @@
         <v>1.1</v>
       </c>
       <c r="AF36">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG36">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,61 +6343,61 @@
         <v>2.02</v>
       </c>
       <c r="O37">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="P37">
         <v>3.35</v>
       </c>
       <c r="Q37">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S37">
+        <v>1.58</v>
+      </c>
+      <c r="T37">
+        <v>2.4</v>
+      </c>
+      <c r="U37">
+        <v>3.31</v>
+      </c>
+      <c r="V37">
+        <v>1.33</v>
+      </c>
+      <c r="W37">
+        <v>1.01</v>
+      </c>
+      <c r="X37">
+        <v>1.06</v>
+      </c>
+      <c r="Y37">
+        <v>1.46</v>
+      </c>
+      <c r="Z37">
+        <v>2.66</v>
+      </c>
+      <c r="AA37">
+        <v>2.58</v>
+      </c>
+      <c r="AB37">
         <v>1.53</v>
       </c>
-      <c r="T37">
-        <v>2.43</v>
-      </c>
-      <c r="U37">
-        <v>3.38</v>
-      </c>
-      <c r="V37">
-        <v>1.32</v>
-      </c>
-      <c r="W37">
-        <v>1.03</v>
-      </c>
-      <c r="X37">
-        <v>1.05</v>
-      </c>
-      <c r="Y37">
-        <v>1.43</v>
-      </c>
-      <c r="Z37">
-        <v>2.62</v>
-      </c>
-      <c r="AA37">
-        <v>2.43</v>
-      </c>
-      <c r="AB37">
-        <v>1.6</v>
-      </c>
       <c r="AC37">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD37">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF37">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AG37">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AK37">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="O38">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="P38">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O39">
         <v>3.15</v>
       </c>
       <c r="P39">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q39">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="R39">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
         <v>1.35</v>
@@ -6687,10 +6687,10 @@
         <v>2.9</v>
       </c>
       <c r="U39">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="V39">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W39">
         <v>1.07</v>
@@ -6711,7 +6711,7 @@
         <v>1.85</v>
       </c>
       <c r="AC39">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AD39">
         <v>1.31</v>
@@ -6720,10 +6720,10 @@
         <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AG39">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.38</v>
       </c>
       <c r="AK39">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="O40">
         <v>4.2</v>
@@ -6841,19 +6841,19 @@
         <v>4.6</v>
       </c>
       <c r="R40">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="S40">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="T40">
         <v>3.68</v>
       </c>
       <c r="U40">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="V40">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W40">
         <v>1.15</v>
@@ -6862,31 +6862,31 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA40">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AB40">
         <v>2.63</v>
       </c>
       <c r="AC40">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AD40">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE40">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF40">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AG40">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6995,31 +6995,31 @@
         <v>1.61</v>
       </c>
       <c r="O41">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P41">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q41">
         <v>2.05</v>
       </c>
       <c r="R41">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="S41">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T41">
-        <v>3.68</v>
+        <v>4.5</v>
       </c>
       <c r="U41">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="V41">
         <v>1.71</v>
       </c>
       <c r="W41">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7034,13 +7034,13 @@
         <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AC41">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AD41">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AE41">
         <v>1.28</v>
@@ -7049,7 +7049,7 @@
         <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK41">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AK42">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7324,49 +7324,49 @@
         <v>2.9</v>
       </c>
       <c r="P43">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q43">
         <v>2.78</v>
       </c>
       <c r="R43">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="S43">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="T43">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="U43">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="V43">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W43">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X43">
         <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z43">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AA43">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="AB43">
         <v>1.57</v>
       </c>
       <c r="AC43">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD43">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE43">
         <v>1.03</v>
@@ -7487,7 +7487,7 @@
         <v>3.18</v>
       </c>
       <c r="P44">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q44">
         <v>2.8</v>
@@ -7499,13 +7499,13 @@
         <v>1.4</v>
       </c>
       <c r="T44">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="U44">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="V44">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W44">
         <v>1.03</v>
@@ -7520,7 +7520,7 @@
         <v>3.1</v>
       </c>
       <c r="AA44">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AB44">
         <v>1.7</v>
@@ -7532,13 +7532,13 @@
         <v>1.25</v>
       </c>
       <c r="AE44">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF44">
         <v>1.83</v>
       </c>
       <c r="AG44">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,28 +7644,28 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O45">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P45">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q45">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R45">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="S45">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T45">
-        <v>3.09</v>
+        <v>2.88</v>
       </c>
       <c r="U45">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="V45">
         <v>1.42</v>
@@ -7674,34 +7674,34 @@
         <v>1.05</v>
       </c>
       <c r="X45">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z45">
-        <v>3.63</v>
+        <v>3.2</v>
       </c>
       <c r="AA45">
         <v>1.83</v>
       </c>
       <c r="AB45">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AC45">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD45">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE45">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF45">
         <v>1.67</v>
       </c>
       <c r="AG45">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.25</v>
       </c>
       <c r="AK45">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,61 +7807,61 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="O46">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="P46">
         <v>3</v>
       </c>
       <c r="Q46">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="R46">
         <v>1.91</v>
       </c>
       <c r="S46">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T46">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="U46">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V46">
         <v>1.25</v>
       </c>
       <c r="W46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X46">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y46">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Z46">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AA46">
         <v>2.5</v>
       </c>
       <c r="AB46">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AC46">
         <v>5</v>
       </c>
       <c r="AD46">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE46">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF46">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AG46">
         <v>1.75</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK46">
         <v>1.5</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="O47">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P47">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="Q47">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S47">
         <v>1.3</v>
@@ -7991,28 +7991,28 @@
         <v>3.22</v>
       </c>
       <c r="U47">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V47">
         <v>1.37</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z47">
-        <v>3.54</v>
+        <v>3.05</v>
       </c>
       <c r="AA47">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AB47">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC47">
         <v>3.25</v>
@@ -8021,13 +8021,13 @@
         <v>1.3</v>
       </c>
       <c r="AE47">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF47">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG47">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK47">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="O48">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
-        <v>5.35</v>
+        <v>4.1</v>
       </c>
       <c r="Q48">
         <v>2.1</v>
       </c>
       <c r="R48">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="S48">
         <v>1.39</v>
@@ -8154,7 +8154,7 @@
         <v>3.2</v>
       </c>
       <c r="U48">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="V48">
         <v>1.41</v>
@@ -8166,28 +8166,28 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z48">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA48">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB48">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC48">
         <v>3.2</v>
       </c>
       <c r="AD48">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AE48">
         <v>1.1</v>
       </c>
       <c r="AF48">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG48">
         <v>1.83</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK48">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8308,25 +8308,25 @@
         <v>2.85</v>
       </c>
       <c r="R49">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S49">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T49">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U49">
         <v>2.88</v>
       </c>
       <c r="V49">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W49">
         <v>1.02</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
         <v>1.3</v>
@@ -8335,25 +8335,25 @@
         <v>3.2</v>
       </c>
       <c r="AA49">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB49">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC49">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AD49">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE49">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG49">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,31 +8459,31 @@
         </is>
       </c>
       <c r="N50">
+        <v>3.8</v>
+      </c>
+      <c r="O50">
         <v>3.6</v>
       </c>
-      <c r="O50">
-        <v>3.75</v>
-      </c>
       <c r="P50">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q50">
-        <v>4.3</v>
+        <v>3.53</v>
       </c>
       <c r="R50">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.48</v>
+        <v>2.31</v>
       </c>
       <c r="V50">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W50">
         <v>1.1</v>
@@ -8492,31 +8492,31 @@
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z50">
         <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AB50">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="AC50">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="AD50">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE50">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
         <v>1.28</v>
@@ -8631,16 +8631,16 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="R51">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="S51">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="T51">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U51">
         <v>4</v>
@@ -8652,28 +8652,28 @@
         <v>1.03</v>
       </c>
       <c r="X51">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y51">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="Z51">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AA51">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AB51">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC51">
         <v>6.5</v>
       </c>
       <c r="AD51">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE51">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF51">
         <v>2.25</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AK51">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,16 +8794,16 @@
         <v>3.8</v>
       </c>
       <c r="Q52">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="R52">
         <v>2.2</v>
       </c>
       <c r="S52">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T52">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U52">
         <v>2.83</v>
@@ -8818,28 +8818,28 @@
         <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z52">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA52">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB52">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AC52">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD52">
         <v>1.25</v>
       </c>
       <c r="AE52">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF52">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG52">
         <v>1.89</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="O53">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="P53">
-        <v>7.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q53">
         <v>2.1</v>
@@ -8963,19 +8963,19 @@
         <v>2.12</v>
       </c>
       <c r="S53">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T53">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="U53">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="V53">
         <v>1.34</v>
       </c>
       <c r="W53">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
         <v>1.02</v>
@@ -8990,22 +8990,22 @@
         <v>1.97</v>
       </c>
       <c r="AB53">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC53">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD53">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE53">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF53">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG53">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK53">
         <v>2.3</v>
@@ -9120,43 +9120,43 @@
         <v>2.28</v>
       </c>
       <c r="Q54">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="R54">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="S54">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="T54">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="U54">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V54">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W54">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X54">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y54">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="Z54">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="AA54">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AB54">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AC54">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AD54">
         <v>1.13</v>
@@ -9165,10 +9165,10 @@
         <v>1.04</v>
       </c>
       <c r="AF54">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG54">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9277,10 +9277,10 @@
         <v>2.2</v>
       </c>
       <c r="O55">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P55">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB55">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC55">
         <v>0</v>
@@ -9437,28 +9437,28 @@
         </is>
       </c>
       <c r="N56">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="O56">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P56">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q56">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="R56">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S56">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T56">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="U56">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="V56">
         <v>1.31</v>
@@ -9467,34 +9467,34 @@
         <v>1.01</v>
       </c>
       <c r="X56">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z56">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AA56">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AB56">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AC56">
-        <v>4.16</v>
+        <v>4.33</v>
       </c>
       <c r="AD56">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE56">
         <v>1.01</v>
       </c>
       <c r="AF56">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG56">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK56">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,22 +9600,22 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O57">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P57">
         <v>2.3</v>
       </c>
       <c r="Q57">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R57">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="S57">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T57">
         <v>4.45</v>
@@ -9627,37 +9627,37 @@
         <v>1.87</v>
       </c>
       <c r="W57">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X57">
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z57">
         <v>7.5</v>
       </c>
       <c r="AA57">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AB57">
-        <v>3.35</v>
+        <v>2.63</v>
       </c>
       <c r="AC57">
-        <v>1.59</v>
+        <v>1.79</v>
       </c>
       <c r="AD57">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE57">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AF57">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AG57">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9769,28 +9769,28 @@
         <v>3.2</v>
       </c>
       <c r="P58">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="Q58">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="R58">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S58">
         <v>1.47</v>
       </c>
       <c r="T58">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="U58">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="V58">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W58">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X58">
         <v>1.05</v>
@@ -9799,25 +9799,25 @@
         <v>1.41</v>
       </c>
       <c r="Z58">
-        <v>2.61</v>
+        <v>2.96</v>
       </c>
       <c r="AA58">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AB58">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AC58">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD58">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE58">
         <v>1.06</v>
       </c>
       <c r="AF58">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG58">
         <v>1.7</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="O59">
         <v>3</v>
       </c>
       <c r="P59">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="Q59">
         <v>3.6</v>
@@ -9962,28 +9962,28 @@
         <v>1.36</v>
       </c>
       <c r="Z59">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="AA59">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AB59">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC59">
-        <v>3.98</v>
+        <v>4.66</v>
       </c>
       <c r="AD59">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE59">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF59">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG59">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AK59">
         <v>1.36</v>
@@ -10098,19 +10098,19 @@
         <v>3.1</v>
       </c>
       <c r="Q60">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="R60">
         <v>1.87</v>
       </c>
       <c r="S60">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="T60">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U60">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V60">
         <v>1.28</v>
@@ -10119,50 +10119,50 @@
         <v>1.02</v>
       </c>
       <c r="X60">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y60">
+        <v>1.52</v>
+      </c>
+      <c r="Z60">
+        <v>2.57</v>
+      </c>
+      <c r="AA60">
+        <v>2.55</v>
+      </c>
+      <c r="AB60">
+        <v>1.49</v>
+      </c>
+      <c r="AC60">
+        <v>5.25</v>
+      </c>
+      <c r="AD60">
+        <v>1.14</v>
+      </c>
+      <c r="AE60">
+        <v>1.03</v>
+      </c>
+      <c r="AF60">
+        <v>2.06</v>
+      </c>
+      <c r="AG60">
+        <v>1.7</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ60">
+        <v>1.37</v>
+      </c>
+      <c r="AK60">
         <v>1.5</v>
-      </c>
-      <c r="Z60">
-        <v>2.5</v>
-      </c>
-      <c r="AA60">
-        <v>2.5</v>
-      </c>
-      <c r="AB60">
-        <v>1.53</v>
-      </c>
-      <c r="AC60">
-        <v>5</v>
-      </c>
-      <c r="AD60">
-        <v>1.17</v>
-      </c>
-      <c r="AE60">
-        <v>1.05</v>
-      </c>
-      <c r="AF60">
-        <v>2.05</v>
-      </c>
-      <c r="AG60">
-        <v>1.67</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ60">
-        <v>1.36</v>
-      </c>
-      <c r="AK60">
-        <v>1.44</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="O61">
-        <v>2.8</v>
+        <v>3.55</v>
       </c>
       <c r="P61">
-        <v>2.33</v>
+        <v>4.94</v>
       </c>
       <c r="Q61">
-        <v>3.36</v>
+        <v>2.25</v>
       </c>
       <c r="R61">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="S61">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="T61">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="U61">
-        <v>3.35</v>
+        <v>2.81</v>
       </c>
       <c r="V61">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="W61">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X61">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="Z61">
-        <v>2.46</v>
+        <v>3.14</v>
       </c>
       <c r="AA61">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AB61">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AC61">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD61">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AE61">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF61">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AG61">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AK61">
-        <v>1.31</v>
+        <v>2.16</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="O62">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="P62">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q62">
-        <v>2.11</v>
+        <v>3.45</v>
       </c>
       <c r="R62">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="S62">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="T62">
-        <v>2.73</v>
+        <v>2.29</v>
       </c>
       <c r="U62">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="V62">
+        <v>1.3</v>
+      </c>
+      <c r="W62">
+        <v>1.01</v>
+      </c>
+      <c r="X62">
+        <v>1.06</v>
+      </c>
+      <c r="Y62">
+        <v>1.48</v>
+      </c>
+      <c r="Z62">
+        <v>2.6</v>
+      </c>
+      <c r="AA62">
+        <v>2.4</v>
+      </c>
+      <c r="AB62">
+        <v>1.53</v>
+      </c>
+      <c r="AC62">
+        <v>4.94</v>
+      </c>
+      <c r="AD62">
+        <v>1.18</v>
+      </c>
+      <c r="AE62">
+        <v>1.01</v>
+      </c>
+      <c r="AF62">
+        <v>2.01</v>
+      </c>
+      <c r="AG62">
+        <v>1.72</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>1.35</v>
+      </c>
+      <c r="AK62">
         <v>1.36</v>
-      </c>
-      <c r="W62">
-        <v>1.04</v>
-      </c>
-      <c r="X62">
-        <v>1.01</v>
-      </c>
-      <c r="Y62">
-        <v>1.32</v>
-      </c>
-      <c r="Z62">
-        <v>3.39</v>
-      </c>
-      <c r="AA62">
-        <v>2.02</v>
-      </c>
-      <c r="AB62">
-        <v>1.83</v>
-      </c>
-      <c r="AC62">
-        <v>3.54</v>
-      </c>
-      <c r="AD62">
-        <v>1.25</v>
-      </c>
-      <c r="AE62">
-        <v>1.05</v>
-      </c>
-      <c r="AF62">
-        <v>1.9</v>
-      </c>
-      <c r="AG62">
-        <v>1.8</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.2</v>
-      </c>
-      <c r="AK62">
-        <v>2.12</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="O63">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="P63">
         <v>3.44</v>
@@ -10590,10 +10590,10 @@
         <v>2.62</v>
       </c>
       <c r="R63">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S63">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="T63">
         <v>2.7</v>
@@ -10608,34 +10608,34 @@
         <v>1.07</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y63">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z63">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA63">
         <v>2.05</v>
       </c>
       <c r="AB63">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AC63">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="AD63">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE63">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF63">
         <v>1.83</v>
       </c>
       <c r="AG63">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK63">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10744,19 +10744,19 @@
         <v>1.44</v>
       </c>
       <c r="O64">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P64">
         <v>5.5</v>
       </c>
       <c r="Q64">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="R64">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="S64">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
         <v>3.6</v>
@@ -10765,25 +10765,25 @@
         <v>2.15</v>
       </c>
       <c r="V64">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W64">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X64">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y64">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z64">
-        <v>4.55</v>
+        <v>4.71</v>
       </c>
       <c r="AA64">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB64">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AC64">
         <v>2.46</v>
@@ -10792,13 +10792,13 @@
         <v>1.56</v>
       </c>
       <c r="AE64">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF64">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG64">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O65">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P65">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q65">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R65">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S65">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="T65">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="U65">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="V65">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="W65">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X65">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Y65">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Z65">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="AA65">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="AB65">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AC65">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD65">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF65">
-        <v>2.5</v>
+        <v>2.93</v>
       </c>
       <c r="AG65">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK65">
         <v>2.1</v>
@@ -11082,22 +11082,22 @@
         <v>2.2</v>
       </c>
       <c r="S66">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T66">
         <v>2.82</v>
       </c>
       <c r="U66">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="V66">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W66">
         <v>1.1</v>
       </c>
       <c r="X66">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
         <v>1.22</v>
@@ -11112,19 +11112,19 @@
         <v>1.93</v>
       </c>
       <c r="AC66">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD66">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE66">
         <v>1.08</v>
       </c>
       <c r="AF66">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG66">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11236,22 +11236,22 @@
         <v>3.65</v>
       </c>
       <c r="P67">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="Q67">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="R67">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S67">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T67">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U67">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="V67">
         <v>1.42</v>
@@ -11263,31 +11263,31 @@
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z67">
         <v>3.7</v>
       </c>
       <c r="AA67">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB67">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC67">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AD67">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE67">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF67">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG67">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.2</v>
       </c>
       <c r="AK67">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,37 +11393,37 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.67</v>
+        <v>2.97</v>
       </c>
       <c r="O68">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P68">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="Q68">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="R68">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S68">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T68">
         <v>2.5</v>
       </c>
       <c r="U68">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="V68">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W68">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y68">
         <v>1.36</v>
@@ -11432,13 +11432,13 @@
         <v>3.1</v>
       </c>
       <c r="AA68">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AB68">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AC68">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AD68">
         <v>1.19</v>
@@ -11447,10 +11447,10 @@
         <v>1.02</v>
       </c>
       <c r="AF68">
+        <v>1.85</v>
+      </c>
+      <c r="AG68">
         <v>1.83</v>
-      </c>
-      <c r="AG68">
-        <v>1.86</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.3</v>
       </c>
       <c r="AK68">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL68">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -612,36 +612,36 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "89"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "76"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -798,28 +798,28 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="O3">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P3">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q3">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R3">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S3">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T3">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="U3">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="V3">
         <v>1.29</v>
@@ -828,34 +828,34 @@
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z3">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="AA3">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AB3">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AC3">
-        <v>3.72</v>
+        <v>4.32</v>
       </c>
       <c r="AD3">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG3">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK3">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="O4">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q4">
-        <v>4.01</v>
+        <v>4.1</v>
       </c>
       <c r="R4">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="S4">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T4">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="U4">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="V4">
+        <v>1.35</v>
+      </c>
+      <c r="W4">
+        <v>1.02</v>
+      </c>
+      <c r="X4">
+        <v>1.02</v>
+      </c>
+      <c r="Y4">
         <v>1.36</v>
       </c>
-      <c r="W4">
+      <c r="Z4">
+        <v>3.15</v>
+      </c>
+      <c r="AA4">
+        <v>2.15</v>
+      </c>
+      <c r="AB4">
+        <v>1.69</v>
+      </c>
+      <c r="AC4">
+        <v>3.82</v>
+      </c>
+      <c r="AD4">
+        <v>1.26</v>
+      </c>
+      <c r="AE4">
         <v>1.03</v>
       </c>
-      <c r="X4">
-        <v>1.01</v>
-      </c>
-      <c r="Y4">
-        <v>1.3</v>
-      </c>
-      <c r="Z4">
-        <v>3.23</v>
-      </c>
-      <c r="AA4">
-        <v>2.09</v>
-      </c>
-      <c r="AB4">
-        <v>1.73</v>
-      </c>
-      <c r="AC4">
-        <v>3.7</v>
-      </c>
-      <c r="AD4">
-        <v>1.22</v>
-      </c>
-      <c r="AE4">
-        <v>1.04</v>
-      </c>
       <c r="AF4">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG4">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK4">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P6">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q6">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R6">
         <v>1.95</v>
@@ -1332,19 +1332,19 @@
         <v>1.55</v>
       </c>
       <c r="AC6">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AD6">
         <v>1.14</v>
       </c>
       <c r="AE6">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AG6">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1442,115 +1442,115 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="P7">
-        <v>2.85</v>
+        <v>5.35</v>
       </c>
       <c r="Q7">
-        <v>3.02</v>
+        <v>1.93</v>
       </c>
       <c r="R7">
-        <v>2.02</v>
+        <v>2.39</v>
       </c>
       <c r="S7">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="U7">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z7">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="AA7">
+        <v>1.57</v>
+      </c>
+      <c r="AB7">
         <v>2.25</v>
       </c>
-      <c r="AB7">
-        <v>1.57</v>
-      </c>
       <c r="AC7">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="AD7">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="AE7">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AF7">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="AG7">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AK7">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1581,139 +1581,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>1.46</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>5.1</v>
+        <v>3</v>
       </c>
       <c r="Q8">
-        <v>1.95</v>
+        <v>2.79</v>
       </c>
       <c r="R8">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="S8">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="T8">
-        <v>3.8</v>
+        <v>2.39</v>
       </c>
       <c r="U8">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="V8">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="Z8">
-        <v>5.5</v>
+        <v>2.61</v>
       </c>
       <c r="AA8">
-        <v>1.5</v>
+        <v>2.31</v>
       </c>
       <c r="AB8">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC8">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="AD8">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="AE8">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>1.63</v>
+        <v>1.96</v>
       </c>
       <c r="AG8">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52", "90+1"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>2.44</v>
+        <v>1.58</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O9">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="P9">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="Q9">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="R9">
         <v>2.03</v>
       </c>
       <c r="S9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T9">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="U9">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="V9">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
         <v>1.02</v>
       </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
       <c r="Y9">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z9">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="AA9">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AB9">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC9">
-        <v>3.72</v>
+        <v>3.92</v>
       </c>
       <c r="AD9">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AG9">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK9">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,61 +1939,61 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
         <v>3.7</v>
       </c>
       <c r="P10">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q10">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="S10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U10">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="V10">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
         <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
         <v>3.9</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB10">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC10">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="AD10">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE10">
         <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AG10">
         <v>1.9</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK10">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,61 +2105,61 @@
         <v>1.51</v>
       </c>
       <c r="O11">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P11">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA11">
         <v>1.53</v>
       </c>
       <c r="AB11">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,16 +2920,16 @@
         <v>2.5</v>
       </c>
       <c r="O16">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="P16">
         <v>3</v>
       </c>
       <c r="Q16">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="R16">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="S16">
         <v>1.77</v>
@@ -2938,7 +2938,7 @@
         <v>1.93</v>
       </c>
       <c r="U16">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="V16">
         <v>1.12</v>
@@ -2950,10 +2950,10 @@
         <v>1.14</v>
       </c>
       <c r="Y16">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Z16">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AA16">
         <v>3.5</v>
@@ -2962,7 +2962,7 @@
         <v>1.22</v>
       </c>
       <c r="AC16">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="AD16">
         <v>1.02</v>
@@ -2971,10 +2971,10 @@
         <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AG16">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AK16">
         <v>1.4</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O17">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="P17">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3415,13 +3415,13 @@
         <v>2.3</v>
       </c>
       <c r="Q19">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="R19">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="S19">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T19">
         <v>2.41</v>
@@ -3445,10 +3445,10 @@
         <v>2.66</v>
       </c>
       <c r="AA19">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AB19">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AC19">
         <v>3.92</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3738,58 +3738,58 @@
         <v>3.1</v>
       </c>
       <c r="P21">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,22 +3895,22 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="O22">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P22">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q22">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="R22">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S22">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="T22">
         <v>2.75</v>
@@ -3922,31 +3922,31 @@
         <v>1.33</v>
       </c>
       <c r="W22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y22">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z22">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="AA22">
-        <v>2.12</v>
+        <v>2.31</v>
       </c>
       <c r="AB22">
         <v>1.62</v>
       </c>
       <c r="AC22">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AD22">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE22">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF22">
         <v>1.9</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK22">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4224,19 +4224,19 @@
         <v>3.8</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
         <v>1.8</v>
       </c>
       <c r="Q24">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R24">
         <v>2.4</v>
       </c>
       <c r="S24">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T24">
         <v>3.25</v>
@@ -4245,10 +4245,10 @@
         <v>2.3</v>
       </c>
       <c r="V24">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4257,13 +4257,13 @@
         <v>1.15</v>
       </c>
       <c r="Z24">
-        <v>4.53</v>
+        <v>4.56</v>
       </c>
       <c r="AA24">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AC24">
         <v>2.41</v>
@@ -4272,13 +4272,13 @@
         <v>1.5</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
         <v>1.55</v>
       </c>
       <c r="AG24">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4556,55 +4556,55 @@
         <v>7.6</v>
       </c>
       <c r="Q26">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="R26">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T26">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="U26">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W26">
         <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z26">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="AA26">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB26">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AC26">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="AD26">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE26">
         <v>1.12</v>
       </c>
       <c r="AF26">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AG26">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AK26">
-        <v>2.99</v>
+        <v>3.46</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O28">
         <v>3.4</v>
@@ -4882,55 +4882,55 @@
         <v>2.1</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA28">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB28">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,16 +5039,16 @@
         <v>2.25</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q29">
         <v>2.8</v>
       </c>
       <c r="R29">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S29">
         <v>1.25</v>
@@ -5057,10 +5057,10 @@
         <v>3.4</v>
       </c>
       <c r="U29">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V29">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
         <v>1.09</v>
@@ -5069,31 +5069,31 @@
         <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z29">
         <v>3.95</v>
       </c>
       <c r="AA29">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB29">
         <v>2.2</v>
       </c>
       <c r="AC29">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AD29">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE29">
         <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG29">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AK29">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P30">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q30">
         <v>2.44</v>
       </c>
       <c r="R30">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
         <v>1.3</v>
       </c>
       <c r="T30">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U30">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V30">
         <v>1.44</v>
       </c>
       <c r="W30">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
         <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z30">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA30">
         <v>1.71</v>
       </c>
       <c r="AB30">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC30">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD30">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
         <v>1.14</v>
       </c>
       <c r="AF30">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG30">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P31">
         <v>2.45</v>
       </c>
       <c r="Q31">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="R31">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S31">
         <v>1.25</v>
       </c>
       <c r="T31">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="U31">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="V31">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W31">
         <v>1.1</v>
@@ -5395,22 +5395,22 @@
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z31">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA31">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AB31">
-        <v>2.23</v>
+        <v>2.36</v>
       </c>
       <c r="AC31">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AD31">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE31">
         <v>1.2</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK31">
         <v>1.44</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.13</v>
+        <v>3.9</v>
       </c>
       <c r="O33">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P33">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="O34">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="P34">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R34">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="S34">
         <v>1.23</v>
@@ -5875,41 +5875,41 @@
         <v>2.12</v>
       </c>
       <c r="V34">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W34">
         <v>1.14</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
         <v>1.14</v>
       </c>
       <c r="Z34">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AA34">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB34">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AC34">
+        <v>2.25</v>
+      </c>
+      <c r="AD34">
+        <v>1.7</v>
+      </c>
+      <c r="AE34">
+        <v>1.25</v>
+      </c>
+      <c r="AF34">
+        <v>1.61</v>
+      </c>
+      <c r="AG34">
         <v>2.18</v>
       </c>
-      <c r="AD34">
-        <v>1.66</v>
-      </c>
-      <c r="AE34">
-        <v>1.23</v>
-      </c>
-      <c r="AF34">
-        <v>1.62</v>
-      </c>
-      <c r="AG34">
-        <v>2.1</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AK34">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="O35">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P35">
-        <v>5.25</v>
+        <v>4.35</v>
       </c>
       <c r="Q35">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="R35">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="S35">
         <v>1.26</v>
@@ -6035,10 +6035,10 @@
         <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V35">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W35">
         <v>1.12</v>
@@ -6047,31 +6047,31 @@
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA35">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB35">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AC35">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AD35">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE35">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF35">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK35">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O36">
         <v>3.47</v>
       </c>
       <c r="P36">
-        <v>4.33</v>
+        <v>3.52</v>
       </c>
       <c r="Q36">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S36">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T36">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="U36">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="V36">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
         <v>1.07</v>
@@ -6210,31 +6210,31 @@
         <v>1.06</v>
       </c>
       <c r="Y36">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="Z36">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA36">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="AB36">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AC36">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AD36">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE36">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF36">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG36">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK36">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,28 +6343,28 @@
         <v>2.02</v>
       </c>
       <c r="O37">
-        <v>2.98</v>
+        <v>3.12</v>
       </c>
       <c r="P37">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R37">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S37">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T37">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="U37">
         <v>3.31</v>
       </c>
       <c r="V37">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="W37">
         <v>1.01</v>
@@ -6373,31 +6373,31 @@
         <v>1.06</v>
       </c>
       <c r="Y37">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Z37">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="AA37">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AB37">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC37">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AD37">
         <v>1.14</v>
       </c>
       <c r="AE37">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF37">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AG37">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.39</v>
       </c>
       <c r="AK37">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="O39">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="P39">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q39">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R39">
         <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="U39">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="V39">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.25</v>
       </c>
       <c r="Z39">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="AA39">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB39">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC39">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD39">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE39">
         <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AK39">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O40">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P40">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q40">
         <v>4.6</v>
       </c>
       <c r="R40">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S40">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="U40">
         <v>2.08</v>
       </c>
       <c r="V40">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W40">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA40">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AB40">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AC40">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AD40">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE40">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF40">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AG40">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,31 +6992,31 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="O41">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="P41">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q41">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R41">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="S41">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T41">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="U41">
         <v>2.06</v>
       </c>
       <c r="V41">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W41">
         <v>1.18</v>
@@ -7031,25 +7031,25 @@
         <v>5.75</v>
       </c>
       <c r="AA41">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AB41">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AC41">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AD41">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE41">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF41">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG41">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK41">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O45">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P45">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="Q45">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R45">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="S45">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
         <v>2.88</v>
       </c>
       <c r="U45">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V45">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Z45">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA45">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB45">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AC45">
         <v>3.1</v>
       </c>
       <c r="AD45">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE45">
         <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG45">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK45">
         <v>1.67</v>
@@ -7807,43 +7807,43 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="O46">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="P46">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q46">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R46">
         <v>1.91</v>
       </c>
       <c r="S46">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="T46">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="U46">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="V46">
         <v>1.25</v>
       </c>
       <c r="W46">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X46">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y46">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="Z46">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AA46">
         <v>2.5</v>
@@ -7855,10 +7855,10 @@
         <v>5</v>
       </c>
       <c r="AD46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF46">
         <v>1.93</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AK46">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O48">
         <v>3.8</v>
       </c>
       <c r="P48">
-        <v>4.1</v>
+        <v>4.84</v>
       </c>
       <c r="Q48">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R48">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S48">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T48">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U48">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="V48">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z48">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA48">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB48">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AC48">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD48">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE48">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF48">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG48">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK48">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O50">
         <v>3.6</v>
       </c>
       <c r="P50">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q50">
-        <v>3.53</v>
+        <v>3.9</v>
       </c>
       <c r="R50">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="S50">
         <v>1.3</v>
       </c>
       <c r="T50">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="U50">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="V50">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="W50">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z50">
-        <v>4.4</v>
+        <v>3.76</v>
       </c>
       <c r="AA50">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AB50">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="AC50">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="AD50">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG50">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.28</v>
+        <v>1.91</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O55">
         <v>3</v>
       </c>
       <c r="P55">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA55">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AB55">
         <v>1.57</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9769,58 +9769,58 @@
         <v>3.2</v>
       </c>
       <c r="P58">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q58">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="R58">
         <v>2.1</v>
       </c>
       <c r="S58">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T58">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U58">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="V58">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W58">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X58">
         <v>1.05</v>
       </c>
       <c r="Y58">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z58">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="AA58">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB58">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AC58">
         <v>4.3</v>
       </c>
       <c r="AD58">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE58">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF58">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG58">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9932,28 +9932,28 @@
         <v>3</v>
       </c>
       <c r="P59">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q59">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="R59">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="S59">
         <v>1.48</v>
       </c>
       <c r="T59">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U59">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V59">
         <v>1.29</v>
       </c>
       <c r="W59">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X59">
         <v>1.1</v>
@@ -9962,28 +9962,28 @@
         <v>1.36</v>
       </c>
       <c r="Z59">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="AA59">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AB59">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AC59">
-        <v>4.66</v>
+        <v>4.71</v>
       </c>
       <c r="AD59">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE59">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF59">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG59">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK59">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="O60">
         <v>3</v>
       </c>
       <c r="P60">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q60">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="R60">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="S60">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T60">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="U60">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="V60">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W60">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X60">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y60">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="Z60">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AA60">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="AB60">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AC60">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="AD60">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE60">
         <v>1.03</v>
       </c>
       <c r="AF60">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AG60">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK60">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL60">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -787,14 +787,14 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,12 +859,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+2"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,26 +938,26 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "33"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "78", "90+1"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,30 +1101,30 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O5">
         <v>3.55</v>
@@ -1133,98 +1133,98 @@
         <v>4.5</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R5">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="U5">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Z5">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="AA5">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB5">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AC5">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AD5">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE5">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG5">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "64", "69", "89"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1276,14 +1276,14 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1768,115 +1768,115 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O9">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="Q9">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="R9">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="S9">
         <v>1.45</v>
       </c>
       <c r="T9">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U9">
-        <v>3.16</v>
+        <v>3.31</v>
       </c>
       <c r="V9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
         <v>1.01</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z9">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AA9">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AB9">
         <v>1.68</v>
       </c>
       <c r="AC9">
-        <v>3.92</v>
+        <v>4.01</v>
       </c>
       <c r="AD9">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE9">
         <v>1.02</v>
       </c>
       <c r="AF9">
+        <v>2.16</v>
+      </c>
+      <c r="AG9">
+        <v>1.6</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>["52"]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.19</v>
+      </c>
+      <c r="AK9">
         <v>2.15</v>
       </c>
-      <c r="AG9">
-        <v>1.61</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.1</v>
-      </c>
-      <c r="AK9">
-        <v>2.3</v>
-      </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1928,14 +1928,14 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,26 +2079,26 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "75", "90+1"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2245,13 +2245,13 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -2261,68 +2261,68 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
         <v>2.5</v>
       </c>
       <c r="O12">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
         <v>2.5</v>
       </c>
       <c r="Q12">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="V12">
         <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="AA12">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB12">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC12">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AE12">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
         <v>1.75</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2331,11 +2331,11 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AJ12">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK12">
         <v>1.4</v>
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2396,16 +2396,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2417,118 +2417,118 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>2.85</v>
+        <v>1.61</v>
       </c>
       <c r="O13">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="P13">
-        <v>2.2</v>
+        <v>4.44</v>
       </c>
       <c r="Q13">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="R13">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="S13">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
         <v>2.63</v>
       </c>
       <c r="U13">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="V13">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
+        <v>1.17</v>
+      </c>
+      <c r="Z13">
+        <v>3.98</v>
+      </c>
+      <c r="AA13">
+        <v>1.7</v>
+      </c>
+      <c r="AB13">
+        <v>2.1</v>
+      </c>
+      <c r="AC13">
+        <v>2.63</v>
+      </c>
+      <c r="AD13">
         <v>1.33</v>
       </c>
-      <c r="Z13">
-        <v>3.25</v>
-      </c>
-      <c r="AA13">
-        <v>2</v>
-      </c>
-      <c r="AB13">
-        <v>1.73</v>
-      </c>
-      <c r="AC13">
-        <v>3.5</v>
-      </c>
-      <c r="AD13">
-        <v>1.28</v>
-      </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AG13">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>["89"]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ13">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.36</v>
+        <v>2.07</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2559,139 +2559,139 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="O14">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
-        <v>3.72</v>
+        <v>2.2</v>
       </c>
       <c r="Q14">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="R14">
+        <v>2.1</v>
+      </c>
+      <c r="S14">
+        <v>1.33</v>
+      </c>
+      <c r="T14">
+        <v>2.88</v>
+      </c>
+      <c r="U14">
+        <v>2.6</v>
+      </c>
+      <c r="V14">
+        <v>1.4</v>
+      </c>
+      <c r="W14">
+        <v>1.07</v>
+      </c>
+      <c r="X14">
+        <v>1</v>
+      </c>
+      <c r="Y14">
+        <v>1.25</v>
+      </c>
+      <c r="Z14">
+        <v>3.21</v>
+      </c>
+      <c r="AA14">
+        <v>1.78</v>
+      </c>
+      <c r="AB14">
+        <v>1.91</v>
+      </c>
+      <c r="AC14">
+        <v>2.88</v>
+      </c>
+      <c r="AD14">
+        <v>1.25</v>
+      </c>
+      <c r="AE14">
+        <v>1.09</v>
+      </c>
+      <c r="AF14">
+        <v>1.61</v>
+      </c>
+      <c r="AG14">
+        <v>2.13</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>["64"]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>["5", "57"]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>1.47</v>
+      </c>
+      <c r="AK14">
+        <v>1.36</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>7</v>
+      </c>
+      <c r="AN14">
+        <v>5</v>
+      </c>
+      <c r="AO14">
+        <v>19</v>
+      </c>
+      <c r="AP14">
+        <v>15</v>
+      </c>
+      <c r="AQ14">
         <v>2.19</v>
       </c>
-      <c r="S14">
-        <v>1.3</v>
-      </c>
-      <c r="T14">
-        <v>3.25</v>
-      </c>
-      <c r="U14">
-        <v>2.38</v>
-      </c>
-      <c r="V14">
-        <v>1.5</v>
-      </c>
-      <c r="W14">
-        <v>1.1</v>
-      </c>
-      <c r="X14">
-        <v>1.02</v>
-      </c>
-      <c r="Y14">
-        <v>1.18</v>
-      </c>
-      <c r="Z14">
-        <v>3.84</v>
-      </c>
-      <c r="AA14">
-        <v>1.65</v>
-      </c>
-      <c r="AB14">
-        <v>2.1</v>
-      </c>
-      <c r="AC14">
-        <v>2.75</v>
-      </c>
-      <c r="AD14">
-        <v>1.42</v>
-      </c>
-      <c r="AE14">
-        <v>1.12</v>
-      </c>
-      <c r="AF14">
-        <v>1.6</v>
-      </c>
-      <c r="AG14">
-        <v>2.12</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.21</v>
-      </c>
-      <c r="AK14">
-        <v>1.85</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>-1</v>
-      </c>
-      <c r="AN14">
-        <v>-1</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>-1</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2722,112 +2722,112 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q15">
-        <v>2.8</v>
+        <v>3.57</v>
       </c>
       <c r="R15">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="S15">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="T15">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U15">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="V15">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="W15">
+        <v>1.02</v>
+      </c>
+      <c r="X15">
+        <v>1.14</v>
+      </c>
+      <c r="Y15">
+        <v>1.85</v>
+      </c>
+      <c r="Z15">
+        <v>1.85</v>
+      </c>
+      <c r="AA15">
+        <v>3.5</v>
+      </c>
+      <c r="AB15">
+        <v>1.22</v>
+      </c>
+      <c r="AC15">
+        <v>7.9</v>
+      </c>
+      <c r="AD15">
+        <v>1.02</v>
+      </c>
+      <c r="AE15">
         <v>1.01</v>
       </c>
-      <c r="X15">
-        <v>1.07</v>
-      </c>
-      <c r="Y15">
-        <v>1.44</v>
-      </c>
-      <c r="Z15">
-        <v>1.97</v>
-      </c>
-      <c r="AA15">
-        <v>2.18</v>
-      </c>
-      <c r="AB15">
-        <v>1.35</v>
-      </c>
-      <c r="AC15">
-        <v>3.7</v>
-      </c>
-      <c r="AD15">
-        <v>1.08</v>
-      </c>
-      <c r="AE15">
-        <v>1.02</v>
-      </c>
       <c r="AF15">
-        <v>1.93</v>
+        <v>2.67</v>
       </c>
       <c r="AG15">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "90+6", "90+11"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "68"]</t>
         </is>
       </c>
       <c r="AJ15">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="AK15">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,19 +2885,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2906,91 +2906,91 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>3.57</v>
+        <v>2.8</v>
       </c>
       <c r="R16">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="S16">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="T16">
+        <v>1.91</v>
+      </c>
+      <c r="U16">
+        <v>2.9</v>
+      </c>
+      <c r="V16">
+        <v>1.17</v>
+      </c>
+      <c r="W16">
+        <v>1.01</v>
+      </c>
+      <c r="X16">
+        <v>1.07</v>
+      </c>
+      <c r="Y16">
+        <v>1.44</v>
+      </c>
+      <c r="Z16">
+        <v>1.97</v>
+      </c>
+      <c r="AA16">
+        <v>2.18</v>
+      </c>
+      <c r="AB16">
+        <v>1.35</v>
+      </c>
+      <c r="AC16">
+        <v>3.7</v>
+      </c>
+      <c r="AD16">
+        <v>1.08</v>
+      </c>
+      <c r="AE16">
+        <v>1.02</v>
+      </c>
+      <c r="AF16">
         <v>1.93</v>
       </c>
-      <c r="U16">
-        <v>4.5</v>
-      </c>
-      <c r="V16">
-        <v>1.12</v>
-      </c>
-      <c r="W16">
-        <v>1.02</v>
-      </c>
-      <c r="X16">
-        <v>1.14</v>
-      </c>
-      <c r="Y16">
-        <v>1.85</v>
-      </c>
-      <c r="Z16">
-        <v>1.85</v>
-      </c>
-      <c r="AA16">
-        <v>3.5</v>
-      </c>
-      <c r="AB16">
-        <v>1.22</v>
-      </c>
-      <c r="AC16">
-        <v>7.9</v>
-      </c>
-      <c r="AD16">
-        <v>1.02</v>
-      </c>
-      <c r="AE16">
-        <v>1.01</v>
-      </c>
-      <c r="AF16">
-        <v>2.67</v>
-      </c>
       <c r="AG16">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47"]</t>
         </is>
       </c>
       <c r="AJ16">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="AK16">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -3072,11 +3072,11 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3220,13 +3220,13 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -3239,35 +3239,35 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>3.65</v>
+        <v>3.53</v>
       </c>
       <c r="O18">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="P18">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="Q18">
-        <v>4.26</v>
+        <v>4.01</v>
       </c>
       <c r="R18">
         <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T18">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U18">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
         <v>1.06</v>
@@ -3276,74 +3276,74 @@
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z18">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="AA18">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB18">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC18">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AD18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE18">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF18">
         <v>1.75</v>
       </c>
       <c r="AG18">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
+          <t>["23"]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ18">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="AK18">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,26 +3383,26 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3415,22 +3415,22 @@
         <v>2.3</v>
       </c>
       <c r="Q19">
-        <v>3.92</v>
+        <v>4.25</v>
       </c>
       <c r="R19">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="S19">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T19">
-        <v>2.41</v>
+        <v>2.66</v>
       </c>
       <c r="U19">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="V19">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W19">
         <v>1.02</v>
@@ -3439,22 +3439,22 @@
         <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AA19">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="AB19">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC19">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="AD19">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE19">
         <v>1.03</v>
@@ -3467,46 +3467,46 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
+          <t>["36", "90+3"]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ19">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AK19">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2", "66", "74"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -3875,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -3887,11 +3887,11 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AJ22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4038,45 +4038,45 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="P23">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="Q23">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T23">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="U23">
         <v>2.15</v>
@@ -4088,35 +4088,35 @@
         <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z23">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA23">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB23">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AC23">
+        <v>2.26</v>
+      </c>
+      <c r="AD23">
+        <v>1.62</v>
+      </c>
+      <c r="AE23">
+        <v>1.19</v>
+      </c>
+      <c r="AF23">
+        <v>1.54</v>
+      </c>
+      <c r="AG23">
         <v>2.3</v>
       </c>
-      <c r="AD23">
-        <v>1.57</v>
-      </c>
-      <c r="AE23">
-        <v>1.18</v>
-      </c>
-      <c r="AF23">
-        <v>1.55</v>
-      </c>
-      <c r="AG23">
-        <v>2.25</v>
-      </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4124,41 +4124,41 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "56"]</t>
         </is>
       </c>
       <c r="AJ23">
-        <v>2.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4217,68 +4217,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q24">
-        <v>4</v>
+        <v>3.46</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S24">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T24">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V24">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W24">
         <v>1.1</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="AA24">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB24">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="AC24">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AD24">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE24">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
         <v>1.55</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AJ24">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4393,49 +4393,49 @@
         <v>3</v>
       </c>
       <c r="Q25">
-        <v>3.16</v>
+        <v>2.63</v>
       </c>
       <c r="R25">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="S25">
         <v>1.45</v>
       </c>
       <c r="T25">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U25">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X25">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
         <v>1.4</v>
       </c>
       <c r="Z25">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AA25">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="AB25">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AC25">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AD25">
         <v>1.16</v>
       </c>
       <c r="AE25">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF25">
         <v>1.95</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK25">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4524,130 +4524,130 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O26">
-        <v>4.9</v>
+        <v>6.45</v>
       </c>
       <c r="P26">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="Q26">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="R26">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="S26">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U26">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="V26">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z26">
-        <v>3.54</v>
+        <v>3.94</v>
       </c>
       <c r="AA26">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AC26">
-        <v>3.23</v>
+        <v>2.74</v>
       </c>
       <c r="AD26">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE26">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="AG26">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "27", "45+1", "47"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "51"]</t>
         </is>
       </c>
       <c r="AJ26">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AK26">
-        <v>3.46</v>
+        <v>4.66</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4687,36 +4687,36 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O27">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "87"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -4862,14 +4862,14 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55", "87", "90+7", "90+11"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49", "52"]</t>
         </is>
       </c>
       <c r="AJ28">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,13 +5013,13 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -5028,11 +5028,11 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5115,28 +5115,28 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5342,23 +5342,23 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "58", "82"]</t>
         </is>
       </c>
       <c r="AJ31">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5521,29 +5521,29 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O32">
         <v>3.7</v>
       </c>
       <c r="P32">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q32">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R32">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.29</v>
+        <v>2.87</v>
       </c>
       <c r="U32">
         <v>2.5</v>
@@ -5552,34 +5552,34 @@
         <v>1.5</v>
       </c>
       <c r="W32">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z32">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="AA32">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB32">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC32">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AD32">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF32">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
         <v>2</v>
@@ -5595,37 +5595,37 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK32">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL32">
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5668,13 +5668,13 @@
         <v>0</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "45", "45+4"]</t>
         </is>
       </c>
       <c r="AJ33">
@@ -5828,26 +5828,26 @@
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "54", "87"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AJ34">
@@ -5930,28 +5930,28 @@
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -6006,11 +6006,11 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
@@ -6075,12 +6075,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32", "42"]</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AJ35">
@@ -6093,28 +6093,28 @@
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6512,55 +6512,55 @@
         <v>5.1</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA38">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB38">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6643,26 +6643,26 @@
         </is>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "43"]</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "78"]</t>
         </is>
       </c>
       <c r="AJ39">
@@ -6745,28 +6745,28 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6797,22 +6797,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>0</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -6825,111 +6825,111 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="O40">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="P40">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="Q40">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="R40">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T40">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="U40">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V40">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W40">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AA40">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AB40">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AC40">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="AD40">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AE40">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF40">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG40">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
+          <t>["45"]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK40">
+        <v>2.29</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>9</v>
+      </c>
+      <c r="AN40">
+        <v>1</v>
+      </c>
+      <c r="AO40">
+        <v>16</v>
+      </c>
+      <c r="AP40">
+        <v>11</v>
+      </c>
+      <c r="AQ40">
+        <v>2.09</v>
+      </c>
+      <c r="AR40">
         <v>1.18</v>
       </c>
-      <c r="AL40">
-        <v>0</v>
-      </c>
-      <c r="AM40">
-        <v>-1</v>
-      </c>
-      <c r="AN40">
-        <v>-1</v>
-      </c>
-      <c r="AO40">
-        <v>-1</v>
-      </c>
-      <c r="AP40">
-        <v>-1</v>
-      </c>
-      <c r="AQ40">
-        <v>0</v>
-      </c>
-      <c r="AR40">
-        <v>0</v>
-      </c>
       <c r="AS40">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6960,139 +6960,139 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
+        <v>4.7</v>
+      </c>
+      <c r="O41">
+        <v>4</v>
+      </c>
+      <c r="P41">
+        <v>1.6</v>
+      </c>
+      <c r="Q41">
+        <v>4.6</v>
+      </c>
+      <c r="R41">
+        <v>2.5</v>
+      </c>
+      <c r="S41">
+        <v>1.22</v>
+      </c>
+      <c r="T41">
+        <v>3.58</v>
+      </c>
+      <c r="U41">
+        <v>2.08</v>
+      </c>
+      <c r="V41">
+        <v>1.68</v>
+      </c>
+      <c r="W41">
+        <v>1.13</v>
+      </c>
+      <c r="X41">
+        <v>1.03</v>
+      </c>
+      <c r="Y41">
+        <v>1.1</v>
+      </c>
+      <c r="Z41">
+        <v>5</v>
+      </c>
+      <c r="AA41">
         <v>1.5</v>
       </c>
-      <c r="O41">
-        <v>4.4</v>
-      </c>
-      <c r="P41">
-        <v>4.3</v>
-      </c>
-      <c r="Q41">
-        <v>2</v>
-      </c>
-      <c r="R41">
-        <v>2.51</v>
-      </c>
-      <c r="S41">
-        <v>1.19</v>
-      </c>
-      <c r="T41">
-        <v>3.88</v>
-      </c>
-      <c r="U41">
-        <v>2.06</v>
-      </c>
-      <c r="V41">
-        <v>1.73</v>
-      </c>
-      <c r="W41">
+      <c r="AB41">
+        <v>2.45</v>
+      </c>
+      <c r="AC41">
+        <v>2.23</v>
+      </c>
+      <c r="AD41">
+        <v>1.57</v>
+      </c>
+      <c r="AE41">
+        <v>1.25</v>
+      </c>
+      <c r="AF41">
+        <v>1.53</v>
+      </c>
+      <c r="AG41">
+        <v>2.31</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>["51"]</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>["3", "7", "37", "39", "45", "59"]</t>
+        </is>
+      </c>
+      <c r="AJ41">
+        <v>1.22</v>
+      </c>
+      <c r="AK41">
         <v>1.18</v>
       </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.08</v>
-      </c>
-      <c r="Z41">
-        <v>5.75</v>
-      </c>
-      <c r="AA41">
-        <v>1.35</v>
-      </c>
-      <c r="AB41">
-        <v>2.9</v>
-      </c>
-      <c r="AC41">
-        <v>2.13</v>
-      </c>
-      <c r="AD41">
-        <v>1.72</v>
-      </c>
-      <c r="AE41">
-        <v>1.3</v>
-      </c>
-      <c r="AF41">
-        <v>1.47</v>
-      </c>
-      <c r="AG41">
-        <v>2.6</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ41">
-        <v>1.16</v>
-      </c>
-      <c r="AK41">
-        <v>2.29</v>
-      </c>
       <c r="AL41">
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO41">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP41">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="O42">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P42">
+        <v>1.92</v>
+      </c>
+      <c r="Q42">
+        <v>4.19</v>
+      </c>
+      <c r="R42">
         <v>1.9</v>
       </c>
-      <c r="Q42">
-        <v>4.22</v>
-      </c>
-      <c r="R42">
-        <v>1.95</v>
-      </c>
       <c r="S42">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="T42">
+        <v>2.36</v>
+      </c>
+      <c r="U42">
+        <v>3.5</v>
+      </c>
+      <c r="V42">
+        <v>1.23</v>
+      </c>
+      <c r="W42">
+        <v>1.04</v>
+      </c>
+      <c r="X42">
+        <v>1.12</v>
+      </c>
+      <c r="Y42">
+        <v>1.51</v>
+      </c>
+      <c r="Z42">
         <v>2.5</v>
       </c>
-      <c r="U42">
-        <v>3.25</v>
-      </c>
-      <c r="V42">
+      <c r="AA42">
+        <v>2.62</v>
+      </c>
+      <c r="AB42">
+        <v>1.5</v>
+      </c>
+      <c r="AC42">
+        <v>4.9</v>
+      </c>
+      <c r="AD42">
+        <v>1.11</v>
+      </c>
+      <c r="AE42">
+        <v>1.04</v>
+      </c>
+      <c r="AF42">
+        <v>2.05</v>
+      </c>
+      <c r="AG42">
+        <v>1.73</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
+        <v>1.68</v>
+      </c>
+      <c r="AK42">
         <v>1.25</v>
-      </c>
-      <c r="W42">
-        <v>1</v>
-      </c>
-      <c r="X42">
-        <v>1.03</v>
-      </c>
-      <c r="Y42">
-        <v>1.45</v>
-      </c>
-      <c r="Z42">
-        <v>2.8</v>
-      </c>
-      <c r="AA42">
-        <v>2.4</v>
-      </c>
-      <c r="AB42">
-        <v>1.49</v>
-      </c>
-      <c r="AC42">
-        <v>4.5</v>
-      </c>
-      <c r="AD42">
-        <v>1.17</v>
-      </c>
-      <c r="AE42">
-        <v>1.01</v>
-      </c>
-      <c r="AF42">
-        <v>1.87</v>
-      </c>
-      <c r="AG42">
-        <v>1.78</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.8</v>
-      </c>
-      <c r="AK42">
-        <v>1.22</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O43">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P43">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q43">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="R43">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="S43">
         <v>1.49</v>
@@ -7339,22 +7339,22 @@
         <v>2.34</v>
       </c>
       <c r="U43">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="V43">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W43">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X43">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z43">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AA43">
         <v>2.21</v>
@@ -7363,19 +7363,19 @@
         <v>1.57</v>
       </c>
       <c r="AC43">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD43">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF43">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG43">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O44">
         <v>3.18</v>
       </c>
       <c r="P44">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="Q44">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="R44">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S44">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T44">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="U44">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="V44">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W44">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X44">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y44">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z44">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AA44">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="AB44">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC44">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AD44">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE44">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF44">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG44">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK44">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="O47">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="P47">
-        <v>3.49</v>
+        <v>4.27</v>
       </c>
       <c r="Q47">
         <v>2.31</v>
       </c>
       <c r="R47">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T47">
-        <v>3.22</v>
+        <v>2.89</v>
       </c>
       <c r="U47">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="V47">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W47">
         <v>1.06</v>
       </c>
       <c r="X47">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y47">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z47">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="AA47">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AB47">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC47">
         <v>3.25</v>
       </c>
       <c r="AD47">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE47">
         <v>1.08</v>
       </c>
       <c r="AF47">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG47">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK47">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O49">
         <v>3.2</v>
       </c>
       <c r="P49">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="Q49">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="R49">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="S49">
         <v>1.4</v>
@@ -8317,59 +8317,59 @@
         <v>2.75</v>
       </c>
       <c r="U49">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V49">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W49">
         <v>1.02</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y49">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z49">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA49">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB49">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC49">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD49">
+        <v>1.22</v>
+      </c>
+      <c r="AE49">
+        <v>1.03</v>
+      </c>
+      <c r="AF49">
+        <v>1.81</v>
+      </c>
+      <c r="AG49">
+        <v>1.83</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
         <v>1.25</v>
       </c>
-      <c r="AE49">
-        <v>1.08</v>
-      </c>
-      <c r="AF49">
-        <v>1.75</v>
-      </c>
-      <c r="AG49">
-        <v>1.91</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.3</v>
-      </c>
       <c r="AK49">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8462,28 +8462,28 @@
         <v>3.75</v>
       </c>
       <c r="O50">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
         <v>1.91</v>
       </c>
       <c r="Q50">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="R50">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T50">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U50">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V50">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="W50">
         <v>1.08</v>
@@ -8492,28 +8492,28 @@
         <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z50">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="AA50">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB50">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AC50">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AD50">
         <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF50">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG50">
         <v>2.12</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.91</v>
+        <v>1.27</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8785,25 +8785,25 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="O52">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P52">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="Q52">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S52">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T52">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="U52">
         <v>2.83</v>
@@ -8815,13 +8815,13 @@
         <v>1.03</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z52">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA52">
         <v>1.95</v>
@@ -8842,7 +8842,7 @@
         <v>1.75</v>
       </c>
       <c r="AG52">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="P53">
-        <v>5.5</v>
+        <v>6.67</v>
       </c>
       <c r="Q53">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="R53">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S53">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T53">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U53">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V53">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W53">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y53">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z53">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA53">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB53">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC53">
         <v>3.5</v>
       </c>
       <c r="AD53">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE53">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF53">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AG53">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AK53">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9114,22 +9114,22 @@
         <v>3.3</v>
       </c>
       <c r="O54">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="P54">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="Q54">
-        <v>4.1</v>
+        <v>3.72</v>
       </c>
       <c r="R54">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="S54">
         <v>1.53</v>
       </c>
       <c r="T54">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U54">
         <v>3.4</v>
@@ -9141,34 +9141,34 @@
         <v>1.01</v>
       </c>
       <c r="X54">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y54">
         <v>1.49</v>
       </c>
       <c r="Z54">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="AA54">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AB54">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AC54">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AD54">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE54">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF54">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG54">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="AK54">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9437,25 +9437,25 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O56">
         <v>3</v>
       </c>
       <c r="P56">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q56">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="R56">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="S56">
         <v>1.47</v>
       </c>
       <c r="T56">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="U56">
         <v>3.3</v>
@@ -9470,19 +9470,19 @@
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z56">
         <v>2.74</v>
       </c>
       <c r="AA56">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB56">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AC56">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AD56">
         <v>1.16</v>
@@ -9491,10 +9491,10 @@
         <v>1.01</v>
       </c>
       <c r="AF56">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG56">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK56">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,31 +9600,31 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="O57">
         <v>3.85</v>
       </c>
       <c r="P57">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q57">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="R57">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="S57">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T57">
         <v>4.45</v>
       </c>
       <c r="U57">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V57">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="W57">
         <v>1.22</v>
@@ -9633,28 +9633,28 @@
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z57">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA57">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AB57">
         <v>2.63</v>
       </c>
       <c r="AC57">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AD57">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="AE57">
         <v>1.38</v>
       </c>
       <c r="AF57">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AG57">
         <v>3.7</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK57">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9926,37 +9926,37 @@
         </is>
       </c>
       <c r="N59">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="O59">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="P59">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="Q59">
-        <v>3.57</v>
+        <v>3.84</v>
       </c>
       <c r="R59">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S59">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="T59">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U59">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="V59">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W59">
         <v>1.01</v>
       </c>
       <c r="X59">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y59">
         <v>1.36</v>
@@ -9965,25 +9965,25 @@
         <v>2.72</v>
       </c>
       <c r="AA59">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AB59">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AC59">
-        <v>4.71</v>
+        <v>4.4</v>
       </c>
       <c r="AD59">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE59">
         <v>1.02</v>
       </c>
       <c r="AF59">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG59">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AK59">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O61">
         <v>3.55</v>
       </c>
       <c r="P61">
-        <v>4.94</v>
+        <v>5.3</v>
       </c>
       <c r="Q61">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="R61">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S61">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T61">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U61">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="V61">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W61">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
         <v>1.05</v>
       </c>
       <c r="Y61">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z61">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AA61">
         <v>2</v>
       </c>
       <c r="AB61">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC61">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AD61">
         <v>1.29</v>
       </c>
       <c r="AE61">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF61">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AG61">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK61">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
+        <v>2.92</v>
+      </c>
+      <c r="O62">
         <v>2.8</v>
       </c>
-      <c r="O62">
-        <v>3</v>
-      </c>
       <c r="P62">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q62">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="R62">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="S62">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T62">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U62">
         <v>3.35</v>
       </c>
       <c r="V62">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W62">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X62">
         <v>1.06</v>
       </c>
       <c r="Y62">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z62">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AA62">
         <v>2.4</v>
       </c>
       <c r="AB62">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC62">
-        <v>4.94</v>
+        <v>4.25</v>
       </c>
       <c r="AD62">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AE62">
         <v>1.01</v>
       </c>
       <c r="AF62">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG62">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.35</v>
       </c>
       <c r="AK62">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11067,55 +11067,55 @@
         </is>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O66">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="Q66">
-        <v>2.48</v>
+        <v>2.67</v>
       </c>
       <c r="R66">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S66">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T66">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="U66">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="V66">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W66">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
         <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z66">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="AA66">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AB66">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AC66">
         <v>3</v>
       </c>
       <c r="AD66">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE66">
         <v>1.08</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK66">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,31 +11230,31 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O67">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P67">
-        <v>4.05</v>
+        <v>4.17</v>
       </c>
       <c r="Q67">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="R67">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S67">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T67">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U67">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="V67">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W67">
         <v>1.1</v>
@@ -11263,47 +11263,47 @@
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z67">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AA67">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB67">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC67">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AD67">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE67">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF67">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG67">
+        <v>1.98</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>1.19</v>
+      </c>
+      <c r="AK67">
         <v>1.85</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>1.2</v>
-      </c>
-      <c r="AK67">
-        <v>2.06</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,19 +11393,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="O68">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P68">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q68">
         <v>3.7</v>
       </c>
       <c r="R68">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="S68">
         <v>1.4</v>
@@ -11414,16 +11414,16 @@
         <v>2.5</v>
       </c>
       <c r="U68">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="V68">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W68">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X68">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
         <v>1.36</v>
@@ -11432,25 +11432,25 @@
         <v>3.1</v>
       </c>
       <c r="AA68">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB68">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC68">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AD68">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE68">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF68">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG68">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
+        <v>1.29</v>
+      </c>
+      <c r="AK68">
         <v>1.3</v>
-      </c>
-      <c r="AK68">
-        <v>1.34</v>
       </c>
       <c r="AL68">
         <v>0</v>

--- a/jogos_2026-08-24.xlsx
+++ b/jogos_2026-08-24.xlsx
@@ -4361,26 +4361,26 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20"]</t>
         </is>
       </c>
       <c r="AJ25">
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
@@ -6256,28 +6256,28 @@
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6317,26 +6317,26 @@
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+4"]</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8"]</t>
         </is>
       </c>
       <c r="AJ37">
@@ -6419,28 +6419,28 @@
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6480,26 +6480,26 @@
         </is>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "41", "81"]</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "59"]</t>
         </is>
       </c>
       <c r="AJ38">
@@ -6582,28 +6582,28 @@
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -7147,11 +7147,11 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AJ42">
@@ -7234,28 +7234,28 @@
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7295,26 +7295,26 @@
         </is>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43">
         <v>0</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "90+5"]</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30"]</t>
         </is>
       </c>
       <c r="AJ43">
@@ -7397,28 +7397,28 @@
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO43">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP43">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7458,26 +7458,26 @@
         </is>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44">
         <v>0</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44">
         <v>0</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44">
         <v>0</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "87"]</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
@@ -7560,28 +7560,28 @@
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN44">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7621,26 +7621,26 @@
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "37"]</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "65"]</t>
         </is>
       </c>
       <c r="AJ45">
@@ -7723,28 +7723,28 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -7796,14 +7796,14 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
@@ -7886,28 +7886,28 @@
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7947,26 +7947,26 @@
         </is>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "64", "68"]</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32"]</t>
         </is>
       </c>
       <c r="AJ47">
@@ -8049,28 +8049,28 @@
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ47">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AR47">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8110,26 +8110,26 @@
         </is>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H48">
         <v>0</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48">
         <v>0</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N48">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "52", "60", "86"]</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
@@ -8212,28 +8212,28 @@
         <v>0</v>
       </c>
       <c r="AM48">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN48">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO48">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP48">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ48">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AR48">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS48">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT48">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
@@ -8273,13 +8273,13 @@
         </is>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -8288,11 +8288,11 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N49">
@@ -8357,12 +8357,12 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31"]</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AJ49">
@@ -8375,28 +8375,28 @@
         <v>0</v>
       </c>
       <c r="AM49">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN49">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO49">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP49">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR49">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS49">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT49">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
@@ -8436,26 +8436,26 @@
         </is>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N50">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "54"]</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "41", "49"]</t>
         </is>
       </c>
       <c r="AJ50">
@@ -8538,28 +8538,28 @@
         <v>0</v>
       </c>
       <c r="AM50">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN50">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO50">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP50">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ50">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR50">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS50">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT50">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
@@ -8618,32 +8618,32 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q51">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R51">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S51">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="T51">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U51">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="V51">
         <v>1.17</v>
@@ -8652,25 +8652,25 @@
         <v>1.03</v>
       </c>
       <c r="X51">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y51">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="Z51">
-        <v>2.32</v>
+        <v>2.07</v>
       </c>
       <c r="AA51">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AB51">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC51">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AD51">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE51">
         <v>1.02</v>
@@ -8679,7 +8679,7 @@
         <v>2.25</v>
       </c>
       <c r="AG51">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,37 +8692,37 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK51">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AL51">
         <v>0</v>
       </c>
       <c r="AM51">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN51">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO51">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP51">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ51">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR51">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS51">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT51">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
@@ -8765,13 +8765,13 @@
         <v>0</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N52">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AJ52">
@@ -8864,28 +8864,28 @@
         <v>0</v>
       </c>
       <c r="AM52">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN52">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO52">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="AP52">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AR52">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS52">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT52">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
@@ -8925,26 +8925,26 @@
         </is>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53">
         <v>0</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N53">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "88"]</t>
         </is>
       </c>
       <c r="AJ53">
@@ -9027,28 +9027,28 @@
         <v>0</v>
       </c>
       <c r="AM53">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN53">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO53">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP53">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR53">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS53">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT53">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
@@ -9088,13 +9088,13 @@
         </is>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -9107,7 +9107,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N54">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
@@ -9190,28 +9190,28 @@
         <v>0</v>
       </c>
       <c r="AM54">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN54">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO54">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP54">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ54">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR54">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS54">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT54">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
@@ -9251,10 +9251,10 @@
         </is>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -9263,14 +9263,14 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N55">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52", "90+8"]</t>
         </is>
       </c>
       <c r="AJ55">
@@ -9353,28 +9353,28 @@
         <v>0</v>
       </c>
       <c r="AM55">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN55">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO55">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP55">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ55">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR55">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS55">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT55">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
@@ -9417,13 +9417,13 @@
         <v>0</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -9433,50 +9433,50 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N56">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O56">
         <v>3</v>
       </c>
       <c r="P56">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q56">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="R56">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="S56">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T56">
-        <v>2.58</v>
+        <v>2.39</v>
       </c>
       <c r="U56">
         <v>3.3</v>
       </c>
       <c r="V56">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X56">
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z56">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="AA56">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB56">
         <v>1.63</v>
@@ -9503,41 +9503,41 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AJ56">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK56">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AL56">
         <v>0</v>
       </c>
       <c r="AM56">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN56">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO56">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP56">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ56">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR56">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AS56">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT56">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
@@ -9577,54 +9577,54 @@
         </is>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57">
         <v>0</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N57">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="O57">
-        <v>3.85</v>
+        <v>3.96</v>
       </c>
       <c r="P57">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q57">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="R57">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="S57">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T57">
-        <v>4.45</v>
+        <v>4.15</v>
       </c>
       <c r="U57">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="V57">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="W57">
         <v>1.22</v>
@@ -9633,74 +9633,74 @@
         <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z57">
-        <v>4.2</v>
+        <v>7.05</v>
       </c>
       <c r="AA57">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AB57">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="AC57">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AD57">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AE57">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AF57">
         <v>1.2</v>
       </c>
       <c r="AG57">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "56", "59"]</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "17", "34", "44"]</t>
         </is>
       </c>
       <c r="AJ57">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK57">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL57">
         <v>0</v>
       </c>
       <c r="AM57">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN57">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO57">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP57">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ57">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR57">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AS57">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT57">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
@@ -9740,13 +9740,13 @@
         </is>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58">
         <v>0</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N58">
@@ -9772,98 +9772,98 @@
         <v>4.5</v>
       </c>
       <c r="Q58">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R58">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S58">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="T58">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="U58">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V58">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W58">
         <v>1.02</v>
       </c>
       <c r="X58">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z58">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA58">
         <v>2.35</v>
       </c>
       <c r="AB58">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC58">
         <v>4.3</v>
       </c>
       <c r="AD58">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE58">
         <v>1.02</v>
       </c>
       <c r="AF58">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AG58">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
+          <t>["20", "45"]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK58">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AL58">
         <v>0</v>
       </c>
       <c r="AM58">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN58">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO58">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP58">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ58">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR58">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS58">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT58">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
@@ -9903,26 +9903,26 @@
         </is>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59">
         <v>0</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N59">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "81"]</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
@@ -10005,28 +10005,28 @@
         <v>0</v>
       </c>
       <c r="AM59">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN59">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO59">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP59">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ59">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR59">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS59">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT59">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
@@ -10066,16 +10066,16 @@
         </is>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -10085,23 +10085,23 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N60">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="O60">
         <v>3</v>
       </c>
       <c r="P60">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="Q60">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="R60">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S60">
         <v>1.52</v>
@@ -10116,22 +10116,22 @@
         <v>1.33</v>
       </c>
       <c r="W60">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X60">
         <v>1.07</v>
       </c>
       <c r="Y60">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z60">
         <v>2.7</v>
       </c>
       <c r="AA60">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AB60">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC60">
         <v>3.6</v>
@@ -10140,56 +10140,56 @@
         <v>1.2</v>
       </c>
       <c r="AE60">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF60">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG60">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AJ60">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK60">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL60">
         <v>0</v>
       </c>
       <c r="AM60">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN60">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO60">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP60">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ60">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR60">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS60">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT60">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="O63">
+        <v>3.18</v>
+      </c>
+      <c r="P63">
+        <v>3</v>
+      </c>
+      <c r="Q63">
         <v>3.02</v>
       </c>
-      <c r="P63">
-        <v>3.44</v>
-      </c>
-      <c r="Q63">
+      <c r="R63">
+        <v>1.99</v>
+      </c>
+      <c r="S63">
+        <v>1.38</v>
+      </c>
+      <c r="T63">
+        <v>3.09</v>
+      </c>
+      <c r="U63">
         <v>2.62</v>
       </c>
-      <c r="R63">
-        <v>2</v>
-      </c>
-      <c r="S63">
-        <v>1.42</v>
-      </c>
-      <c r="T63">
-        <v>2.7</v>
-      </c>
-      <c r="U63">
-        <v>2.8</v>
-      </c>
       <c r="V63">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W63">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X63">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y63">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z63">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="AA63">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AB63">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC63">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="AD63">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AE63">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF63">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG63">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK63">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,28 +10741,28 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O64">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="P64">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q64">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="R64">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="S64">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T64">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="U64">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="V64">
         <v>1.62</v>
@@ -10771,34 +10771,34 @@
         <v>1.13</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z64">
-        <v>4.71</v>
+        <v>4.8</v>
       </c>
       <c r="AA64">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AB64">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AC64">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AD64">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE64">
         <v>1.23</v>
       </c>
       <c r="AF64">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG64">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK64">
         <v>2.7</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="O65">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P65">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q65">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="R65">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="S65">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="T65">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="U65">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="V65">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W65">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X65">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Y65">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="Z65">
         <v>2.03</v>
       </c>
       <c r="AA65">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AB65">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC65">
         <v>8</v>
       </c>
       <c r="AD65">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE65">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF65">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="AG65">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK65">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O66">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P66">
         <v>3.13</v>
@@ -11082,13 +11082,13 @@
         <v>2.09</v>
       </c>
       <c r="S66">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T66">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="U66">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="V66">
         <v>1.39</v>
@@ -11103,16 +11103,16 @@
         <v>1.23</v>
       </c>
       <c r="Z66">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AA66">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB66">
         <v>1.88</v>
       </c>
       <c r="AC66">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD66">
         <v>1.3</v>
@@ -11230,22 +11230,22 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="O67">
         <v>3.7</v>
       </c>
       <c r="P67">
-        <v>4.17</v>
+        <v>4.03</v>
       </c>
       <c r="Q67">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="R67">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="S67">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T67">
         <v>3</v>
@@ -11254,37 +11254,37 @@
         <v>2.6</v>
       </c>
       <c r="V67">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W67">
         <v>1.1</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
         <v>1.24</v>
       </c>
       <c r="Z67">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="AA67">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB67">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC67">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="AD67">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE67">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF67">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG67">
         <v>1.98</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK67">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,61 +11393,61 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="O68">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P68">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q68">
-        <v>3.7</v>
+        <v>3.96</v>
       </c>
       <c r="R68">
         <v>1.96</v>
       </c>
       <c r="S68">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T68">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U68">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="V68">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W68">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y68">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z68">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AA68">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AB68">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC68">
-        <v>3.82</v>
+        <v>3.96</v>
       </c>
       <c r="AD68">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE68">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF68">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG68">
         <v>1.87</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK68">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL68">
         <v>0</v>
